--- a/documentation/SimPaths_Variable_Codebook.xlsx
+++ b/documentation/SimPaths_Variable_Codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F07A3E-053E-A74A-84AD-D3241A71C4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6972B61-DCDD-8C4E-8D97-A47A82139316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="620" windowWidth="38400" windowHeight="19540" tabRatio="652" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="19500" tabRatio="652" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="9" r:id="rId1"/>
@@ -242,7 +242,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3808" uniqueCount="1822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3808" uniqueCount="1823">
   <si>
     <t>Description</t>
   </si>
@@ -5449,9 +5449,6 @@
     <t>yFinDstrssFlag</t>
   </si>
   <si>
-    <t>careCareFormal</t>
-  </si>
-  <si>
     <t>careHrsFormal</t>
   </si>
   <si>
@@ -6093,6 +6090,12 @@
     <t>Partnership status
  1 Partnered 
  2 Single</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>careFormalX</t>
   </si>
 </sst>
 </file>
@@ -6768,11 +6771,11 @@
         <v>1139</v>
       </c>
       <c r="I2" s="10" t="str">
-        <f>CONCATENATE(A2, B2,C2,D2,E2,F2,G2,H2)</f>
+        <f t="shared" ref="I2:I65" si="0">CONCATENATE(A2, B2,C2,D2,E2,F2,G2,H2)</f>
         <v>careAdj</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>850</v>
@@ -6781,7 +6784,7 @@
         <v>1023</v>
       </c>
       <c r="M2" s="10" t="str">
-        <f>IF(OR(O2&lt;&gt;"", Q2&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M2:M65" si="1">IF(OR(O2&lt;&gt;"", Q2&lt;&gt;""),"Yes","No")</f>
         <v>No</v>
       </c>
       <c r="R2" s="4" t="s">
@@ -6800,22 +6803,21 @@
         <f t="array" ref="B3">_xlfn.IFS(S3 = Modules!$A$2,Modules!$B$2,S3 = Modules!$A$3,Modules!$B$3,S3 = Modules!$A$4,Modules!$B$4,S3 = Modules!$A$5,Modules!$B$5,S3 = Modules!$A$6,Modules!$B$6,S3 = Modules!$A$7,Modules!$B$7,S3 = Modules!$A$8,Modules!$B$8,S3 = Modules!$A$9,Modules!$B$9,S3 = Modules!$A$10,Modules!$B$10,S3 = Modules!$A$11,Modules!$B$11,S3 = Modules!$A$12,Modules!$B$12, S3 = Modules!$A$13,Modules!$B$13)</f>
         <v>care</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>1058</v>
-      </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10" t="s">
         <v>1059</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="10" t="s">
+        <v>1821</v>
+      </c>
       <c r="H3" s="10"/>
       <c r="I3" s="10" t="str">
-        <f>CONCATENATE(A3, B3,C3,D3,E3,F3,G3,H3)</f>
-        <v>careCareFormal</v>
+        <f t="shared" si="0"/>
+        <v>careFormalX</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>1608</v>
+        <v>1822</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>679</v>
@@ -6824,7 +6826,7 @@
         <v>333</v>
       </c>
       <c r="M3" s="10" t="str">
-        <f>IF(OR(O3&lt;&gt;"", Q3&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N3" s="2" t="s">
@@ -6858,11 +6860,11 @@
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="str">
-        <f>CONCATENATE(A4, B4,C4,D4,E4,F4,G4,H4)</f>
+        <f t="shared" si="0"/>
         <v>careFormalFlag</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>854</v>
@@ -6871,7 +6873,7 @@
         <v>333</v>
       </c>
       <c r="M4" s="10" t="str">
-        <f>IF(OR(O4&lt;&gt;"", Q4&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S4" s="2" t="s">
@@ -6896,11 +6898,11 @@
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10" t="str">
-        <f>CONCATENATE(A5, B5,C5,D5,E5,F5,G5,H5)</f>
+        <f t="shared" si="0"/>
         <v>careFromDaughterFlag</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>856</v>
@@ -6909,7 +6911,7 @@
         <v>333</v>
       </c>
       <c r="M5" s="10" t="str">
-        <f>IF(OR(O5&lt;&gt;"", Q5&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S5" s="2" t="s">
@@ -6934,11 +6936,11 @@
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10" t="str">
-        <f>CONCATENATE(A6, B6,C6,D6,E6,F6,G6,H6)</f>
+        <f t="shared" si="0"/>
         <v>careFromOtherFlag</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>858</v>
@@ -6947,7 +6949,7 @@
         <v>333</v>
       </c>
       <c r="M6" s="10" t="str">
-        <f>IF(OR(O6&lt;&gt;"", Q6&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S6" s="2" t="s">
@@ -6972,11 +6974,11 @@
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="str">
-        <f>CONCATENATE(A7, B7,C7,D7,E7,F7,G7,H7)</f>
+        <f t="shared" si="0"/>
         <v>careFromPartnerFlag</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>855</v>
@@ -6985,7 +6987,7 @@
         <v>333</v>
       </c>
       <c r="M7" s="10" t="str">
-        <f>IF(OR(O7&lt;&gt;"", Q7&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S7" s="2" t="s">
@@ -7010,11 +7012,11 @@
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="10" t="str">
-        <f>CONCATENATE(A8, B8,C8,D8,E8,F8,G8,H8)</f>
+        <f t="shared" si="0"/>
         <v>careFromSonFlag</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>857</v>
@@ -7023,7 +7025,7 @@
         <v>333</v>
       </c>
       <c r="M8" s="10" t="str">
-        <f>IF(OR(O8&lt;&gt;"", Q8&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S8" s="2" t="s">
@@ -7045,11 +7047,11 @@
         <v>1059</v>
       </c>
       <c r="I9" s="10" t="str">
-        <f>CONCATENATE(A9, B9,C9,D9,E9,F9,G9,H9)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFormal</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>674</v>
@@ -7058,7 +7060,7 @@
         <v>333</v>
       </c>
       <c r="M9" s="10" t="str">
-        <f>IF(OR(O9&lt;&gt;"", Q9&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N9" s="2" t="s">
@@ -7093,7 +7095,7 @@
         <v>1002</v>
       </c>
       <c r="I10" s="10" t="str">
-        <f>CONCATENATE(A10, B10,C10,D10,E10,F10,G10,H10)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFormalWeek</v>
       </c>
       <c r="J10" s="10" t="s">
@@ -7106,7 +7108,7 @@
         <v>333</v>
       </c>
       <c r="M10" s="10" t="str">
-        <f>IF(OR(O10&lt;&gt;"", Q10&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S10" s="2" t="s">
@@ -7135,7 +7137,7 @@
         <v>1225</v>
       </c>
       <c r="I11" s="10" t="str">
-        <f>CONCATENATE(A11, B11,C11,D11,E11,F11,G11,H11)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFormalWeekL1</v>
       </c>
       <c r="J11" s="10" t="s">
@@ -7148,7 +7150,7 @@
         <v>333</v>
       </c>
       <c r="M11" s="10" t="str">
-        <f>IF(OR(O11&lt;&gt;"", Q11&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S11" s="2" t="s">
@@ -7175,7 +7177,7 @@
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10" t="str">
-        <f>CONCATENATE(A12, B12,C12,D12,E12,F12,G12,H12)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromDaughter</v>
       </c>
       <c r="J12" s="10" t="s">
@@ -7188,7 +7190,7 @@
         <v>333</v>
       </c>
       <c r="M12" s="10" t="str">
-        <f>IF(OR(O12&lt;&gt;"", Q12&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N12" s="2" t="s">
@@ -7223,7 +7225,7 @@
         <v>1002</v>
       </c>
       <c r="I13" s="10" t="str">
-        <f>CONCATENATE(A13, B13,C13,D13,E13,F13,G13,H13)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromDaughterWeek</v>
       </c>
       <c r="J13" s="10" t="s">
@@ -7236,7 +7238,7 @@
         <v>333</v>
       </c>
       <c r="M13" s="10" t="str">
-        <f>IF(OR(O13&lt;&gt;"", Q13&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S13" s="2" t="s">
@@ -7246,7 +7248,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="str" cm="1">
         <f t="array" ref="B14">_xlfn.IFS(S14 = Modules!$A$2,Modules!$B$2,S14 = Modules!$A$3,Modules!$B$3,S14 = Modules!$A$4,Modules!$B$4,S14 = Modules!$A$5,Modules!$B$5,S14 = Modules!$A$6,Modules!$B$6,S14 = Modules!$A$7,Modules!$B$7,S14 = Modules!$A$8,Modules!$B$8,S14 = Modules!$A$9,Modules!$B$9,S14 = Modules!$A$10,Modules!$B$10,S14 = Modules!$A$11,Modules!$B$11,S14 = Modules!$A$12,Modules!$B$12, S14 = Modules!$A$13,Modules!$B$13)</f>
@@ -7265,7 +7267,7 @@
         <v>1225</v>
       </c>
       <c r="I14" s="10" t="str">
-        <f>CONCATENATE(A14, B14,C14,D14,E14,F14,G14,H14)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromDaughterWeekL1</v>
       </c>
       <c r="J14" s="10" t="s">
@@ -7278,7 +7280,7 @@
         <v>333</v>
       </c>
       <c r="M14" s="10" t="str">
-        <f>IF(OR(O14&lt;&gt;"", Q14&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S14" s="2" t="s">
@@ -7305,11 +7307,11 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10" t="str">
-        <f>CONCATENATE(A15, B15,C15,D15,E15,F15,G15,H15)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromOther</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>678</v>
@@ -7318,7 +7320,7 @@
         <v>333</v>
       </c>
       <c r="M15" s="10" t="str">
-        <f>IF(OR(O15&lt;&gt;"", Q15&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N15" s="2" t="s">
@@ -7353,7 +7355,7 @@
         <v>1002</v>
       </c>
       <c r="I16" s="10" t="str">
-        <f>CONCATENATE(A16, B16,C16,D16,E16,F16,G16,H16)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromOtherWeek</v>
       </c>
       <c r="J16" s="10" t="s">
@@ -7366,7 +7368,7 @@
         <v>333</v>
       </c>
       <c r="M16" s="10" t="str">
-        <f>IF(OR(O16&lt;&gt;"", Q16&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S16" s="2" t="s">
@@ -7395,7 +7397,7 @@
         <v>1225</v>
       </c>
       <c r="I17" s="10" t="str">
-        <f>CONCATENATE(A17, B17,C17,D17,E17,F17,G17,H17)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromOtherWeekL1</v>
       </c>
       <c r="J17" s="10" t="s">
@@ -7408,7 +7410,7 @@
         <v>333</v>
       </c>
       <c r="M17" s="10" t="str">
-        <f>IF(OR(O17&lt;&gt;"", Q17&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S17" s="2" t="s">
@@ -7437,7 +7439,7 @@
         <v>1002</v>
       </c>
       <c r="I18" s="10" t="str">
-        <f>CONCATENATE(A18, B18,C18,D18,E18,F18,G18,H18)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromParentWeek</v>
       </c>
       <c r="J18" s="10" t="s">
@@ -7450,7 +7452,7 @@
         <v>333</v>
       </c>
       <c r="M18" s="10" t="str">
-        <f>IF(OR(O18&lt;&gt;"", Q18&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S18" s="2" t="s">
@@ -7479,7 +7481,7 @@
         <v>1225</v>
       </c>
       <c r="I19" s="10" t="str">
-        <f>CONCATENATE(A19, B19,C19,D19,E19,F19,G19,H19)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromParentWeekL1</v>
       </c>
       <c r="J19" s="10" t="s">
@@ -7492,7 +7494,7 @@
         <v>333</v>
       </c>
       <c r="M19" s="10" t="str">
-        <f>IF(OR(O19&lt;&gt;"", Q19&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S19" s="2" t="s">
@@ -7514,11 +7516,11 @@
         <v>1063</v>
       </c>
       <c r="I20" s="10" t="str">
-        <f>CONCATENATE(A20, B20,C20,D20,E20,F20,G20,H20)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromPartner</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>675</v>
@@ -7527,7 +7529,7 @@
         <v>333</v>
       </c>
       <c r="M20" s="10" t="str">
-        <f>IF(OR(O20&lt;&gt;"", Q20&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N20" s="2" t="s">
@@ -7562,7 +7564,7 @@
         <v>1002</v>
       </c>
       <c r="I21" s="10" t="str">
-        <f>CONCATENATE(A21, B21,C21,D21,E21,F21,G21,H21)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromPartnerWeek</v>
       </c>
       <c r="J21" s="10" t="s">
@@ -7575,7 +7577,7 @@
         <v>333</v>
       </c>
       <c r="M21" s="10" t="str">
-        <f>IF(OR(O21&lt;&gt;"", Q21&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S21" s="2" t="s">
@@ -7604,7 +7606,7 @@
         <v>1225</v>
       </c>
       <c r="I22" s="10" t="str">
-        <f>CONCATENATE(A22, B22,C22,D22,E22,F22,G22,H22)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromPartnerWeekL1</v>
       </c>
       <c r="J22" s="10" t="s">
@@ -7617,7 +7619,7 @@
         <v>333</v>
       </c>
       <c r="M22" s="10" t="str">
-        <f>IF(OR(O22&lt;&gt;"", Q22&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S22" s="2" t="s">
@@ -7644,11 +7646,11 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10" t="str">
-        <f>CONCATENATE(A23, B23,C23,D23,E23,F23,G23,H23)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromSon</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>677</v>
@@ -7657,7 +7659,7 @@
         <v>333</v>
       </c>
       <c r="M23" s="10" t="str">
-        <f>IF(OR(O23&lt;&gt;"", Q23&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N23" s="2" t="s">
@@ -7692,7 +7694,7 @@
         <v>1002</v>
       </c>
       <c r="I24" s="10" t="str">
-        <f>CONCATENATE(A24, B24,C24,D24,E24,F24,G24,H24)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromSonWeek</v>
       </c>
       <c r="J24" s="10" t="s">
@@ -7705,7 +7707,7 @@
         <v>333</v>
       </c>
       <c r="M24" s="10" t="str">
-        <f>IF(OR(O24&lt;&gt;"", Q24&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S24" s="2" t="s">
@@ -7734,7 +7736,7 @@
         <v>1225</v>
       </c>
       <c r="I25" s="10" t="str">
-        <f>CONCATENATE(A25, B25,C25,D25,E25,F25,G25,H25)</f>
+        <f t="shared" si="0"/>
         <v>careHrsFromSonWeekL1</v>
       </c>
       <c r="J25" s="10" t="s">
@@ -7747,7 +7749,7 @@
         <v>333</v>
       </c>
       <c r="M25" s="10" t="str">
-        <f>IF(OR(O25&lt;&gt;"", Q25&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S25" s="2" t="s">
@@ -7772,7 +7774,7 @@
         <v>1002</v>
       </c>
       <c r="I26" s="10" t="str">
-        <f>CONCATENATE(A26, B26,C26,D26,E26,F26,G26,H26)</f>
+        <f t="shared" si="0"/>
         <v>careHrsProvidedWeek</v>
       </c>
       <c r="J26" s="10" t="s">
@@ -7785,7 +7787,7 @@
         <v>333</v>
       </c>
       <c r="M26" s="10" t="str">
-        <f>IF(OR(O26&lt;&gt;"", Q26&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N26" s="2" t="s">
@@ -7823,7 +7825,7 @@
         <v>1002</v>
       </c>
       <c r="I27" s="10" t="str">
-        <f>CONCATENATE(A27, B27,C27,D27,E27,F27,G27,H27)</f>
+        <f t="shared" si="0"/>
         <v>careHrsProvidedWeek</v>
       </c>
       <c r="J27" s="10" t="s">
@@ -7836,7 +7838,7 @@
         <v>333</v>
       </c>
       <c r="M27" s="10" t="str">
-        <f>IF(OR(O27&lt;&gt;"", Q27&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S27" s="2" t="s">
@@ -7861,11 +7863,11 @@
         <v>968</v>
       </c>
       <c r="I28" s="10" t="str">
-        <f>CONCATENATE(A28, B28,C28,D28,E28,F28,G28,H28)</f>
+        <f t="shared" si="0"/>
         <v>careNeedFlag</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>672</v>
@@ -7874,7 +7876,7 @@
         <v>1021</v>
       </c>
       <c r="M28" s="10" t="str">
-        <f>IF(OR(O28&lt;&gt;"", Q28&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N28" s="2" t="s">
@@ -7902,11 +7904,11 @@
         <v>968</v>
       </c>
       <c r="I29" s="10" t="str">
-        <f>CONCATENATE(A29, B29,C29,D29,E29,F29,G29,H29)</f>
+        <f t="shared" si="0"/>
         <v>careNeedFlag</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>767</v>
@@ -7915,7 +7917,7 @@
         <v>333</v>
       </c>
       <c r="M29" s="10" t="str">
-        <f>IF(OR(O29&lt;&gt;"", Q29&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S29" s="2" t="s">
@@ -7940,11 +7942,11 @@
         <v>1050</v>
       </c>
       <c r="I30" s="10" t="str">
-        <f>CONCATENATE(A30, B30,C30,D30,E30,F30,G30,H30)</f>
+        <f t="shared" si="0"/>
         <v>careNeedFlagL1</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>768</v>
@@ -7953,7 +7955,7 @@
         <v>333</v>
       </c>
       <c r="M30" s="10" t="str">
-        <f>IF(OR(O30&lt;&gt;"", Q30&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S30" s="2" t="s">
@@ -7979,11 +7981,11 @@
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="10" t="str">
-        <f>CONCATENATE(A31, B31,C31,D31,E31,F31,G31,H31)</f>
+        <f t="shared" si="0"/>
         <v>careProvidedFlag</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>727</v>
@@ -7992,7 +7994,7 @@
         <v>449</v>
       </c>
       <c r="M31" s="10" t="str">
-        <f>IF(OR(O31&lt;&gt;"", Q31&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S31" s="2" t="s">
@@ -8023,11 +8025,11 @@
         <v>1050</v>
       </c>
       <c r="I32" s="10" t="str">
-        <f>CONCATENATE(A32, B32,C32,D32,E32,F32,G32,H32)</f>
+        <f t="shared" si="0"/>
         <v>careProvidedFlagL1</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>728</v>
@@ -8036,7 +8038,7 @@
         <v>333</v>
       </c>
       <c r="M32" s="10" t="str">
-        <f>IF(OR(O32&lt;&gt;"", Q32&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S32" s="2" t="s">
@@ -8061,11 +8063,11 @@
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="10" t="str">
-        <f>CONCATENATE(A33, B33,C33,D33,E33,F33,G33,H33)</f>
+        <f t="shared" si="0"/>
         <v>careReceivedFlag</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>853</v>
@@ -8074,7 +8076,7 @@
         <v>333</v>
       </c>
       <c r="M33" s="10" t="str">
-        <f>IF(OR(O33&lt;&gt;"", Q33&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S33" s="2" t="s">
@@ -8093,7 +8095,7 @@
         <v>1065</v>
       </c>
       <c r="I34" s="10" t="str">
-        <f>CONCATENATE(A34, B34,C34,D34,E34,F34,G34,H34)</f>
+        <f t="shared" si="0"/>
         <v>careWho</v>
       </c>
       <c r="J34" s="10" t="s">
@@ -8106,7 +8108,7 @@
         <v>170</v>
       </c>
       <c r="M34" s="10" t="str">
-        <f>IF(OR(O34&lt;&gt;"", Q34&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N34" s="2" t="s">
@@ -8137,7 +8139,7 @@
         <v>968</v>
       </c>
       <c r="I35" s="10" t="str">
-        <f>CONCATENATE(A35, B35,C35,D35,E35,F35,G35,H35)</f>
+        <f t="shared" si="0"/>
         <v>covidSEISSReceivedFlag</v>
       </c>
       <c r="J35" s="10" t="s">
@@ -8150,7 +8152,7 @@
         <v>333</v>
       </c>
       <c r="M35" s="10" t="str">
-        <f>IF(OR(O35&lt;&gt;"", Q35&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S35" s="2" t="s">
@@ -8172,7 +8174,7 @@
         <v>577</v>
       </c>
       <c r="I36" s="10" t="str">
-        <f>CONCATENATE(A36, B36,C36,D36,E36,F36,G36,H36)</f>
+        <f t="shared" si="0"/>
         <v>covidYLabGross</v>
       </c>
       <c r="J36" s="10" t="s">
@@ -8185,7 +8187,7 @@
         <v>333</v>
       </c>
       <c r="M36" s="10" t="str">
-        <f>IF(OR(O36&lt;&gt;"", Q36&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S36" s="2" t="s">
@@ -8210,7 +8212,7 @@
         <v>1050</v>
       </c>
       <c r="I37" s="10" t="str">
-        <f>CONCATENATE(A37, B37,C37,D37,E37,F37,G37,H37)</f>
+        <f t="shared" si="0"/>
         <v>covidYLabGrossL1</v>
       </c>
       <c r="J37" s="10" t="s">
@@ -8223,7 +8225,7 @@
         <v>333</v>
       </c>
       <c r="M37" s="10" t="str">
-        <f>IF(OR(O37&lt;&gt;"", Q37&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S37" s="2" t="s">
@@ -8252,7 +8254,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
       <c r="I38" s="10" t="str">
-        <f>CONCATENATE(A38, B38,C38,D38,E38,F38,G38,H38)</f>
+        <f t="shared" si="0"/>
         <v>covidYLabGrossXt5</v>
       </c>
       <c r="J38" s="10" t="s">
@@ -8265,7 +8267,7 @@
         <v>333</v>
       </c>
       <c r="M38" s="10" t="str">
-        <f>IF(OR(O38&lt;&gt;"", Q38&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S38" s="2" t="s">
@@ -8290,11 +8292,11 @@
         <v>1050</v>
       </c>
       <c r="I39" s="10" t="str">
-        <f>CONCATENATE(A39, B39,C39,D39,E39,F39,G39,H39)</f>
+        <f t="shared" si="0"/>
         <v>dem4to12L1</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>438</v>
@@ -8303,7 +8305,7 @@
         <v>449</v>
       </c>
       <c r="M39" s="10" t="str">
-        <f>IF(OR(O39&lt;&gt;"", Q39&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S39" s="2" t="s">
@@ -8325,7 +8327,7 @@
         <v>968</v>
       </c>
       <c r="I40" s="10" t="str">
-        <f>CONCATENATE(A40, B40,C40,D40,E40,F40,G40,H40)</f>
+        <f t="shared" si="0"/>
         <v>demAdultChildFlag</v>
       </c>
       <c r="J40" s="10" t="s">
@@ -8338,7 +8340,7 @@
         <v>333</v>
       </c>
       <c r="M40" s="10" t="str">
-        <f>IF(OR(O40&lt;&gt;"", Q40&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N40" s="2" t="s">
@@ -8369,7 +8371,7 @@
         <v>465</v>
       </c>
       <c r="I41" s="10" t="str">
-        <f>CONCATENATE(A41, B41,C41,D41,E41,F41,G41,H41)</f>
+        <f t="shared" si="0"/>
         <v>demAge</v>
       </c>
       <c r="J41" s="10" t="s">
@@ -8382,7 +8384,7 @@
         <v>333</v>
       </c>
       <c r="M41" s="10" t="str">
-        <f>IF(OR(O41&lt;&gt;"", Q41&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N41" s="2" t="s">
@@ -8419,7 +8421,7 @@
         <v>1084</v>
       </c>
       <c r="I42" s="10" t="str">
-        <f>CONCATENATE(A42, B42,C42,D42,E42,F42,G42,H42)</f>
+        <f t="shared" si="0"/>
         <v>demAgeDiffDesired</v>
       </c>
       <c r="J42" s="10" t="s">
@@ -8432,7 +8434,7 @@
         <v>333</v>
       </c>
       <c r="M42" s="10" t="str">
-        <f>IF(OR(O42&lt;&gt;"", Q42&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S42" s="2" t="s">
@@ -8460,11 +8462,11 @@
         <v>968</v>
       </c>
       <c r="I43" s="10" t="str">
-        <f>CONCATENATE(A43, B43,C43,D43,E43,F43,G43,H43)</f>
+        <f t="shared" si="0"/>
         <v>demAgeEduRangeFlag</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>929</v>
@@ -8473,7 +8475,7 @@
         <v>170</v>
       </c>
       <c r="M43" s="10" t="str">
-        <f>IF(OR(O43&lt;&gt;"", Q43&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N43" s="2" t="s">
@@ -8504,7 +8506,7 @@
         <v>1046</v>
       </c>
       <c r="I44" s="10" t="str">
-        <f>CONCATENATE(A44, B44,C44,D44,E44,F44,G44,H44)</f>
+        <f t="shared" si="0"/>
         <v>demAgeGroup</v>
       </c>
       <c r="J44" s="10" t="s">
@@ -8517,7 +8519,7 @@
         <v>333</v>
       </c>
       <c r="M44" s="10" t="str">
-        <f>IF(OR(O44&lt;&gt;"", Q44&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S44" s="2" t="s">
@@ -8539,7 +8541,7 @@
         <v>1074</v>
       </c>
       <c r="I45" s="10" t="str">
-        <f>CONCATENATE(A45, B45,C45,D45,E45,F45,G45,H45)</f>
+        <f t="shared" si="0"/>
         <v>demAgePartner</v>
       </c>
       <c r="J45" s="10" t="s">
@@ -8552,7 +8554,7 @@
         <v>170</v>
       </c>
       <c r="M45" s="10" t="str">
-        <f>IF(OR(O45&lt;&gt;"", Q45&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N45" s="2" t="s">
@@ -8586,7 +8588,7 @@
         <v>1073</v>
       </c>
       <c r="I46" s="10" t="str">
-        <f>CONCATENATE(A46, B46,C46,D46,E46,F46,G46,H46)</f>
+        <f t="shared" si="0"/>
         <v>demAgePartnerDiff</v>
       </c>
       <c r="J46" s="10" t="s">
@@ -8599,7 +8601,7 @@
         <v>333</v>
       </c>
       <c r="M46" s="10" t="str">
-        <f>IF(OR(O46&lt;&gt;"", Q46&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N46" s="2" t="s">
@@ -8642,7 +8644,7 @@
         <v>1050</v>
       </c>
       <c r="I47" s="10" t="str">
-        <f>CONCATENATE(A47, B47,C47,D47,E47,F47,G47,H47)</f>
+        <f t="shared" si="0"/>
         <v>demAgePartnerDiffL1</v>
       </c>
       <c r="J47" s="10" t="s">
@@ -8655,7 +8657,7 @@
         <v>333</v>
       </c>
       <c r="M47" s="10" t="str">
-        <f>IF(OR(O47&lt;&gt;"", Q47&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S47" s="2" t="s">
@@ -8677,7 +8679,7 @@
         <v>1075</v>
       </c>
       <c r="I48" s="10" t="str">
-        <f>CONCATENATE(A48, B48,C48,D48,E48,F48,G48,H48)</f>
+        <f t="shared" si="0"/>
         <v>demAgeSq</v>
       </c>
       <c r="J48" s="10" t="s">
@@ -8690,7 +8692,7 @@
         <v>333</v>
       </c>
       <c r="M48" s="10" t="str">
-        <f>IF(OR(O48&lt;&gt;"", Q48&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N48" s="2" t="s">
@@ -8726,11 +8728,11 @@
         <v>1386</v>
       </c>
       <c r="I49" s="10" t="str">
-        <f>CONCATENATE(A49, B49,C49,D49,E49,F49,G49,H49)</f>
+        <f t="shared" si="0"/>
         <v>demAlignPartnerProcess</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1385</v>
@@ -8739,7 +8741,7 @@
         <v>333</v>
       </c>
       <c r="M49" s="10" t="str">
-        <f>IF(OR(O49&lt;&gt;"", Q49&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S49" s="2" t="s">
@@ -8761,11 +8763,11 @@
         <v>968</v>
       </c>
       <c r="I50" s="10" t="str">
-        <f>CONCATENATE(A50, B50,C50,D50,E50,F50,G50,H50)</f>
+        <f t="shared" si="0"/>
         <v>demBePartnerFlag</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1390</v>
@@ -8774,7 +8776,7 @@
         <v>333</v>
       </c>
       <c r="M50" s="10" t="str">
-        <f>IF(OR(O50&lt;&gt;"", Q50&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S50" s="2" t="s">
@@ -8801,7 +8803,7 @@
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="10" t="str">
-        <f>CONCATENATE(A51, B51,C51,D51,E51,F51,G51,H51)</f>
+        <f t="shared" si="0"/>
         <v>demBornInSimFlag</v>
       </c>
       <c r="J51" s="10" t="s">
@@ -8814,7 +8816,7 @@
         <v>333</v>
       </c>
       <c r="M51" s="10" t="str">
-        <f>IF(OR(O51&lt;&gt;"", Q51&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S51" s="2" t="s">
@@ -8824,7 +8826,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="str" cm="1">
         <f t="array" ref="B52">_xlfn.IFS(S52 = Modules!$A$2,Modules!$B$2,S52 = Modules!$A$3,Modules!$B$3,S52 = Modules!$A$4,Modules!$B$4,S52 = Modules!$A$5,Modules!$B$5,S52 = Modules!$A$6,Modules!$B$6,S52 = Modules!$A$7,Modules!$B$7,S52 = Modules!$A$8,Modules!$B$8,S52 = Modules!$A$9,Modules!$B$9,S52 = Modules!$A$10,Modules!$B$10,S52 = Modules!$A$11,Modules!$B$11,S52 = Modules!$A$12,Modules!$B$12, S52 = Modules!$A$13,Modules!$B$13)</f>
@@ -8841,7 +8843,7 @@
       </c>
       <c r="H52" s="10"/>
       <c r="I52" s="10" t="str">
-        <f>CONCATENATE(A52, B52,C52,D52,E52,F52,G52,H52)</f>
+        <f t="shared" si="0"/>
         <v>demClonedFlag</v>
       </c>
       <c r="J52" s="10" t="s">
@@ -8854,7 +8856,7 @@
         <v>333</v>
       </c>
       <c r="M52" s="10" t="str">
-        <f>IF(OR(O52&lt;&gt;"", Q52&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S52" s="2" t="s">
@@ -8864,7 +8866,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="80" x14ac:dyDescent="0.2">
       <c r="B53" s="10" t="str" cm="1">
         <f t="array" ref="B53">_xlfn.IFS(S53 = Modules!$A$2,Modules!$B$2,S53 = Modules!$A$3,Modules!$B$3,S53 = Modules!$A$4,Modules!$B$4,S53 = Modules!$A$5,Modules!$B$5,S53 = Modules!$A$6,Modules!$B$6,S53 = Modules!$A$7,Modules!$B$7,S53 = Modules!$A$8,Modules!$B$8,S53 = Modules!$A$9,Modules!$B$9,S53 = Modules!$A$10,Modules!$B$10,S53 = Modules!$A$11,Modules!$B$11,S53 = Modules!$A$12,Modules!$B$12, S53 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -8876,7 +8878,7 @@
         <v>1103</v>
       </c>
       <c r="I53" s="10" t="str">
-        <f>CONCATENATE(A53, B53,C53,D53,E53,F53,G53,H53)</f>
+        <f t="shared" si="0"/>
         <v>demCompHh</v>
       </c>
       <c r="J53" s="10" t="s">
@@ -8889,7 +8891,7 @@
         <v>449</v>
       </c>
       <c r="M53" s="10" t="str">
-        <f>IF(OR(O53&lt;&gt;"", Q53&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N53" s="2" t="s">
@@ -8923,7 +8925,7 @@
         <v>1104</v>
       </c>
       <c r="I54" s="10" t="str">
-        <f>CONCATENATE(A54, B54,C54,D54,E54,F54,G54,H54)</f>
+        <f t="shared" si="0"/>
         <v>demCompHhC4</v>
       </c>
       <c r="J54" s="10" t="s">
@@ -8936,7 +8938,7 @@
         <v>449</v>
       </c>
       <c r="M54" s="10" t="str">
-        <f>IF(OR(O54&lt;&gt;"", Q54&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N54" s="2" t="s">
@@ -8979,7 +8981,7 @@
         <v>1050</v>
       </c>
       <c r="I55" s="10" t="str">
-        <f>CONCATENATE(A55, B55,C55,D55,E55,F55,G55,H55)</f>
+        <f t="shared" si="0"/>
         <v>demCompHhC4L1</v>
       </c>
       <c r="J55" s="10" t="s">
@@ -8992,7 +8994,7 @@
         <v>449</v>
       </c>
       <c r="M55" s="10" t="str">
-        <f>IF(OR(O55&lt;&gt;"", Q55&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S55" s="2" t="s">
@@ -9017,7 +9019,7 @@
         <v>1334</v>
       </c>
       <c r="I56" s="2" t="str">
-        <f>CONCATENATE(A56, B56,C56,D56,E56,F56,G56,H56)</f>
+        <f t="shared" si="0"/>
         <v>demCompHhC8</v>
       </c>
       <c r="J56" s="2" t="s">
@@ -9030,7 +9032,7 @@
         <v>333</v>
       </c>
       <c r="M56" s="10" t="str">
-        <f>IF(OR(O56&lt;&gt;"", Q56&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="P56" s="2" t="s">
@@ -9057,7 +9059,7 @@
         <v>458</v>
       </c>
       <c r="I57" s="19" t="str">
-        <f>CONCATENATE(A57, B57,C57,D57,E57,F57,G57,H57)</f>
+        <f t="shared" si="0"/>
         <v>demCountry</v>
       </c>
       <c r="J57" s="19" t="s">
@@ -9070,7 +9072,7 @@
         <v>1020</v>
       </c>
       <c r="M57" s="10" t="str">
-        <f>IF(OR(O57&lt;&gt;"", Q57&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="O57" s="2" t="s">
@@ -9094,7 +9096,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="B58" s="10" t="str" cm="1">
         <f t="array" ref="B58">_xlfn.IFS(S58 = Modules!$A$2,Modules!$B$2,S58 = Modules!$A$3,Modules!$B$3,S58 = Modules!$A$4,Modules!$B$4,S58 = Modules!$A$5,Modules!$B$5,S58 = Modules!$A$6,Modules!$B$6,S58 = Modules!$A$7,Modules!$B$7,S58 = Modules!$A$8,Modules!$B$8,S58 = Modules!$A$9,Modules!$B$9,S58 = Modules!$A$10,Modules!$B$10,S58 = Modules!$A$11,Modules!$B$11,S58 = Modules!$A$12,Modules!$B$12, S58 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -9103,7 +9105,7 @@
         <v>1072</v>
       </c>
       <c r="I58" s="10" t="str">
-        <f>CONCATENATE(A58, B58,C58,D58,E58,F58,G58,H58)</f>
+        <f t="shared" si="0"/>
         <v>demCreatedByConstructor</v>
       </c>
       <c r="J58" s="10" t="s">
@@ -9116,7 +9118,7 @@
         <v>449</v>
       </c>
       <c r="M58" s="10" t="str">
-        <f>IF(OR(O58&lt;&gt;"", Q58&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S58" s="2" t="s">
@@ -9141,11 +9143,11 @@
         <v>1425</v>
       </c>
       <c r="I59" s="10" t="str">
-        <f>CONCATENATE(A59, B59,C59,D59,E59,F59,G59,H59)</f>
+        <f t="shared" si="0"/>
         <v>demDbMatchTax</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1421</v>
@@ -9154,7 +9156,7 @@
         <v>449</v>
       </c>
       <c r="M59" s="10" t="str">
-        <f>IF(OR(O59&lt;&gt;"", Q59&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S59" s="2" t="s">
@@ -9183,11 +9185,11 @@
       </c>
       <c r="H60" s="10"/>
       <c r="I60" s="10" t="str">
-        <f>CONCATENATE(A60, B60,C60,D60,E60,F60,G60,H60)</f>
+        <f t="shared" si="0"/>
         <v>demDsbl18to29Share</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>835</v>
@@ -9196,7 +9198,7 @@
         <v>1019</v>
       </c>
       <c r="M60" s="10" t="str">
-        <f>IF(OR(O60&lt;&gt;"", Q60&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="R60" s="4" t="s">
@@ -9228,11 +9230,11 @@
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="10" t="str">
-        <f>CONCATENATE(A61, B61,C61,D61,E61,F61,G61,H61)</f>
+        <f t="shared" si="0"/>
         <v>demDsbl30to54Share</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>836</v>
@@ -9241,7 +9243,7 @@
         <v>1019</v>
       </c>
       <c r="M61" s="10" t="str">
-        <f>IF(OR(O61&lt;&gt;"", Q61&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="R61" s="4" t="s">
@@ -9273,11 +9275,11 @@
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="10" t="str">
-        <f>CONCATENATE(A62, B62,C62,D62,E62,F62,G62,H62)</f>
+        <f t="shared" si="0"/>
         <v>demDsbl55to74Share</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>837</v>
@@ -9286,7 +9288,7 @@
         <v>1019</v>
       </c>
       <c r="M62" s="10" t="str">
-        <f>IF(OR(O62&lt;&gt;"", Q62&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="R62" s="4" t="s">
@@ -9314,7 +9316,7 @@
         <v>968</v>
       </c>
       <c r="I63" s="10" t="str">
-        <f>CONCATENATE(A63, B63,C63,D63,E63,F63,G63,H63)</f>
+        <f t="shared" si="0"/>
         <v>demEnterPartnerFlag</v>
       </c>
       <c r="J63" s="10" t="s">
@@ -9327,7 +9329,7 @@
         <v>170</v>
       </c>
       <c r="M63" s="10" t="str">
-        <f>IF(OR(O63&lt;&gt;"", Q63&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="N63" s="2" t="s">
@@ -9367,7 +9369,7 @@
         <v>968</v>
       </c>
       <c r="I64" s="2" t="str">
-        <f>CONCATENATE(A64, B64,C64,D64,E64,F64,G64,H64)</f>
+        <f t="shared" si="0"/>
         <v>demEnterPartnerFlag</v>
       </c>
       <c r="J64" s="2" t="s">
@@ -9380,7 +9382,7 @@
         <v>333</v>
       </c>
       <c r="M64" s="10" t="str">
-        <f>IF(OR(O64&lt;&gt;"", Q64&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>Yes</v>
       </c>
       <c r="P64" s="2" t="s">
@@ -9413,11 +9415,11 @@
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10" t="str">
-        <f>CONCATENATE(A65, B65,C65,D65,E65,F65,G65,H65)</f>
+        <f t="shared" si="0"/>
         <v>demEnterSample</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1219</v>
@@ -9426,7 +9428,7 @@
         <v>333</v>
       </c>
       <c r="M65" s="10" t="str">
-        <f>IF(OR(O65&lt;&gt;"", Q65&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="1"/>
         <v>No</v>
       </c>
       <c r="S65" s="2" t="s">
@@ -9439,7 +9441,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="144" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:22" ht="80" x14ac:dyDescent="0.2">
       <c r="A66" s="10"/>
       <c r="B66" s="10" t="str" cm="1">
         <f t="array" ref="B66">_xlfn.IFS(S66 = Modules!$A$2,Modules!$B$2,S66 = Modules!$A$3,Modules!$B$3,S66 = Modules!$A$4,Modules!$B$4,S66 = Modules!$A$5,Modules!$B$5,S66 = Modules!$A$6,Modules!$B$6,S66 = Modules!$A$7,Modules!$B$7,S66 = Modules!$A$8,Modules!$B$8,S66 = Modules!$A$9,Modules!$B$9,S66 = Modules!$A$10,Modules!$B$10,S66 = Modules!$A$11,Modules!$B$11,S66 = Modules!$A$12,Modules!$B$12, S66 = Modules!$A$13,Modules!$B$13)</f>
@@ -9456,7 +9458,7 @@
       </c>
       <c r="H66" s="10"/>
       <c r="I66" s="10" t="str">
-        <f>CONCATENATE(A66, B66,C66,D66,E66,F66,G66,H66)</f>
+        <f t="shared" ref="I66:I129" si="2">CONCATENATE(A66, B66,C66,D66,E66,F66,G66,H66)</f>
         <v>demEthnC4</v>
       </c>
       <c r="J66" s="10" t="s">
@@ -9469,7 +9471,7 @@
         <v>333</v>
       </c>
       <c r="M66" s="10" t="str">
-        <f>IF(OR(O66&lt;&gt;"", Q66&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M66:M129" si="3">IF(OR(O66&lt;&gt;"", Q66&lt;&gt;""),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="N66" s="2" t="s">
@@ -9502,7 +9504,7 @@
       </c>
       <c r="H67" s="10"/>
       <c r="I67" s="10" t="str">
-        <f>CONCATENATE(A67, B67,C67,D67,E67,F67,G67,H67)</f>
+        <f t="shared" si="2"/>
         <v>demEthnC6</v>
       </c>
       <c r="J67" s="10" t="s">
@@ -9515,7 +9517,7 @@
         <v>333</v>
       </c>
       <c r="M67" s="10" t="str">
-        <f>IF(OR(O67&lt;&gt;"", Q67&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N67" s="2" t="s">
@@ -9549,7 +9551,7 @@
         <v>968</v>
       </c>
       <c r="I68" s="10" t="str">
-        <f>CONCATENATE(A68, B68,C68,D68,E68,F68,G68,H68)</f>
+        <f t="shared" si="2"/>
         <v>demExitParentHomeFlag</v>
       </c>
       <c r="J68" s="10" t="s">
@@ -9562,7 +9564,7 @@
         <v>170</v>
       </c>
       <c r="M68" s="10" t="str">
-        <f>IF(OR(O68&lt;&gt;"", Q68&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N68" s="2" t="s">
@@ -9602,7 +9604,7 @@
         <v>968</v>
       </c>
       <c r="I69" s="10" t="str">
-        <f>CONCATENATE(A69, B69,C69,D69,E69,F69,G69,H69)</f>
+        <f t="shared" si="2"/>
         <v>demExitPartnerFlag</v>
       </c>
       <c r="J69" s="10" t="s">
@@ -9615,7 +9617,7 @@
         <v>170</v>
       </c>
       <c r="M69" s="10" t="str">
-        <f>IF(OR(O69&lt;&gt;"", Q69&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N69" s="2" t="s">
@@ -9657,11 +9659,11 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="10" t="str">
-        <f>CONCATENATE(A70, B70,C70,D70,E70,F70,G70,H70)</f>
+        <f t="shared" si="2"/>
         <v>demExitSample</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>778</v>
@@ -9670,7 +9672,7 @@
         <v>333</v>
       </c>
       <c r="M70" s="10" t="str">
-        <f>IF(OR(O70&lt;&gt;"", Q70&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S70" s="2" t="s">
@@ -9700,7 +9702,7 @@
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
       <c r="I71" s="10" t="str">
-        <f>CONCATENATE(A71, B71,C71,D71,E71,F71,G71,H71)</f>
+        <f t="shared" si="2"/>
         <v>demFertAdj</v>
       </c>
       <c r="J71" s="10" t="s">
@@ -9713,7 +9715,7 @@
         <v>1023</v>
       </c>
       <c r="M71" s="10" t="str">
-        <f>IF(OR(O71&lt;&gt;"", Q71&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R71" s="4" t="s">
@@ -9742,11 +9744,11 @@
       </c>
       <c r="H72" s="10"/>
       <c r="I72" s="10" t="str">
-        <f>CONCATENATE(A72, B72,C72,D72,E72,F72,G72,H72)</f>
+        <f t="shared" si="2"/>
         <v>demFertFlag</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>918</v>
@@ -9755,7 +9757,7 @@
         <v>170</v>
       </c>
       <c r="M72" s="10" t="str">
-        <f>IF(OR(O72&lt;&gt;"", Q72&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N72" s="2" t="s">
@@ -9780,7 +9782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="10"/>
       <c r="B73" s="10" t="str" cm="1">
         <f t="array" ref="B73">_xlfn.IFS(S73 = Modules!$A$2,Modules!$B$2,S73 = Modules!$A$3,Modules!$B$3,S73 = Modules!$A$4,Modules!$B$4,S73 = Modules!$A$5,Modules!$B$5,S73 = Modules!$A$6,Modules!$B$6,S73 = Modules!$A$7,Modules!$B$7,S73 = Modules!$A$8,Modules!$B$8,S73 = Modules!$A$9,Modules!$B$9,S73 = Modules!$A$10,Modules!$B$10,S73 = Modules!$A$11,Modules!$B$11,S73 = Modules!$A$12,Modules!$B$12, S73 = Modules!$A$13,Modules!$B$13)</f>
@@ -9799,7 +9801,7 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="10" t="str">
-        <f>CONCATENATE(A73, B73,C73,D73,E73,F73,G73,H73)</f>
+        <f t="shared" si="2"/>
         <v>demFertRateSim</v>
       </c>
       <c r="J73" s="10" t="s">
@@ -9812,7 +9814,7 @@
         <v>1023</v>
       </c>
       <c r="M73" s="10" t="str">
-        <f>IF(OR(O73&lt;&gt;"", Q73&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R73" s="4" t="s">
@@ -9844,7 +9846,7 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="10" t="str">
-        <f>CONCATENATE(A74, B74,C74,D74,E74,F74,G74,H74)</f>
+        <f t="shared" si="2"/>
         <v>demFertRateTarget</v>
       </c>
       <c r="J74" s="10" t="s">
@@ -9857,7 +9859,7 @@
         <v>1023</v>
       </c>
       <c r="M74" s="10" t="str">
-        <f>IF(OR(O74&lt;&gt;"", Q74&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R74" s="4" t="s">
@@ -9870,7 +9872,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="80" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B75" s="10" t="str" cm="1">
         <f t="array" ref="B75">_xlfn.IFS(S75 = Modules!$A$2,Modules!$B$2,S75 = Modules!$A$3,Modules!$B$3,S75 = Modules!$A$4,Modules!$B$4,S75 = Modules!$A$5,Modules!$B$5,S75 = Modules!$A$6,Modules!$B$6,S75 = Modules!$A$7,Modules!$B$7,S75 = Modules!$A$8,Modules!$B$8,S75 = Modules!$A$9,Modules!$B$9,S75 = Modules!$A$10,Modules!$B$10,S75 = Modules!$A$11,Modules!$B$11,S75 = Modules!$A$12,Modules!$B$12, S75 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -9882,11 +9884,11 @@
         <v>968</v>
       </c>
       <c r="I75" s="10" t="str">
-        <f>CONCATENATE(A75, B75,C75,D75,E75,F75,G75,H75)</f>
+        <f t="shared" si="2"/>
         <v>demGiveBirthFlag</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>1391</v>
@@ -9895,7 +9897,7 @@
         <v>333</v>
       </c>
       <c r="M75" s="10" t="str">
-        <f>IF(OR(O75&lt;&gt;"", Q75&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S75" s="2" t="s">
@@ -9917,11 +9919,11 @@
         <v>968</v>
       </c>
       <c r="I76" s="10" t="str">
-        <f>CONCATENATE(A76, B76,C76,D76,E76,F76,G76,H76)</f>
+        <f t="shared" si="2"/>
         <v>demIoFlag</v>
       </c>
       <c r="J76" s="10" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>852</v>
@@ -9930,7 +9932,7 @@
         <v>333</v>
       </c>
       <c r="M76" s="10" t="str">
-        <f>IF(OR(O76&lt;&gt;"", Q76&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S76" s="2" t="s">
@@ -9955,11 +9957,11 @@
         <v>968</v>
       </c>
       <c r="I77" s="10" t="str">
-        <f>CONCATENATE(A77, B77,C77,D77,E77,F77,G77,H77)</f>
+        <f t="shared" si="2"/>
         <v>demLeavePartnerFlag</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>400</v>
@@ -9968,7 +9970,7 @@
         <v>333</v>
       </c>
       <c r="M77" s="10" t="str">
-        <f>IF(OR(O77&lt;&gt;"", Q77&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S77" s="2" t="s">
@@ -9993,11 +9995,11 @@
         <v>968</v>
       </c>
       <c r="I78" s="10" t="str">
-        <f>CONCATENATE(A78, B78,C78,D78,E78,F78,G78,H78)</f>
+        <f t="shared" si="2"/>
         <v>demLeftPartnerFlag</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>866</v>
@@ -10006,7 +10008,7 @@
         <v>333</v>
       </c>
       <c r="M78" s="10" t="str">
-        <f>IF(OR(O78&lt;&gt;"", Q78&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S78" s="2" t="s">
@@ -10016,7 +10018,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="192" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="10"/>
       <c r="B79" s="10" t="str" cm="1">
         <f t="array" ref="B79">_xlfn.IFS(S79 = Modules!$A$2,Modules!$B$2,S79 = Modules!$A$3,Modules!$B$3,S79 = Modules!$A$4,Modules!$B$4,S79 = Modules!$A$5,Modules!$B$5,S79 = Modules!$A$6,Modules!$B$6,S79 = Modules!$A$7,Modules!$B$7,S79 = Modules!$A$8,Modules!$B$8,S79 = Modules!$A$9,Modules!$B$9,S79 = Modules!$A$10,Modules!$B$10,S79 = Modules!$A$11,Modules!$B$11,S79 = Modules!$A$12,Modules!$B$12, S79 = Modules!$A$13,Modules!$B$13)</f>
@@ -10033,11 +10035,11 @@
       </c>
       <c r="H79" s="10"/>
       <c r="I79" s="10" t="str">
-        <f>CONCATENATE(A79, B79,C79,D79,E79,F79,G79,H79)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatEQ5D</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>760</v>
@@ -10046,7 +10048,7 @@
         <v>333</v>
       </c>
       <c r="M79" s="10" t="str">
-        <f>IF(OR(O79&lt;&gt;"", Q79&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S79" s="2" t="s">
@@ -10078,20 +10080,20 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="10" t="str">
-        <f>CONCATENATE(A80, B80,C80,D80,E80,F80,G80,H80)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7</v>
       </c>
       <c r="J80" s="10" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K80" s="2" t="s">
         <v>1804</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>1805</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>333</v>
       </c>
       <c r="M80" s="10" t="str">
-        <f>IF(OR(O80&lt;&gt;"", Q80&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N80" s="2" t="s">
@@ -10104,7 +10106,7 @@
         <v>962</v>
       </c>
       <c r="U80" s="2" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="V80" s="10" t="s">
         <v>165</v>
@@ -10131,11 +10133,11 @@
       </c>
       <c r="H81" s="10"/>
       <c r="I81" s="10" t="str">
-        <f>CONCATENATE(A81, B81,C81,D81,E81,F81,G81,H81)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7Avg</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>616</v>
@@ -10144,7 +10146,7 @@
         <v>1021</v>
       </c>
       <c r="M81" s="10" t="str">
-        <f>IF(OR(O81&lt;&gt;"", Q81&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R81" s="4" t="s">
@@ -10177,11 +10179,11 @@
         <v>1050</v>
       </c>
       <c r="I82" s="10" t="str">
-        <f>CONCATENATE(A82, B82,C82,D82,E82,F82,G82,H82)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7L1</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>687</v>
@@ -10190,7 +10192,7 @@
         <v>333</v>
       </c>
       <c r="M82" s="10" t="str">
-        <f>IF(OR(O82&lt;&gt;"", Q82&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S82" s="2" t="s">
@@ -10221,11 +10223,11 @@
       </c>
       <c r="H83" s="10"/>
       <c r="I83" s="10" t="str">
-        <f>CONCATENATE(A83, B83,C83,D83,E83,F83,G83,H83)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7P10</v>
       </c>
       <c r="J83" s="10" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>618</v>
@@ -10234,7 +10236,7 @@
         <v>1021</v>
       </c>
       <c r="M83" s="10" t="str">
-        <f>IF(OR(O83&lt;&gt;"", Q83&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R83" s="4" t="s">
@@ -10268,11 +10270,11 @@
       </c>
       <c r="H84" s="10"/>
       <c r="I84" s="10" t="str">
-        <f>CONCATENATE(A84, B84,C84,D84,E84,F84,G84,H84)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7P25</v>
       </c>
       <c r="J84" s="10" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>619</v>
@@ -10281,7 +10283,7 @@
         <v>1021</v>
       </c>
       <c r="M84" s="10" t="str">
-        <f>IF(OR(O84&lt;&gt;"", Q84&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R84" s="4" t="s">
@@ -10315,11 +10317,11 @@
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="10" t="str">
-        <f>CONCATENATE(A85, B85,C85,D85,E85,F85,G85,H85)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7P50</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>617</v>
@@ -10328,7 +10330,7 @@
         <v>1021</v>
       </c>
       <c r="M85" s="10" t="str">
-        <f>IF(OR(O85&lt;&gt;"", Q85&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R85" s="4" t="s">
@@ -10362,11 +10364,11 @@
       </c>
       <c r="H86" s="10"/>
       <c r="I86" s="10" t="str">
-        <f>CONCATENATE(A86, B86,C86,D86,E86,F86,G86,H86)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7P75</v>
       </c>
       <c r="J86" s="10" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>620</v>
@@ -10375,7 +10377,7 @@
         <v>1021</v>
       </c>
       <c r="M86" s="10" t="str">
-        <f>IF(OR(O86&lt;&gt;"", Q86&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R86" s="4" t="s">
@@ -10409,20 +10411,20 @@
       </c>
       <c r="H87" s="10"/>
       <c r="I87" s="10" t="str">
-        <f>CONCATENATE(A87, B87,C87,D87,E87,F87,G87,H87)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7P90</v>
       </c>
       <c r="J87" s="10" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="L87" s="10" t="s">
         <v>1021</v>
       </c>
       <c r="M87" s="10" t="str">
-        <f>IF(OR(O87&lt;&gt;"", Q87&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R87" s="4" t="s">
@@ -10456,11 +10458,11 @@
       </c>
       <c r="H88" s="10"/>
       <c r="I88" s="10" t="str">
-        <f>CONCATENATE(A88, B88,C88,D88,E88,F88,G88,H88)</f>
+        <f t="shared" si="2"/>
         <v>demLifeSatScore1to7Pred</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>688</v>
@@ -10469,7 +10471,7 @@
         <v>333</v>
       </c>
       <c r="M88" s="10" t="str">
-        <f>IF(OR(O88&lt;&gt;"", Q88&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S88" s="2" t="s">
@@ -10491,7 +10493,7 @@
         <v>968</v>
       </c>
       <c r="I89" s="10" t="str">
-        <f>CONCATENATE(A89, B89,C89,D89,E89,F89,G89,H89)</f>
+        <f t="shared" si="2"/>
         <v>demMaleFlag</v>
       </c>
       <c r="J89" s="10" t="s">
@@ -10504,7 +10506,7 @@
         <v>333</v>
       </c>
       <c r="M89" s="10" t="str">
-        <f>IF(OR(O89&lt;&gt;"", Q89&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N89" s="2" t="s">
@@ -10529,7 +10531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B90" s="10" t="str" cm="1">
         <f t="array" ref="B90">_xlfn.IFS(S90 = Modules!$A$2,Modules!$B$2,S90 = Modules!$A$3,Modules!$B$3,S90 = Modules!$A$4,Modules!$B$4,S90 = Modules!$A$5,Modules!$B$5,S90 = Modules!$A$6,Modules!$B$6,S90 = Modules!$A$7,Modules!$B$7,S90 = Modules!$A$8,Modules!$B$8,S90 = Modules!$A$9,Modules!$B$9,S90 = Modules!$A$10,Modules!$B$10,S90 = Modules!$A$11,Modules!$B$11,S90 = Modules!$A$12,Modules!$B$12, S90 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -10544,7 +10546,7 @@
         <v>968</v>
       </c>
       <c r="I90" s="10" t="str">
-        <f>CONCATENATE(A90, B90,C90,D90,E90,F90,G90,H90)</f>
+        <f t="shared" si="2"/>
         <v>demMalePartnerFlag</v>
       </c>
       <c r="J90" s="10" t="s">
@@ -10554,7 +10556,7 @@
         <v>907</v>
       </c>
       <c r="M90" s="10" t="str">
-        <f>IF(OR(O90&lt;&gt;"", Q90&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="O90" s="4"/>
@@ -10590,11 +10592,11 @@
       </c>
       <c r="H91" s="10"/>
       <c r="I91" s="10" t="str">
-        <f>CONCATENATE(A91, B91,C91,D91,E91,F91,G91,H91)</f>
+        <f t="shared" si="2"/>
         <v>demMarried18to29Share</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>838</v>
@@ -10603,7 +10605,7 @@
         <v>1019</v>
       </c>
       <c r="M91" s="10" t="str">
-        <f>IF(OR(O91&lt;&gt;"", Q91&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R91" s="4" t="s">
@@ -10635,11 +10637,11 @@
       </c>
       <c r="H92" s="10"/>
       <c r="I92" s="10" t="str">
-        <f>CONCATENATE(A92, B92,C92,D92,E92,F92,G92,H92)</f>
+        <f t="shared" si="2"/>
         <v>demMarried30to54Share</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>839</v>
@@ -10648,7 +10650,7 @@
         <v>1019</v>
       </c>
       <c r="M92" s="10" t="str">
-        <f>IF(OR(O92&lt;&gt;"", Q92&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R92" s="4" t="s">
@@ -10680,11 +10682,11 @@
       </c>
       <c r="H93" s="10"/>
       <c r="I93" s="10" t="str">
-        <f>CONCATENATE(A93, B93,C93,D93,E93,F93,G93,H93)</f>
+        <f t="shared" si="2"/>
         <v>demMarried55to74Share</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>840</v>
@@ -10693,7 +10695,7 @@
         <v>1019</v>
       </c>
       <c r="M93" s="10" t="str">
-        <f>IF(OR(O93&lt;&gt;"", Q93&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R93" s="4" t="s">
@@ -10715,7 +10717,7 @@
         <v>1127</v>
       </c>
       <c r="I94" s="10" t="str">
-        <f>CONCATENATE(A94, B94,C94,D94,E94,F94,G94,H94)</f>
+        <f t="shared" si="2"/>
         <v>demNChild</v>
       </c>
       <c r="J94" s="10" t="s">
@@ -10728,7 +10730,7 @@
         <v>333</v>
       </c>
       <c r="M94" s="10" t="str">
-        <f>IF(OR(O94&lt;&gt;"", Q94&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N94" s="2" t="s">
@@ -10765,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="2" t="str">
-        <f>CONCATENATE(A95, B95,C95,D95,E95,F95,G95,H95)</f>
+        <f t="shared" si="2"/>
         <v>demNChild0</v>
       </c>
       <c r="J95" s="2" t="s">
@@ -10775,7 +10777,7 @@
         <v>1332</v>
       </c>
       <c r="M95" s="10" t="str">
-        <f>IF(OR(O95&lt;&gt;"", Q95&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P95" s="2" t="s">
@@ -10803,7 +10805,7 @@
         <v>1128</v>
       </c>
       <c r="I96" s="10" t="str">
-        <f>CONCATENATE(A96, B96,C96,D96,E96,F96,G96,H96)</f>
+        <f t="shared" si="2"/>
         <v>demNChild0to2</v>
       </c>
       <c r="J96" s="10" t="s">
@@ -10816,7 +10818,7 @@
         <v>333</v>
       </c>
       <c r="M96" s="10" t="str">
-        <f>IF(OR(O96&lt;&gt;"", Q96&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N96" s="2" t="s">
@@ -10860,7 +10862,7 @@
       </c>
       <c r="H97" s="10"/>
       <c r="I97" s="10" t="str">
-        <f>CONCATENATE(A97, B97,C97,D97,E97,F97,G97,H97)</f>
+        <f t="shared" si="2"/>
         <v>demNChild18to29Avg</v>
       </c>
       <c r="J97" s="10" t="s">
@@ -10873,7 +10875,7 @@
         <v>1019</v>
       </c>
       <c r="M97" s="10" t="str">
-        <f>IF(OR(O97&lt;&gt;"", Q97&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R97" s="4" t="s">
@@ -10905,7 +10907,7 @@
       </c>
       <c r="H98" s="10"/>
       <c r="I98" s="10" t="str">
-        <f>CONCATENATE(A98, B98,C98,D98,E98,F98,G98,H98)</f>
+        <f t="shared" si="2"/>
         <v>demNChild30to54Avg</v>
       </c>
       <c r="J98" s="10" t="s">
@@ -10918,7 +10920,7 @@
         <v>1019</v>
       </c>
       <c r="M98" s="10" t="str">
-        <f>IF(OR(O98&lt;&gt;"", Q98&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R98" s="4" t="s">
@@ -10950,7 +10952,7 @@
       </c>
       <c r="H99" s="10"/>
       <c r="I99" s="10" t="str">
-        <f>CONCATENATE(A99, B99,C99,D99,E99,F99,G99,H99)</f>
+        <f t="shared" si="2"/>
         <v>demNChild55to74Avg</v>
       </c>
       <c r="J99" s="10" t="s">
@@ -10963,7 +10965,7 @@
         <v>1019</v>
       </c>
       <c r="M99" s="10" t="str">
-        <f>IF(OR(O99&lt;&gt;"", Q99&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R99" s="4" t="s">
@@ -10993,11 +10995,11 @@
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
       <c r="I100" s="10" t="str">
-        <f>CONCATENATE(A100, B100,C100,D100,E100,F100,G100,H100)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerAdj</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>847</v>
@@ -11006,7 +11008,7 @@
         <v>1023</v>
       </c>
       <c r="M100" s="10" t="str">
-        <f>IF(OR(O100&lt;&gt;"", Q100&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R100" s="4" t="s">
@@ -11031,7 +11033,7 @@
         <v>1080</v>
       </c>
       <c r="I101" s="10" t="str">
-        <f>CONCATENATE(A101, B101,C101,D101,E101,F101,G101,H101)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerNYear</v>
       </c>
       <c r="J101" s="10" t="s">
@@ -11044,7 +11046,7 @@
         <v>333</v>
       </c>
       <c r="M101" s="10" t="str">
-        <f>IF(OR(O101&lt;&gt;"", Q101&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N101" s="2" t="s">
@@ -11084,7 +11086,7 @@
         <v>1050</v>
       </c>
       <c r="I102" s="10" t="str">
-        <f>CONCATENATE(A102, B102,C102,D102,E102,F102,G102,H102)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerNYearL1</v>
       </c>
       <c r="J102" s="10" t="s">
@@ -11097,7 +11099,7 @@
         <v>333</v>
       </c>
       <c r="M102" s="10" t="str">
-        <f>IF(OR(O102&lt;&gt;"", Q102&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S102" s="2" t="s">
@@ -11107,7 +11109,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="103" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B103" s="10" t="str" cm="1">
         <f t="array" ref="B103">_xlfn.IFS(S103 = Modules!$A$2,Modules!$B$2,S103 = Modules!$A$3,Modules!$B$3,S103 = Modules!$A$4,Modules!$B$4,S103 = Modules!$A$5,Modules!$B$5,S103 = Modules!$A$6,Modules!$B$6,S103 = Modules!$A$7,Modules!$B$7,S103 = Modules!$A$8,Modules!$B$8,S103 = Modules!$A$9,Modules!$B$9,S103 = Modules!$A$10,Modules!$B$10,S103 = Modules!$A$11,Modules!$B$11,S103 = Modules!$A$12,Modules!$B$12, S103 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -11124,11 +11126,11 @@
       </c>
       <c r="H103" s="10"/>
       <c r="I103" s="10" t="str">
-        <f>CONCATENATE(A103, B103,C103,D103,E103,F103,G103,H103)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerSameSexFlag</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>917</v>
@@ -11137,7 +11139,7 @@
         <v>170</v>
       </c>
       <c r="M103" s="10" t="str">
-        <f>IF(OR(O103&lt;&gt;"", Q103&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N103" s="2" t="s">
@@ -11180,11 +11182,11 @@
       </c>
       <c r="H104" s="10"/>
       <c r="I104" s="10" t="str">
-        <f>CONCATENATE(A104, B104,C104,D104,E104,F104,G104,H104)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerSimShare</v>
       </c>
       <c r="J104" s="10" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>848</v>
@@ -11193,7 +11195,7 @@
         <v>1023</v>
       </c>
       <c r="M104" s="10" t="str">
-        <f>IF(OR(O104&lt;&gt;"", Q104&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R104" s="4" t="s">
@@ -11218,20 +11220,20 @@
         <v>530</v>
       </c>
       <c r="I105" s="10" t="str">
-        <f>CONCATENATE(A105, B105,C105,D105,E105,F105,G105,H105)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerStatus</v>
       </c>
       <c r="J105" s="10" t="s">
         <v>1521</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>333</v>
       </c>
       <c r="M105" s="10" t="str">
-        <f>IF(OR(O105&lt;&gt;"", Q105&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N105" s="2" t="s">
@@ -11271,7 +11273,7 @@
         <v>1050</v>
       </c>
       <c r="I106" s="10" t="str">
-        <f>CONCATENATE(A106, B106,C106,D106,E106,F106,G106,H106)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerStatusL1</v>
       </c>
       <c r="J106" s="10" t="s">
@@ -11284,7 +11286,7 @@
         <v>333</v>
       </c>
       <c r="M106" s="10" t="str">
-        <f>IF(OR(O106&lt;&gt;"", Q106&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S106" s="2" t="s">
@@ -11294,7 +11296,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="107" spans="1:22" ht="96" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B107" s="10" t="str" cm="1">
         <f t="array" ref="B107">_xlfn.IFS(S107 = Modules!$A$2,Modules!$B$2,S107 = Modules!$A$3,Modules!$B$3,S107 = Modules!$A$4,Modules!$B$4,S107 = Modules!$A$5,Modules!$B$5,S107 = Modules!$A$6,Modules!$B$6,S107 = Modules!$A$7,Modules!$B$7,S107 = Modules!$A$8,Modules!$B$8,S107 = Modules!$A$9,Modules!$B$9,S107 = Modules!$A$10,Modules!$B$10,S107 = Modules!$A$11,Modules!$B$11,S107 = Modules!$A$12,Modules!$B$12, S107 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -11309,7 +11311,7 @@
         <v>1078</v>
       </c>
       <c r="I107" s="10" t="str">
-        <f>CONCATENATE(A107, B107,C107,D107,E107,F107,G107,H107)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerStatusL2</v>
       </c>
       <c r="J107" s="10" t="s">
@@ -11322,7 +11324,7 @@
         <v>333</v>
       </c>
       <c r="M107" s="10" t="str">
-        <f>IF(OR(O107&lt;&gt;"", Q107&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S107" s="2" t="s">
@@ -11350,11 +11352,11 @@
       </c>
       <c r="H108" s="10"/>
       <c r="I108" s="10" t="str">
-        <f>CONCATENATE(A108, B108,C108,D108,E108,F108,G108,H108)</f>
+        <f t="shared" si="2"/>
         <v>demPartnerTargetShare</v>
       </c>
       <c r="J108" s="10" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>849</v>
@@ -11363,7 +11365,7 @@
         <v>1023</v>
       </c>
       <c r="M108" s="10" t="str">
-        <f>IF(OR(O108&lt;&gt;"", Q108&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R108" s="4" t="s">
@@ -11391,7 +11393,7 @@
         <v>968</v>
       </c>
       <c r="I109" s="2" t="str">
-        <f>CONCATENATE(A109, B109,C109,D109,E109,F109,G109,H109)</f>
+        <f t="shared" si="2"/>
         <v>demPensAgeFlag</v>
       </c>
       <c r="J109" s="2" t="s">
@@ -11401,7 +11403,7 @@
         <v>1324</v>
       </c>
       <c r="M109" s="10" t="str">
-        <f>IF(OR(O109&lt;&gt;"", Q109&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N109" s="6"/>
@@ -11438,7 +11440,7 @@
         <v>968</v>
       </c>
       <c r="I110" s="2" t="str">
-        <f>CONCATENATE(A110, B110,C110,D110,E110,F110,G110,H110)</f>
+        <f t="shared" si="2"/>
         <v>demPensEnterAgeFlag</v>
       </c>
       <c r="J110" s="2" t="s">
@@ -11448,7 +11450,7 @@
         <v>1325</v>
       </c>
       <c r="M110" s="10" t="str">
-        <f>IF(OR(O110&lt;&gt;"", Q110&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P110" s="6" t="s">
@@ -11485,7 +11487,7 @@
         <v>1050</v>
       </c>
       <c r="I111" s="2" t="str">
-        <f>CONCATENATE(A111, B111,C111,D111,E111,F111,G111,H111)</f>
+        <f t="shared" si="2"/>
         <v>demPensEnterAgeFlagL1</v>
       </c>
       <c r="J111" s="2" t="s">
@@ -11495,7 +11497,7 @@
         <v>1326</v>
       </c>
       <c r="M111" s="10" t="str">
-        <f>IF(OR(O111&lt;&gt;"", Q111&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P111" s="6" t="s">
@@ -11529,7 +11531,7 @@
         <v>968</v>
       </c>
       <c r="I112" s="2" t="str">
-        <f>CONCATENATE(A112, B112,C112,D112,E112,F112,G112,H112)</f>
+        <f t="shared" si="2"/>
         <v>demPensPartnerAgeFlag</v>
       </c>
       <c r="J112" s="2" t="s">
@@ -11539,7 +11541,7 @@
         <v>1328</v>
       </c>
       <c r="M112" s="10" t="str">
-        <f>IF(OR(O112&lt;&gt;"", Q112&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P112" s="6" t="s">
@@ -11576,7 +11578,7 @@
         <v>968</v>
       </c>
       <c r="I113" s="2" t="str">
-        <f>CONCATENATE(A113, B113,C113,D113,E113,F113,G113,H113)</f>
+        <f t="shared" si="2"/>
         <v>demPensPartnerEnterAgeFlag</v>
       </c>
       <c r="J113" s="2" t="s">
@@ -11586,7 +11588,7 @@
         <v>1329</v>
       </c>
       <c r="M113" s="10" t="str">
-        <f>IF(OR(O113&lt;&gt;"", Q113&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P113" s="6" t="s">
@@ -11626,7 +11628,7 @@
         <v>1050</v>
       </c>
       <c r="I114" s="2" t="str">
-        <f>CONCATENATE(A114, B114,C114,D114,E114,F114,G114,H114)</f>
+        <f t="shared" si="2"/>
         <v>demPensPartnerEnterAgeFlagL1</v>
       </c>
       <c r="J114" s="2" t="s">
@@ -11636,7 +11638,7 @@
         <v>1330</v>
       </c>
       <c r="M114" s="10" t="str">
-        <f>IF(OR(O114&lt;&gt;"", Q114&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="P114" s="6" t="s">
@@ -11671,11 +11673,11 @@
       </c>
       <c r="H115" s="10"/>
       <c r="I115" s="10" t="str">
-        <f>CONCATENATE(A115, B115,C115,D115,E115,F115,G115,H115)</f>
+        <f t="shared" si="2"/>
         <v>demPop18to29N</v>
       </c>
       <c r="J115" s="10" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>832</v>
@@ -11684,7 +11686,7 @@
         <v>1019</v>
       </c>
       <c r="M115" s="10" t="str">
-        <f>IF(OR(O115&lt;&gt;"", Q115&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R115" s="4" t="s">
@@ -11716,11 +11718,11 @@
       </c>
       <c r="H116" s="10"/>
       <c r="I116" s="10" t="str">
-        <f>CONCATENATE(A116, B116,C116,D116,E116,F116,G116,H116)</f>
+        <f t="shared" si="2"/>
         <v>demPop30to54N</v>
       </c>
       <c r="J116" s="10" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>833</v>
@@ -11729,7 +11731,7 @@
         <v>1019</v>
       </c>
       <c r="M116" s="10" t="str">
-        <f>IF(OR(O116&lt;&gt;"", Q116&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R116" s="4" t="s">
@@ -11761,11 +11763,11 @@
       </c>
       <c r="H117" s="10"/>
       <c r="I117" s="10" t="str">
-        <f>CONCATENATE(A117, B117,C117,D117,E117,F117,G117,H117)</f>
+        <f t="shared" si="2"/>
         <v>demPop55to74N</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>834</v>
@@ -11774,7 +11776,7 @@
         <v>1019</v>
       </c>
       <c r="M117" s="10" t="str">
-        <f>IF(OR(O117&lt;&gt;"", Q117&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R117" s="4" t="s">
@@ -11787,7 +11789,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="144" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B118" s="10" t="str" cm="1">
         <f t="array" ref="B118">_xlfn.IFS(S118 = Modules!$A$2,Modules!$B$2,S118 = Modules!$A$3,Modules!$B$3,S118 = Modules!$A$4,Modules!$B$4,S118 = Modules!$A$5,Modules!$B$5,S118 = Modules!$A$6,Modules!$B$6,S118 = Modules!$A$7,Modules!$B$7,S118 = Modules!$A$8,Modules!$B$8,S118 = Modules!$A$9,Modules!$B$9,S118 = Modules!$A$10,Modules!$B$10,S118 = Modules!$A$11,Modules!$B$11,S118 = Modules!$A$12,Modules!$B$12, S118 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -11799,11 +11801,11 @@
         <v>1040</v>
       </c>
       <c r="I118" s="10" t="str">
-        <f>CONCATENATE(A118, B118,C118,D118,E118,F118,G118,H118)</f>
+        <f t="shared" si="2"/>
         <v>demPopSurveyShare</v>
       </c>
       <c r="J118" s="10" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>665</v>
@@ -11812,7 +11814,7 @@
         <v>170</v>
       </c>
       <c r="M118" s="10" t="str">
-        <f>IF(OR(O118&lt;&gt;"", Q118&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N118" s="2" t="s">
@@ -11849,11 +11851,11 @@
         <v>1050</v>
       </c>
       <c r="I119" s="10" t="str">
-        <f>CONCATENATE(A119, B119,C119,D119,E119,F119,G119,H119)</f>
+        <f t="shared" si="2"/>
         <v>demPrptyFlagL1</v>
       </c>
       <c r="J119" s="10" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>859</v>
@@ -11862,7 +11864,7 @@
         <v>333</v>
       </c>
       <c r="M119" s="10" t="str">
-        <f>IF(OR(O119&lt;&gt;"", Q119&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S119" s="2" t="s">
@@ -11872,7 +11874,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="B120" s="10" t="str" cm="1">
         <f t="array" ref="B120">_xlfn.IFS(S120 = Modules!$A$2,Modules!$B$2,S120 = Modules!$A$3,Modules!$B$3,S120 = Modules!$A$4,Modules!$B$4,S120 = Modules!$A$5,Modules!$B$5,S120 = Modules!$A$6,Modules!$B$6,S120 = Modules!$A$7,Modules!$B$7,S120 = Modules!$A$8,Modules!$B$8,S120 = Modules!$A$9,Modules!$B$9,S120 = Modules!$A$10,Modules!$B$10,S120 = Modules!$A$11,Modules!$B$11,S120 = Modules!$A$12,Modules!$B$12, S120 = Modules!$A$13,Modules!$B$13)</f>
         <v>dem</v>
@@ -11881,7 +11883,7 @@
         <v>1130</v>
       </c>
       <c r="I120" s="10" t="str">
-        <f>CONCATENATE(A120, B120,C120,D120,E120,F120,G120,H120)</f>
+        <f t="shared" si="2"/>
         <v>demRgn</v>
       </c>
       <c r="J120" s="10" t="s">
@@ -11894,7 +11896,7 @@
         <v>170</v>
       </c>
       <c r="M120" s="10" t="str">
-        <f>IF(OR(O120&lt;&gt;"", Q120&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N120" s="2" t="s">
@@ -11928,7 +11930,7 @@
         <v>1130</v>
       </c>
       <c r="I121" s="10" t="str">
-        <f>CONCATENATE(A121, B121,C121,D121,E121,F121,G121,H121)</f>
+        <f t="shared" si="2"/>
         <v>demRgn</v>
       </c>
       <c r="J121" s="10" t="s">
@@ -11941,7 +11943,7 @@
         <v>449</v>
       </c>
       <c r="M121" s="10" t="str">
-        <f>IF(OR(O121&lt;&gt;"", Q121&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="N121" s="2" t="s">
@@ -11972,7 +11974,7 @@
         <v>968</v>
       </c>
       <c r="I122" s="10" t="str">
-        <f>CONCATENATE(A122, B122,C122,D122,E122,F122,G122,H122)</f>
+        <f t="shared" si="2"/>
         <v>demRtrdEnterFlag</v>
       </c>
       <c r="J122" s="10" t="s">
@@ -11985,7 +11987,7 @@
         <v>170</v>
       </c>
       <c r="M122" s="10" t="str">
-        <f>IF(OR(O122&lt;&gt;"", Q122&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N122" s="2" t="s">
@@ -12019,11 +12021,11 @@
         <v>1087</v>
       </c>
       <c r="I123" s="10" t="str">
-        <f>CONCATENATE(A123, B123,C123,D123,E123,F123,G123,H123)</f>
+        <f t="shared" si="2"/>
         <v>demSex</v>
       </c>
       <c r="J123" s="10" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>737</v>
@@ -12032,7 +12034,7 @@
         <v>1021</v>
       </c>
       <c r="M123" s="10" t="str">
-        <f>IF(OR(O123&lt;&gt;"", Q123&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R123" s="4" t="s">
@@ -12060,11 +12062,11 @@
         <v>1050</v>
       </c>
       <c r="I124" s="10" t="str">
-        <f>CONCATENATE(A124, B124,C124,D124,E124,F124,G124,H124)</f>
+        <f t="shared" si="2"/>
         <v>demStatusHhL1</v>
       </c>
       <c r="J124" s="10" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>861</v>
@@ -12073,7 +12075,7 @@
         <v>333</v>
       </c>
       <c r="M124" s="10" t="str">
-        <f>IF(OR(O124&lt;&gt;"", Q124&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="S124" s="2" t="s">
@@ -12102,11 +12104,11 @@
       <c r="G125" s="10"/>
       <c r="H125" s="10"/>
       <c r="I125" s="10" t="str">
-        <f>CONCATENATE(A125, B125,C125,D125,E125,F125,G125,H125)</f>
+        <f t="shared" si="2"/>
         <v>demUtilAdjCouple</v>
       </c>
       <c r="J125" s="10" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>851</v>
@@ -12115,7 +12117,7 @@
         <v>1023</v>
       </c>
       <c r="M125" s="10" t="str">
-        <f>IF(OR(O125&lt;&gt;"", Q125&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R125" s="4" t="s">
@@ -12128,7 +12130,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="126" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="10"/>
       <c r="B126" s="10" t="str" cm="1">
         <f t="array" ref="B126">_xlfn.IFS(S126 = Modules!$A$2,Modules!$B$2,S126 = Modules!$A$3,Modules!$B$3,S126 = Modules!$A$4,Modules!$B$4,S126 = Modules!$A$5,Modules!$B$5,S126 = Modules!$A$6,Modules!$B$6,S126 = Modules!$A$7,Modules!$B$7,S126 = Modules!$A$8,Modules!$B$8,S126 = Modules!$A$9,Modules!$B$9,S126 = Modules!$A$10,Modules!$B$10,S126 = Modules!$A$11,Modules!$B$11,S126 = Modules!$A$12,Modules!$B$12, S126 = Modules!$A$13,Modules!$B$13)</f>
@@ -12147,11 +12149,11 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="10" t="str">
-        <f>CONCATENATE(A126, B126,C126,D126,E126,F126,G126,H126)</f>
+        <f t="shared" si="2"/>
         <v>demUtilAdjSingleF</v>
       </c>
       <c r="J126" s="10" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>948</v>
@@ -12160,7 +12162,7 @@
         <v>1023</v>
       </c>
       <c r="M126" s="10" t="str">
-        <f>IF(OR(O126&lt;&gt;"", Q126&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R126" s="4" t="s">
@@ -12173,7 +12175,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="127" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="10"/>
       <c r="B127" s="10" t="str" cm="1">
         <f t="array" ref="B127">_xlfn.IFS(S127 = Modules!$A$2,Modules!$B$2,S127 = Modules!$A$3,Modules!$B$3,S127 = Modules!$A$4,Modules!$B$4,S127 = Modules!$A$5,Modules!$B$5,S127 = Modules!$A$6,Modules!$B$6,S127 = Modules!$A$7,Modules!$B$7,S127 = Modules!$A$8,Modules!$B$8,S127 = Modules!$A$9,Modules!$B$9,S127 = Modules!$A$10,Modules!$B$10,S127 = Modules!$A$11,Modules!$B$11,S127 = Modules!$A$12,Modules!$B$12, S127 = Modules!$A$13,Modules!$B$13)</f>
@@ -12192,11 +12194,11 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="10" t="str">
-        <f>CONCATENATE(A127, B127,C127,D127,E127,F127,G127,H127)</f>
+        <f t="shared" si="2"/>
         <v>demUtilAdjSingleM</v>
       </c>
       <c r="J127" s="10" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>949</v>
@@ -12205,7 +12207,7 @@
         <v>1023</v>
       </c>
       <c r="M127" s="10" t="str">
-        <f>IF(OR(O127&lt;&gt;"", Q127&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R127" s="4" t="s">
@@ -12227,18 +12229,18 @@
         <v>697</v>
       </c>
       <c r="I128" s="10" t="str">
-        <f>CONCATENATE(A128, B128,C128,D128,E128,F128,G128,H128)</f>
+        <f t="shared" si="2"/>
         <v>demYear</v>
       </c>
       <c r="J128" s="10" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>697</v>
       </c>
       <c r="L128" s="10"/>
       <c r="M128" s="10" t="str">
-        <f>IF(OR(O128&lt;&gt;"", Q128&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="R128" s="4" t="s">
@@ -12251,7 +12253,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B129" s="10" t="str" cm="1">
         <f t="array" ref="B129">_xlfn.IFS(S129 = Modules!$A$2,Modules!$B$2,S129 = Modules!$A$3,Modules!$B$3,S129 = Modules!$A$4,Modules!$B$4,S129 = Modules!$A$5,Modules!$B$5,S129 = Modules!$A$6,Modules!$B$6,S129 = Modules!$A$7,Modules!$B$7,S129 = Modules!$A$8,Modules!$B$8,S129 = Modules!$A$9,Modules!$B$9,S129 = Modules!$A$10,Modules!$B$10,S129 = Modules!$A$11,Modules!$B$11,S129 = Modules!$A$12,Modules!$B$12, S129 = Modules!$A$13,Modules!$B$13)</f>
         <v>edu</v>
@@ -12266,11 +12268,11 @@
         <v>968</v>
       </c>
       <c r="I129" s="10" t="str">
-        <f>CONCATENATE(A129, B129,C129,D129,E129,F129,G129,H129)</f>
+        <f t="shared" si="2"/>
         <v>eduExitSampleFlag</v>
       </c>
       <c r="J129" s="10" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>916</v>
@@ -12279,7 +12281,7 @@
         <v>333</v>
       </c>
       <c r="M129" s="10" t="str">
-        <f>IF(OR(O129&lt;&gt;"", Q129&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="N129" s="2" t="s">
@@ -12316,7 +12318,7 @@
         <v>1089</v>
       </c>
       <c r="I130" s="10" t="str">
-        <f>CONCATENATE(A130, B130,C130,D130,E130,F130,G130,H130)</f>
+        <f t="shared" ref="I130:I193" si="4">CONCATENATE(A130, B130,C130,D130,E130,F130,G130,H130)</f>
         <v>eduHighestC3</v>
       </c>
       <c r="J130" s="10" t="s">
@@ -12329,7 +12331,7 @@
         <v>333</v>
       </c>
       <c r="M130" s="10" t="str">
-        <f>IF(OR(O130&lt;&gt;"", Q130&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M130:M193" si="5">IF(OR(O130&lt;&gt;"", Q130&lt;&gt;""),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="N130" s="2" t="s">
@@ -12369,7 +12371,7 @@
         <v>1050</v>
       </c>
       <c r="I131" s="10" t="str">
-        <f>CONCATENATE(A131, B131,C131,D131,E131,F131,G131,H131)</f>
+        <f t="shared" si="4"/>
         <v>eduHighestC3L1</v>
       </c>
       <c r="J131" s="10" t="s">
@@ -12382,7 +12384,7 @@
         <v>333</v>
       </c>
       <c r="M131" s="10" t="str">
-        <f>IF(OR(O131&lt;&gt;"", Q131&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S131" s="5" t="s">
@@ -12407,7 +12409,7 @@
         <v>1089</v>
       </c>
       <c r="I132" s="10" t="str">
-        <f>CONCATENATE(A132, B132,C132,D132,E132,F132,G132,H132)</f>
+        <f t="shared" si="4"/>
         <v>eduHighestFatherC3</v>
       </c>
       <c r="J132" s="10" t="s">
@@ -12420,7 +12422,7 @@
         <v>333</v>
       </c>
       <c r="M132" s="10" t="str">
-        <f>IF(OR(O132&lt;&gt;"", Q132&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N132" s="2" t="s">
@@ -12454,7 +12456,7 @@
         <v>1089</v>
       </c>
       <c r="I133" s="10" t="str">
-        <f>CONCATENATE(A133, B133,C133,D133,E133,F133,G133,H133)</f>
+        <f t="shared" si="4"/>
         <v>eduHighestMotherC3</v>
       </c>
       <c r="J133" s="10" t="s">
@@ -12467,7 +12469,7 @@
         <v>333</v>
       </c>
       <c r="M133" s="10" t="str">
-        <f>IF(OR(O133&lt;&gt;"", Q133&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N133" s="2" t="s">
@@ -12501,7 +12503,7 @@
         <v>1089</v>
       </c>
       <c r="I134" s="10" t="str">
-        <f>CONCATENATE(A134, B134,C134,D134,E134,F134,G134,H134)</f>
+        <f t="shared" si="4"/>
         <v>eduHighestPartnerC3</v>
       </c>
       <c r="J134" s="10" t="s">
@@ -12514,7 +12516,7 @@
         <v>333</v>
       </c>
       <c r="M134" s="10" t="str">
-        <f>IF(OR(O134&lt;&gt;"", Q134&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N134" s="2" t="s">
@@ -12557,7 +12559,7 @@
         <v>1050</v>
       </c>
       <c r="I135" s="10" t="str">
-        <f>CONCATENATE(A135, B135,C135,D135,E135,F135,G135,H135)</f>
+        <f t="shared" si="4"/>
         <v>eduHighestPartnerC3L1</v>
       </c>
       <c r="J135" s="10" t="s">
@@ -12570,7 +12572,7 @@
         <v>333</v>
       </c>
       <c r="M135" s="10" t="str">
-        <f>IF(OR(O135&lt;&gt;"", Q135&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S135" s="5" t="s">
@@ -12592,11 +12594,11 @@
         <v>968</v>
       </c>
       <c r="I136" s="10" t="str">
-        <f>CONCATENATE(A136, B136,C136,D136,E136,F136,G136,H136)</f>
+        <f t="shared" si="4"/>
         <v>eduLeaveSchoolFlag</v>
       </c>
       <c r="J136" s="10" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1392</v>
@@ -12605,7 +12607,7 @@
         <v>333</v>
       </c>
       <c r="M136" s="10" t="str">
-        <f>IF(OR(O136&lt;&gt;"", Q136&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S136" s="2" t="s">
@@ -12630,11 +12632,11 @@
         <v>968</v>
       </c>
       <c r="I137" s="10" t="str">
-        <f>CONCATENATE(A137, B137,C137,D137,E137,F137,G137,H137)</f>
+        <f t="shared" si="4"/>
         <v>eduLeftEduFlag</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>865</v>
@@ -12643,7 +12645,7 @@
         <v>333</v>
       </c>
       <c r="M137" s="10" t="str">
-        <f>IF(OR(O137&lt;&gt;"", Q137&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S137" s="2" t="s">
@@ -12665,7 +12667,7 @@
         <v>968</v>
       </c>
       <c r="I138" s="10" t="str">
-        <f>CONCATENATE(A138, B138,C138,D138,E138,F138,G138,H138)</f>
+        <f t="shared" si="4"/>
         <v>eduReturnFlag</v>
       </c>
       <c r="J138" s="10" t="s">
@@ -12678,7 +12680,7 @@
         <v>333</v>
       </c>
       <c r="M138" s="10" t="str">
-        <f>IF(OR(O138&lt;&gt;"", Q138&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N138" s="2" t="s">
@@ -12718,11 +12720,11 @@
         <v>968</v>
       </c>
       <c r="I139" s="10" t="str">
-        <f>CONCATENATE(A139, B139,C139,D139,E139,F139,G139,H139)</f>
+        <f t="shared" si="4"/>
         <v>eduReturnSampleFlag</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>920</v>
@@ -12731,7 +12733,7 @@
         <v>170</v>
       </c>
       <c r="M139" s="10" t="str">
-        <f>IF(OR(O139&lt;&gt;"", Q139&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N139" s="2" t="s">
@@ -12756,7 +12758,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="140" spans="2:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:22" ht="160" x14ac:dyDescent="0.2">
       <c r="B140" s="10" t="str" cm="1">
         <f t="array" ref="B140">_xlfn.IFS(S140 = Modules!$A$2,Modules!$B$2,S140 = Modules!$A$3,Modules!$B$3,S140 = Modules!$A$4,Modules!$B$4,S140 = Modules!$A$5,Modules!$B$5,S140 = Modules!$A$6,Modules!$B$6,S140 = Modules!$A$7,Modules!$B$7,S140 = Modules!$A$8,Modules!$B$8,S140 = Modules!$A$9,Modules!$B$9,S140 = Modules!$A$10,Modules!$B$10,S140 = Modules!$A$11,Modules!$B$11,S140 = Modules!$A$12,Modules!$B$12, S140 = Modules!$A$13,Modules!$B$13)</f>
         <v>edu</v>
@@ -12768,11 +12770,11 @@
         <v>968</v>
       </c>
       <c r="I140" s="10" t="str">
-        <f>CONCATENATE(A140, B140,C140,D140,E140,F140,G140,H140)</f>
+        <f t="shared" si="4"/>
         <v>eduSampleFlag</v>
       </c>
       <c r="J140" s="10" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>921</v>
@@ -12781,7 +12783,7 @@
         <v>170</v>
       </c>
       <c r="M140" s="10" t="str">
-        <f>IF(OR(O140&lt;&gt;"", Q140&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N140" s="2" t="s">
@@ -12806,7 +12808,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="141" spans="2:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:22" ht="64" x14ac:dyDescent="0.2">
       <c r="B141" s="10" t="str" cm="1">
         <f t="array" ref="B141">_xlfn.IFS(S141 = Modules!$A$2,Modules!$B$2,S141 = Modules!$A$3,Modules!$B$3,S141 = Modules!$A$4,Modules!$B$4,S141 = Modules!$A$5,Modules!$B$5,S141 = Modules!$A$6,Modules!$B$6,S141 = Modules!$A$7,Modules!$B$7,S141 = Modules!$A$8,Modules!$B$8,S141 = Modules!$A$9,Modules!$B$9,S141 = Modules!$A$10,Modules!$B$10,S141 = Modules!$A$11,Modules!$B$11,S141 = Modules!$A$12,Modules!$B$12, S141 = Modules!$A$13,Modules!$B$13)</f>
         <v>edu</v>
@@ -12818,11 +12820,11 @@
         <v>968</v>
       </c>
       <c r="I141" s="10" t="str">
-        <f>CONCATENATE(A141, B141,C141,D141,E141,F141,G141,H141)</f>
+        <f t="shared" si="4"/>
         <v>eduSampleFlag</v>
       </c>
       <c r="J141" s="10" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>919</v>
@@ -12831,7 +12833,7 @@
         <v>170</v>
       </c>
       <c r="M141" s="10" t="str">
-        <f>IF(OR(O141&lt;&gt;"", Q141&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N141" s="2" t="s">
@@ -12868,7 +12870,7 @@
         <v>968</v>
       </c>
       <c r="I142" s="10" t="str">
-        <f>CONCATENATE(A142, B142,C142,D142,E142,F142,G142,H142)</f>
+        <f t="shared" si="4"/>
         <v>eduSpellFlag</v>
       </c>
       <c r="J142" s="10" t="s">
@@ -12881,7 +12883,7 @@
         <v>333</v>
       </c>
       <c r="M142" s="10" t="str">
-        <f>IF(OR(O142&lt;&gt;"", Q142&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N142" s="2" t="s">
@@ -12921,7 +12923,7 @@
         <v>968</v>
       </c>
       <c r="I143" s="10" t="str">
-        <f>CONCATENATE(A143, B143,C143,D143,E143,F143,G143,H143)</f>
+        <f t="shared" si="4"/>
         <v>healthDsblLongtermFlag</v>
       </c>
       <c r="J143" s="10" t="s">
@@ -12934,7 +12936,7 @@
         <v>333</v>
       </c>
       <c r="M143" s="10" t="str">
-        <f>IF(OR(O143&lt;&gt;"", Q143&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N143" s="2" t="s">
@@ -12959,7 +12961,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="144" spans="2:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B144" s="10" t="str" cm="1">
         <f t="array" ref="B144">_xlfn.IFS(S144 = Modules!$A$2,Modules!$B$2,S144 = Modules!$A$3,Modules!$B$3,S144 = Modules!$A$4,Modules!$B$4,S144 = Modules!$A$5,Modules!$B$5,S144 = Modules!$A$6,Modules!$B$6,S144 = Modules!$A$7,Modules!$B$7,S144 = Modules!$A$8,Modules!$B$8,S144 = Modules!$A$9,Modules!$B$9,S144 = Modules!$A$10,Modules!$B$10,S144 = Modules!$A$11,Modules!$B$11,S144 = Modules!$A$12,Modules!$B$12, S144 = Modules!$A$13,Modules!$B$13)</f>
         <v>health</v>
@@ -12974,7 +12976,7 @@
         <v>968</v>
       </c>
       <c r="I144" s="10" t="str">
-        <f>CONCATENATE(A144, B144,C144,D144,E144,F144,G144,H144)</f>
+        <f t="shared" si="4"/>
         <v>healthDsblLongtermFlag</v>
       </c>
       <c r="J144" s="10" t="s">
@@ -12987,7 +12989,7 @@
         <v>333</v>
       </c>
       <c r="M144" s="10" t="str">
-        <f>IF(OR(O144&lt;&gt;"", Q144&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N144" s="2" t="s">
@@ -13024,7 +13026,7 @@
         <v>1050</v>
       </c>
       <c r="I145" s="10" t="str">
-        <f>CONCATENATE(A145, B145,C145,D145,E145,F145,G145,H145)</f>
+        <f t="shared" si="4"/>
         <v>healthDsblLongtermFlagL1</v>
       </c>
       <c r="J145" s="10" t="s">
@@ -13037,7 +13039,7 @@
         <v>333</v>
       </c>
       <c r="M145" s="10" t="str">
-        <f>IF(OR(O145&lt;&gt;"", Q145&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S145" s="2" t="s">
@@ -13047,7 +13049,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="146" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B146" s="2" t="str" cm="1">
         <f t="array" ref="B146">_xlfn.IFS(S146 = Modules!$A$2,Modules!$B$2,S146 = Modules!$A$3,Modules!$B$3,S146 = Modules!$A$4,Modules!$B$4,S146 = Modules!$A$5,Modules!$B$5,S146 = Modules!$A$6,Modules!$B$6,S146 = Modules!$A$7,Modules!$B$7,S146 = Modules!$A$8,Modules!$B$8,S146 = Modules!$A$9,Modules!$B$9,S146 = Modules!$A$10,Modules!$B$10,S146 = Modules!$A$11,Modules!$B$11,S146 = Modules!$A$12,Modules!$B$12, S146 = Modules!$A$13,Modules!$B$13)</f>
         <v>health</v>
@@ -13065,7 +13067,7 @@
         <v>968</v>
       </c>
       <c r="I146" s="2" t="str">
-        <f>CONCATENATE(A146, B146,C146,D146,E146,F146,G146,H146)</f>
+        <f t="shared" si="4"/>
         <v>healthDsblPartnerLongtermFlag</v>
       </c>
       <c r="J146" s="2" t="s">
@@ -13075,7 +13077,7 @@
         <v>1322</v>
       </c>
       <c r="M146" s="10" t="str">
-        <f>IF(OR(O146&lt;&gt;"", Q146&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="P146" s="2" t="s">
@@ -13108,11 +13110,11 @@
       <c r="G147" s="10"/>
       <c r="H147" s="10"/>
       <c r="I147" s="10" t="str">
-        <f>CONCATENATE(A147, B147,C147,D147,E147,F147,G147,H147)</f>
+        <f t="shared" si="4"/>
         <v>healthLifeYearQualAdj</v>
       </c>
       <c r="J147" s="10" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>1402</v>
@@ -13121,7 +13123,7 @@
         <v>1021</v>
       </c>
       <c r="M147" s="10" t="str">
-        <f>IF(OR(O147&lt;&gt;"", Q147&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R147" s="4" t="s">
@@ -13151,11 +13153,11 @@
       <c r="G148" s="10"/>
       <c r="H148" s="10"/>
       <c r="I148" s="10" t="str">
-        <f>CONCATENATE(A148, B148,C148,D148,E148,F148,G148,H148)</f>
+        <f t="shared" si="4"/>
         <v>healthLifeYearWbAdj</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>1407</v>
@@ -13164,7 +13166,7 @@
         <v>1021</v>
       </c>
       <c r="M148" s="10" t="str">
-        <f>IF(OR(O148&lt;&gt;"", Q148&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R148" s="4" t="s">
@@ -13177,7 +13179,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A149" s="10"/>
       <c r="B149" s="10" t="str" cm="1">
         <f t="array" ref="B149">_xlfn.IFS(S149 = Modules!$A$2,Modules!$B$2,S149 = Modules!$A$3,Modules!$B$3,S149 = Modules!$A$4,Modules!$B$4,S149 = Modules!$A$5,Modules!$B$5,S149 = Modules!$A$6,Modules!$B$6,S149 = Modules!$A$7,Modules!$B$7,S149 = Modules!$A$8,Modules!$B$8,S149 = Modules!$A$9,Modules!$B$9,S149 = Modules!$A$10,Modules!$B$10,S149 = Modules!$A$11,Modules!$B$11,S149 = Modules!$A$12,Modules!$B$12, S149 = Modules!$A$13,Modules!$B$13)</f>
@@ -13194,7 +13196,7 @@
       <c r="G149" s="10"/>
       <c r="H149" s="10"/>
       <c r="I149" s="10" t="str">
-        <f>CONCATENATE(A149, B149,C149,D149,E149,F149,G149,H149)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcs</v>
       </c>
       <c r="J149" s="10" t="s">
@@ -13207,7 +13209,7 @@
         <v>333</v>
       </c>
       <c r="M149" s="10" t="str">
-        <f>IF(OR(O149&lt;&gt;"", Q149&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N149" s="10" t="s">
@@ -13226,7 +13228,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="96" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="10"/>
       <c r="B150" s="10" t="str" cm="1">
         <f t="array" ref="B150">_xlfn.IFS(S150 = Modules!$A$2,Modules!$B$2,S150 = Modules!$A$3,Modules!$B$3,S150 = Modules!$A$4,Modules!$B$4,S150 = Modules!$A$5,Modules!$B$5,S150 = Modules!$A$6,Modules!$B$6,S150 = Modules!$A$7,Modules!$B$7,S150 = Modules!$A$8,Modules!$B$8,S150 = Modules!$A$9,Modules!$B$9,S150 = Modules!$A$10,Modules!$B$10,S150 = Modules!$A$11,Modules!$B$11,S150 = Modules!$A$12,Modules!$B$12, S150 = Modules!$A$13,Modules!$B$13)</f>
@@ -13245,7 +13247,7 @@
       </c>
       <c r="H150" s="10"/>
       <c r="I150" s="10" t="str">
-        <f>CONCATENATE(A150, B150,C150,D150,E150,F150,G150,H150)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsAvg</v>
       </c>
       <c r="J150" s="10" t="s">
@@ -13258,7 +13260,7 @@
         <v>1021</v>
       </c>
       <c r="M150" s="10" t="str">
-        <f>IF(OR(O150&lt;&gt;"", Q150&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R150" s="4" t="s">
@@ -13290,7 +13292,7 @@
         <v>1050</v>
       </c>
       <c r="I151" s="10" t="str">
-        <f>CONCATENATE(A151, B151,C151,D151,E151,F151,G151,H151)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsL1</v>
       </c>
       <c r="J151" s="10" t="s">
@@ -13303,7 +13305,7 @@
         <v>333</v>
       </c>
       <c r="M151" s="10" t="str">
-        <f>IF(OR(O151&lt;&gt;"", Q151&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="N151" s="10"/>
@@ -13337,7 +13339,7 @@
       </c>
       <c r="H152" s="10"/>
       <c r="I152" s="10" t="str">
-        <f>CONCATENATE(A152, B152,C152,D152,E152,F152,G152,H152)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsP10</v>
       </c>
       <c r="J152" s="10" t="s">
@@ -13350,7 +13352,7 @@
         <v>1021</v>
       </c>
       <c r="M152" s="10" t="str">
-        <f>IF(OR(O152&lt;&gt;"", Q152&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R152" s="4" t="s">
@@ -13382,7 +13384,7 @@
       </c>
       <c r="H153" s="10"/>
       <c r="I153" s="10" t="str">
-        <f>CONCATENATE(A153, B153,C153,D153,E153,F153,G153,H153)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsP25</v>
       </c>
       <c r="J153" s="10" t="s">
@@ -13395,7 +13397,7 @@
         <v>1021</v>
       </c>
       <c r="M153" s="10" t="str">
-        <f>IF(OR(O153&lt;&gt;"", Q153&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R153" s="4" t="s">
@@ -13427,7 +13429,7 @@
       </c>
       <c r="H154" s="10"/>
       <c r="I154" s="10" t="str">
-        <f>CONCATENATE(A154, B154,C154,D154,E154,F154,G154,H154)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsP50</v>
       </c>
       <c r="J154" s="10" t="s">
@@ -13440,7 +13442,7 @@
         <v>1021</v>
       </c>
       <c r="M154" s="10" t="str">
-        <f>IF(OR(O154&lt;&gt;"", Q154&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R154" s="4" t="s">
@@ -13472,7 +13474,7 @@
       </c>
       <c r="H155" s="10"/>
       <c r="I155" s="10" t="str">
-        <f>CONCATENATE(A155, B155,C155,D155,E155,F155,G155,H155)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsP75</v>
       </c>
       <c r="J155" s="10" t="s">
@@ -13485,7 +13487,7 @@
         <v>1021</v>
       </c>
       <c r="M155" s="10" t="str">
-        <f>IF(OR(O155&lt;&gt;"", Q155&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R155" s="4" t="s">
@@ -13517,20 +13519,20 @@
       </c>
       <c r="H156" s="10"/>
       <c r="I156" s="10" t="str">
-        <f>CONCATENATE(A156, B156,C156,D156,E156,F156,G156,H156)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalMcsP90</v>
       </c>
       <c r="J156" s="10" t="s">
         <v>1550</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="L156" s="10" t="s">
         <v>1021</v>
       </c>
       <c r="M156" s="10" t="str">
-        <f>IF(OR(O156&lt;&gt;"", Q156&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R156" s="4" t="s">
@@ -13562,7 +13564,7 @@
       <c r="G157" s="10"/>
       <c r="H157" s="10"/>
       <c r="I157" s="10" t="str">
-        <f>CONCATENATE(A157, B157,C157,D157,E157,F157,G157,H157)</f>
+        <f t="shared" si="4"/>
         <v>healthMentalPartnerMcs</v>
       </c>
       <c r="J157" s="10" t="s">
@@ -13575,7 +13577,7 @@
         <v>333</v>
       </c>
       <c r="M157" s="10" t="str">
-        <f>IF(OR(O157&lt;&gt;"", Q157&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="O157" s="2" t="s">
@@ -13588,7 +13590,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="112" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A158" s="10"/>
       <c r="B158" s="10" t="str" cm="1">
         <f t="array" ref="B158">_xlfn.IFS(S158 = Modules!$A$2,Modules!$B$2,S158 = Modules!$A$3,Modules!$B$3,S158 = Modules!$A$4,Modules!$B$4,S158 = Modules!$A$5,Modules!$B$5,S158 = Modules!$A$6,Modules!$B$6,S158 = Modules!$A$7,Modules!$B$7,S158 = Modules!$A$8,Modules!$B$8,S158 = Modules!$A$9,Modules!$B$9,S158 = Modules!$A$10,Modules!$B$10,S158 = Modules!$A$11,Modules!$B$11,S158 = Modules!$A$12,Modules!$B$12, S158 = Modules!$A$13,Modules!$B$13)</f>
@@ -13605,11 +13607,11 @@
       <c r="G158" s="10"/>
       <c r="H158" s="10"/>
       <c r="I158" s="10" t="str">
-        <f>CONCATENATE(A158, B158,C158,D158,E158,F158,G158,H158)</f>
+        <f t="shared" si="4"/>
         <v>healthNObsSubGroup</v>
       </c>
       <c r="J158" s="10" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>1397</v>
@@ -13618,7 +13620,7 @@
         <v>1021</v>
       </c>
       <c r="M158" s="10" t="str">
-        <f>IF(OR(O158&lt;&gt;"", Q158&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R158" s="4" t="s">
@@ -13643,7 +13645,7 @@
         <v>1088</v>
       </c>
       <c r="I159" s="10" t="str">
-        <f>CONCATENATE(A159, B159,C159,D159,E159,F159,G159,H159)</f>
+        <f t="shared" si="4"/>
         <v>healthPartnerSelfRated</v>
       </c>
       <c r="J159" s="10" t="s">
@@ -13656,7 +13658,7 @@
         <v>333</v>
       </c>
       <c r="M159" s="10" t="str">
-        <f>IF(OR(O159&lt;&gt;"", Q159&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N159" s="2" t="s">
@@ -13696,7 +13698,7 @@
         <v>1050</v>
       </c>
       <c r="I160" s="10" t="str">
-        <f>CONCATENATE(A160, B160,C160,D160,E160,F160,G160,H160)</f>
+        <f t="shared" si="4"/>
         <v>healthPartnerSelfRatedL1</v>
       </c>
       <c r="J160" s="10" t="s">
@@ -13709,7 +13711,7 @@
         <v>333</v>
       </c>
       <c r="M160" s="10" t="str">
-        <f>IF(OR(O160&lt;&gt;"", Q160&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S160" s="2" t="s">
@@ -13719,7 +13721,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="161" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="10"/>
       <c r="B161" s="10" t="str" cm="1">
         <f t="array" ref="B161">_xlfn.IFS(S161 = Modules!$A$2,Modules!$B$2,S161 = Modules!$A$3,Modules!$B$3,S161 = Modules!$A$4,Modules!$B$4,S161 = Modules!$A$5,Modules!$B$5,S161 = Modules!$A$6,Modules!$B$6,S161 = Modules!$A$7,Modules!$B$7,S161 = Modules!$A$8,Modules!$B$8,S161 = Modules!$A$9,Modules!$B$9,S161 = Modules!$A$10,Modules!$B$10,S161 = Modules!$A$11,Modules!$B$11,S161 = Modules!$A$12,Modules!$B$12, S161 = Modules!$A$13,Modules!$B$13)</f>
@@ -13738,7 +13740,7 @@
       <c r="G161" s="10"/>
       <c r="H161" s="10"/>
       <c r="I161" s="10" t="str">
-        <f>CONCATENATE(A161, B161,C161,D161,E161,F161,G161,H161)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPartnerPcs</v>
       </c>
       <c r="J161" s="10" t="s">
@@ -13751,7 +13753,7 @@
         <v>333</v>
       </c>
       <c r="M161" s="10" t="str">
-        <f>IF(OR(O161&lt;&gt;"", Q161&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="O161" s="2" t="s">
@@ -13781,7 +13783,7 @@
       <c r="G162" s="10"/>
       <c r="H162" s="10"/>
       <c r="I162" s="10" t="str">
-        <f>CONCATENATE(A162, B162,C162,D162,E162,F162,G162,H162)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcs</v>
       </c>
       <c r="J162" s="10" t="s">
@@ -13794,7 +13796,7 @@
         <v>333</v>
       </c>
       <c r="M162" s="10" t="str">
-        <f>IF(OR(O162&lt;&gt;"", Q162&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N162" s="2" t="s">
@@ -13831,7 +13833,7 @@
       </c>
       <c r="H163" s="10"/>
       <c r="I163" s="10" t="str">
-        <f>CONCATENATE(A163, B163,C163,D163,E163,F163,G163,H163)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsAvg</v>
       </c>
       <c r="J163" s="10" t="s">
@@ -13844,7 +13846,7 @@
         <v>1021</v>
       </c>
       <c r="M163" s="10" t="str">
-        <f>IF(OR(O163&lt;&gt;"", Q163&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R163" s="4" t="s">
@@ -13876,7 +13878,7 @@
         <v>1050</v>
       </c>
       <c r="I164" s="10" t="str">
-        <f>CONCATENATE(A164, B164,C164,D164,E164,F164,G164,H164)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsL1</v>
       </c>
       <c r="J164" s="10" t="s">
@@ -13889,7 +13891,7 @@
         <v>333</v>
       </c>
       <c r="M164" s="10" t="str">
-        <f>IF(OR(O164&lt;&gt;"", Q164&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S164" s="2" t="s">
@@ -13918,7 +13920,7 @@
       </c>
       <c r="H165" s="10"/>
       <c r="I165" s="10" t="str">
-        <f>CONCATENATE(A165, B165,C165,D165,E165,F165,G165,H165)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsP10</v>
       </c>
       <c r="J165" s="10" t="s">
@@ -13931,7 +13933,7 @@
         <v>1021</v>
       </c>
       <c r="M165" s="10" t="str">
-        <f>IF(OR(O165&lt;&gt;"", Q165&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R165" s="4" t="s">
@@ -13963,7 +13965,7 @@
       </c>
       <c r="H166" s="10"/>
       <c r="I166" s="10" t="str">
-        <f>CONCATENATE(A166, B166,C166,D166,E166,F166,G166,H166)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsP25</v>
       </c>
       <c r="J166" s="10" t="s">
@@ -13976,7 +13978,7 @@
         <v>1021</v>
       </c>
       <c r="M166" s="10" t="str">
-        <f>IF(OR(O166&lt;&gt;"", Q166&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R166" s="4" t="s">
@@ -14008,7 +14010,7 @@
       </c>
       <c r="H167" s="10"/>
       <c r="I167" s="10" t="str">
-        <f>CONCATENATE(A167, B167,C167,D167,E167,F167,G167,H167)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsP50</v>
       </c>
       <c r="J167" s="10" t="s">
@@ -14021,7 +14023,7 @@
         <v>1021</v>
       </c>
       <c r="M167" s="10" t="str">
-        <f>IF(OR(O167&lt;&gt;"", Q167&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R167" s="4" t="s">
@@ -14053,7 +14055,7 @@
       </c>
       <c r="H168" s="10"/>
       <c r="I168" s="10" t="str">
-        <f>CONCATENATE(A168, B168,C168,D168,E168,F168,G168,H168)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsP75</v>
       </c>
       <c r="J168" s="10" t="s">
@@ -14066,7 +14068,7 @@
         <v>1021</v>
       </c>
       <c r="M168" s="10" t="str">
-        <f>IF(OR(O168&lt;&gt;"", Q168&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R168" s="4" t="s">
@@ -14098,20 +14100,20 @@
       </c>
       <c r="H169" s="10"/>
       <c r="I169" s="10" t="str">
-        <f>CONCATENATE(A169, B169,C169,D169,E169,F169,G169,H169)</f>
+        <f t="shared" si="4"/>
         <v>healthPhysicalPcsP90</v>
       </c>
       <c r="J169" s="10" t="s">
         <v>1559</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="L169" s="10" t="s">
         <v>1021</v>
       </c>
       <c r="M169" s="10" t="str">
-        <f>IF(OR(O169&lt;&gt;"", Q169&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R169" s="4" t="s">
@@ -14136,7 +14138,7 @@
         <v>968</v>
       </c>
       <c r="I170" s="10" t="str">
-        <f>CONCATENATE(A170, B170,C170,D170,E170,F170,G170,H170)</f>
+        <f t="shared" si="4"/>
         <v>healthPsyDstrssFlag</v>
       </c>
       <c r="J170" s="10" t="s">
@@ -14149,7 +14151,7 @@
         <v>333</v>
       </c>
       <c r="M170" s="10" t="str">
-        <f>IF(OR(O170&lt;&gt;"", Q170&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N170" s="2" t="s">
@@ -14183,11 +14185,11 @@
         <v>1198</v>
       </c>
       <c r="I171" s="10" t="str">
-        <f>CONCATENATE(A171, B171,C171,D171,E171,F171,G171,H171)</f>
+        <f t="shared" si="4"/>
         <v>demWbScore0to12</v>
       </c>
       <c r="J171" s="10" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="K171" s="2" t="s">
         <v>599</v>
@@ -14196,7 +14198,7 @@
         <v>170</v>
       </c>
       <c r="M171" s="10" t="str">
-        <f>IF(OR(O171&lt;&gt;"", Q171&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N171" s="2" t="s">
@@ -14209,7 +14211,7 @@
         <v>962</v>
       </c>
       <c r="U171" s="2" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="V171" s="2" t="s">
         <v>123</v>
@@ -14234,11 +14236,11 @@
       </c>
       <c r="H172" s="10"/>
       <c r="I172" s="10" t="str">
-        <f>CONCATENATE(A172, B172,C172,D172,E172,F172,G172,H172)</f>
+        <f t="shared" si="4"/>
         <v>healthScore18to29Avg</v>
       </c>
       <c r="J172" s="10" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K172" s="6" t="s">
         <v>817</v>
@@ -14247,7 +14249,7 @@
         <v>1019</v>
       </c>
       <c r="M172" s="10" t="str">
-        <f>IF(OR(O172&lt;&gt;"", Q172&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R172" s="4" t="s">
@@ -14279,11 +14281,11 @@
       </c>
       <c r="H173" s="10"/>
       <c r="I173" s="10" t="str">
-        <f>CONCATENATE(A173, B173,C173,D173,E173,F173,G173,H173)</f>
+        <f t="shared" si="4"/>
         <v>healthScore30to54Avg</v>
       </c>
       <c r="J173" s="10" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="K173" s="6" t="s">
         <v>818</v>
@@ -14292,7 +14294,7 @@
         <v>1019</v>
       </c>
       <c r="M173" s="10" t="str">
-        <f>IF(OR(O173&lt;&gt;"", Q173&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R173" s="4" t="s">
@@ -14324,11 +14326,11 @@
       </c>
       <c r="H174" s="10"/>
       <c r="I174" s="10" t="str">
-        <f>CONCATENATE(A174, B174,C174,D174,E174,F174,G174,H174)</f>
+        <f t="shared" si="4"/>
         <v>healthScore55to74Avg</v>
       </c>
       <c r="J174" s="10" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="K174" s="6" t="s">
         <v>819</v>
@@ -14337,7 +14339,7 @@
         <v>1019</v>
       </c>
       <c r="M174" s="10" t="str">
-        <f>IF(OR(O174&lt;&gt;"", Q174&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R174" s="4" t="s">
@@ -14359,7 +14361,7 @@
         <v>1088</v>
       </c>
       <c r="I175" s="10" t="str">
-        <f>CONCATENATE(A175, B175,C175,D175,E175,F175,G175,H175)</f>
+        <f t="shared" si="4"/>
         <v>healthSelfRated</v>
       </c>
       <c r="J175" s="10" t="s">
@@ -14372,7 +14374,7 @@
         <v>333</v>
       </c>
       <c r="M175" s="10" t="str">
-        <f>IF(OR(O175&lt;&gt;"", Q175&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N175" s="2" t="s">
@@ -14409,7 +14411,7 @@
         <v>1050</v>
       </c>
       <c r="I176" s="10" t="str">
-        <f>CONCATENATE(A176, B176,C176,D176,E176,F176,G176,H176)</f>
+        <f t="shared" si="4"/>
         <v>healthSelfRatedL1</v>
       </c>
       <c r="J176" s="10" t="s">
@@ -14422,7 +14424,7 @@
         <v>333</v>
       </c>
       <c r="M176" s="10" t="str">
-        <f>IF(OR(O176&lt;&gt;"", Q176&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S176" s="2" t="s">
@@ -14447,7 +14449,7 @@
         <v>1111</v>
       </c>
       <c r="I177" s="10" t="str">
-        <f>CONCATENATE(A177, B177,C177,D177,E177,F177,G177,H177)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36</v>
       </c>
       <c r="J177" s="10" t="s">
@@ -14460,7 +14462,7 @@
         <v>333</v>
       </c>
       <c r="M177" s="10" t="str">
-        <f>IF(OR(O177&lt;&gt;"", Q177&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>Yes</v>
       </c>
       <c r="N177" s="2" t="s">
@@ -14500,7 +14502,7 @@
       </c>
       <c r="H178" s="10"/>
       <c r="I178" s="10" t="str">
-        <f>CONCATENATE(A178, B178,C178,D178,E178,F178,G178,H178)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36Avg</v>
       </c>
       <c r="J178" s="10" t="s">
@@ -14513,7 +14515,7 @@
         <v>1021</v>
       </c>
       <c r="M178" s="10" t="str">
-        <f>IF(OR(O178&lt;&gt;"", Q178&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R178" s="4" t="s">
@@ -14544,7 +14546,7 @@
         <v>1050</v>
       </c>
       <c r="I179" s="10" t="str">
-        <f>CONCATENATE(A179, B179,C179,D179,E179,F179,G179,H179)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36L1</v>
       </c>
       <c r="J179" s="10" t="s">
@@ -14557,7 +14559,7 @@
         <v>333</v>
       </c>
       <c r="M179" s="10" t="str">
-        <f>IF(OR(O179&lt;&gt;"", Q179&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S179" s="2" t="s">
@@ -14587,7 +14589,7 @@
       </c>
       <c r="H180" s="10"/>
       <c r="I180" s="10" t="str">
-        <f>CONCATENATE(A180, B180,C180,D180,E180,F180,G180,H180)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36P10</v>
       </c>
       <c r="J180" s="10" t="s">
@@ -14600,7 +14602,7 @@
         <v>1021</v>
       </c>
       <c r="M180" s="10" t="str">
-        <f>IF(OR(O180&lt;&gt;"", Q180&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R180" s="4" t="s">
@@ -14633,7 +14635,7 @@
       </c>
       <c r="H181" s="10"/>
       <c r="I181" s="10" t="str">
-        <f>CONCATENATE(A181, B181,C181,D181,E181,F181,G181,H181)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36P25</v>
       </c>
       <c r="J181" s="10" t="s">
@@ -14646,7 +14648,7 @@
         <v>1021</v>
       </c>
       <c r="M181" s="10" t="str">
-        <f>IF(OR(O181&lt;&gt;"", Q181&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R181" s="4" t="s">
@@ -14679,7 +14681,7 @@
       </c>
       <c r="H182" s="10"/>
       <c r="I182" s="10" t="str">
-        <f>CONCATENATE(A182, B182,C182,D182,E182,F182,G182,H182)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36P50</v>
       </c>
       <c r="J182" s="10" t="s">
@@ -14692,7 +14694,7 @@
         <v>1021</v>
       </c>
       <c r="M182" s="10" t="str">
-        <f>IF(OR(O182&lt;&gt;"", Q182&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R182" s="4" t="s">
@@ -14725,7 +14727,7 @@
       </c>
       <c r="H183" s="10"/>
       <c r="I183" s="10" t="str">
-        <f>CONCATENATE(A183, B183,C183,D183,E183,F183,G183,H183)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36P75</v>
       </c>
       <c r="J183" s="10" t="s">
@@ -14738,7 +14740,7 @@
         <v>1021</v>
       </c>
       <c r="M183" s="10" t="str">
-        <f>IF(OR(O183&lt;&gt;"", Q183&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R183" s="4" t="s">
@@ -14771,20 +14773,20 @@
       </c>
       <c r="H184" s="10"/>
       <c r="I184" s="10" t="str">
-        <f>CONCATENATE(A184, B184,C184,D184,E184,F184,G184,H184)</f>
+        <f t="shared" si="4"/>
         <v>healthWbScore0to36P90</v>
       </c>
       <c r="J184" s="10" t="s">
         <v>1578</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="L184" s="10" t="s">
         <v>1021</v>
       </c>
       <c r="M184" s="10" t="str">
-        <f>IF(OR(O184&lt;&gt;"", Q184&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="R184" s="4" t="s">
@@ -14820,7 +14822,7 @@
         <v>1050</v>
       </c>
       <c r="I185" s="10" t="str">
-        <f>CONCATENATE(A185, B185,C185,D185,E185,F185,G185,H185)</f>
+        <f t="shared" si="4"/>
         <v>i_demCompHhC4L1</v>
       </c>
       <c r="J185" s="10" t="s">
@@ -14833,7 +14835,7 @@
         <v>333</v>
       </c>
       <c r="M185" s="10" t="str">
-        <f>IF(OR(O185&lt;&gt;"", Q185&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S185" s="2" t="s">
@@ -14846,7 +14848,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>1221</v>
       </c>
@@ -14858,11 +14860,11 @@
         <v>1051</v>
       </c>
       <c r="I186" s="10" t="str">
-        <f>CONCATENATE(A186, B186,C186,D186,E186,F186,G186,H186)</f>
+        <f t="shared" si="4"/>
         <v>i_demNchild</v>
       </c>
       <c r="J186" s="10" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="K186" s="2" t="s">
         <v>878</v>
@@ -14871,7 +14873,7 @@
         <v>333</v>
       </c>
       <c r="M186" s="10" t="str">
-        <f>IF(OR(O186&lt;&gt;"", Q186&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S186" s="2" t="s">
@@ -14899,11 +14901,11 @@
         <v>1222</v>
       </c>
       <c r="I187" s="10" t="str">
-        <f>CONCATENATE(A187, B187,C187,D187,E187,F187,G187,H187)</f>
+        <f t="shared" si="4"/>
         <v>i_demNchild0to17</v>
       </c>
       <c r="J187" s="10" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="K187" s="2" t="s">
         <v>881</v>
@@ -14912,7 +14914,7 @@
         <v>333</v>
       </c>
       <c r="M187" s="10" t="str">
-        <f>IF(OR(O187&lt;&gt;"", Q187&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S187" s="2" t="s">
@@ -14940,11 +14942,11 @@
         <v>1128</v>
       </c>
       <c r="I188" s="10" t="str">
-        <f>CONCATENATE(A188, B188,C188,D188,E188,F188,G188,H188)</f>
+        <f t="shared" si="4"/>
         <v>i_demNChild0to2</v>
       </c>
       <c r="J188" s="10" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="K188" s="2" t="s">
         <v>880</v>
@@ -14953,7 +14955,7 @@
         <v>333</v>
       </c>
       <c r="M188" s="10" t="str">
-        <f>IF(OR(O188&lt;&gt;"", Q188&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S188" s="2" t="s">
@@ -14984,11 +14986,11 @@
         <v>1050</v>
       </c>
       <c r="I189" s="10" t="str">
-        <f>CONCATENATE(A189, B189,C189,D189,E189,F189,G189,H189)</f>
+        <f t="shared" si="4"/>
         <v>i_demNChild0to2L1</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="K189" s="2" t="s">
         <v>439</v>
@@ -14997,7 +14999,7 @@
         <v>449</v>
       </c>
       <c r="M189" s="10" t="str">
-        <f>IF(OR(O189&lt;&gt;"", Q189&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S189" s="2" t="s">
@@ -15025,11 +15027,11 @@
         <v>1050</v>
       </c>
       <c r="I190" s="10" t="str">
-        <f>CONCATENATE(A190, B190,C190,D190,E190,F190,G190,H190)</f>
+        <f t="shared" si="4"/>
         <v>i_demNchild0to2L1</v>
       </c>
       <c r="J190" s="10" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="K190" s="2" t="s">
         <v>882</v>
@@ -15038,7 +15040,7 @@
         <v>333</v>
       </c>
       <c r="M190" s="10" t="str">
-        <f>IF(OR(O190&lt;&gt;"", Q190&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S190" s="2" t="s">
@@ -15066,11 +15068,11 @@
         <v>1050</v>
       </c>
       <c r="I191" s="10" t="str">
-        <f>CONCATENATE(A191, B191,C191,D191,E191,F191,G191,H191)</f>
+        <f t="shared" si="4"/>
         <v>i_demNchildL1</v>
       </c>
       <c r="J191" s="10" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="K191" s="2" t="s">
         <v>879</v>
@@ -15079,7 +15081,7 @@
         <v>333</v>
       </c>
       <c r="M191" s="10" t="str">
-        <f>IF(OR(O191&lt;&gt;"", Q191&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S191" s="2" t="s">
@@ -15104,11 +15106,11 @@
         <v>1191</v>
       </c>
       <c r="I192" s="10" t="str">
-        <f>CONCATENATE(A192, B192,C192,D192,E192,F192,G192,H192)</f>
+        <f t="shared" si="4"/>
         <v>i_demOccupancy</v>
       </c>
       <c r="J192" s="10" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="K192" s="2" t="s">
         <v>1377</v>
@@ -15117,7 +15119,7 @@
         <v>449</v>
       </c>
       <c r="M192" s="10" t="str">
-        <f>IF(OR(O192&lt;&gt;"", Q192&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S192" s="2" t="s">
@@ -15142,7 +15144,7 @@
         <v>530</v>
       </c>
       <c r="I193" s="10" t="str">
-        <f>CONCATENATE(A193, B193,C193,D193,E193,F193,G193,H193)</f>
+        <f t="shared" si="4"/>
         <v>i_demPartnerStatus</v>
       </c>
       <c r="J193" s="10" t="s">
@@ -15155,7 +15157,7 @@
         <v>333</v>
       </c>
       <c r="M193" s="10" t="str">
-        <f>IF(OR(O193&lt;&gt;"", Q193&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="5"/>
         <v>No</v>
       </c>
       <c r="S193" s="2" t="s">
@@ -15180,11 +15182,11 @@
         <v>1130</v>
       </c>
       <c r="I194" s="10" t="str">
-        <f>CONCATENATE(A194, B194,C194,D194,E194,F194,G194,H194)</f>
+        <f t="shared" ref="I194:I257" si="6">CONCATENATE(A194, B194,C194,D194,E194,F194,G194,H194)</f>
         <v>i_demRgn</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="K194" s="2" t="s">
         <v>875</v>
@@ -15193,7 +15195,7 @@
         <v>333</v>
       </c>
       <c r="M194" s="10" t="str">
-        <f>IF(OR(O194&lt;&gt;"", Q194&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M194:M257" si="7">IF(OR(O194&lt;&gt;"", Q194&lt;&gt;""),"Yes","No")</f>
         <v>No</v>
       </c>
       <c r="S194" s="2" t="s">
@@ -15218,11 +15220,11 @@
         <v>697</v>
       </c>
       <c r="I195" s="10" t="str">
-        <f>CONCATENATE(A195, B195,C195,D195,E195,F195,G195,H195)</f>
+        <f t="shared" si="6"/>
         <v>i_demYear</v>
       </c>
       <c r="J195" s="10" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>874</v>
@@ -15231,7 +15233,7 @@
         <v>333</v>
       </c>
       <c r="M195" s="10" t="str">
-        <f>IF(OR(O195&lt;&gt;"", Q195&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S195" s="2" t="s">
@@ -15259,7 +15261,7 @@
         <v>1089</v>
       </c>
       <c r="I196" s="10" t="str">
-        <f>CONCATENATE(A196, B196,C196,D196,E196,F196,G196,H196)</f>
+        <f t="shared" si="6"/>
         <v>i_eduHighestC3</v>
       </c>
       <c r="J196" s="10" t="s">
@@ -15272,7 +15274,7 @@
         <v>449</v>
       </c>
       <c r="M196" s="10" t="str">
-        <f>IF(OR(O196&lt;&gt;"", Q196&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S196" s="5" t="s">
@@ -15303,11 +15305,11 @@
         <v>1002</v>
       </c>
       <c r="I197" s="10" t="str">
-        <f>CONCATENATE(A197, B197,C197,D197,E197,F197,G197,H197)</f>
+        <f t="shared" si="6"/>
         <v>i_labHrsWork1Week</v>
       </c>
       <c r="J197" s="10" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="K197" s="2" t="s">
         <v>1387</v>
@@ -15316,7 +15318,7 @@
         <v>449</v>
       </c>
       <c r="M197" s="10" t="str">
-        <f>IF(OR(O197&lt;&gt;"", Q197&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S197" s="2" t="s">
@@ -15347,11 +15349,11 @@
         <v>1002</v>
       </c>
       <c r="I198" s="10" t="str">
-        <f>CONCATENATE(A198, B198,C198,D198,E198,F198,G198,H198)</f>
+        <f t="shared" si="6"/>
         <v>i_labHrsWork2Week</v>
       </c>
       <c r="J198" s="10" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="K198" s="2" t="s">
         <v>1388</v>
@@ -15360,7 +15362,7 @@
         <v>449</v>
       </c>
       <c r="M198" s="10" t="str">
-        <f>IF(OR(O198&lt;&gt;"", Q198&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S198" s="2" t="s">
@@ -15388,11 +15390,11 @@
         <v>1105</v>
       </c>
       <c r="I199" s="10" t="str">
-        <f>CONCATENATE(A199, B199,C199,D199,E199,F199,G199,H199)</f>
+        <f t="shared" si="6"/>
         <v>i_yHhQuintilesC5</v>
       </c>
       <c r="J199" s="10" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="K199" s="2" t="s">
         <v>877</v>
@@ -15401,7 +15403,7 @@
         <v>333</v>
       </c>
       <c r="M199" s="10" t="str">
-        <f>IF(OR(O199&lt;&gt;"", Q199&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S199" s="2" t="s">
@@ -15435,11 +15437,11 @@
         <v>1414</v>
       </c>
       <c r="I200" s="10" t="str">
-        <f>CONCATENATE(A200, B200,C200,D200,E200,F200,G200,H200)</f>
+        <f t="shared" si="6"/>
         <v>i_yNonBenHhGrossAsinh</v>
       </c>
       <c r="J200" s="10" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="K200" s="2" t="s">
         <v>1415</v>
@@ -15448,7 +15450,7 @@
         <v>449</v>
       </c>
       <c r="M200" s="10" t="str">
-        <f>IF(OR(O200&lt;&gt;"", Q200&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S200" s="2" t="s">
@@ -15467,18 +15469,18 @@
         <v>1162</v>
       </c>
       <c r="I201" s="10" t="str">
-        <f>CONCATENATE(A201, B201,C201,D201,E201,F201,G201,H201)</f>
+        <f t="shared" si="6"/>
         <v>idBu</v>
       </c>
       <c r="J201" s="10" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>479</v>
       </c>
       <c r="L201" s="10"/>
       <c r="M201" s="10" t="str">
-        <f>IF(OR(O201&lt;&gt;"", Q201&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R201" s="4" t="s">
@@ -15500,11 +15502,11 @@
         <v>1162</v>
       </c>
       <c r="I202" s="10" t="str">
-        <f>CONCATENATE(A202, B202,C202,D202,E202,F202,G202,H202)</f>
+        <f t="shared" si="6"/>
         <v>idBu</v>
       </c>
       <c r="J202" s="10" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K202" s="2" t="s">
         <v>711</v>
@@ -15513,7 +15515,7 @@
         <v>333</v>
       </c>
       <c r="M202" s="10" t="str">
-        <f>IF(OR(O202&lt;&gt;"", Q202&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="O202" s="4" t="s">
@@ -15542,11 +15544,11 @@
         <v>1162</v>
       </c>
       <c r="I203" s="10" t="str">
-        <f>CONCATENATE(A203, B203,C203,D203,E203,F203,G203,H203)</f>
+        <f t="shared" si="6"/>
         <v>idBu</v>
       </c>
       <c r="J203" s="10" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K203" s="2" t="s">
         <v>711</v>
@@ -15555,7 +15557,7 @@
         <v>333</v>
       </c>
       <c r="M203" s="10" t="str">
-        <f>IF(OR(O203&lt;&gt;"", Q203&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S203" s="2" t="s">
@@ -15582,11 +15584,11 @@
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
       <c r="I204" s="10" t="str">
-        <f>CONCATENATE(A204, B204,C204,D204,E204,F204,G204,H204)</f>
+        <f t="shared" si="6"/>
         <v>idBuOriginal</v>
       </c>
       <c r="J204" s="10" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K204" s="2" t="s">
         <v>711</v>
@@ -15595,7 +15597,7 @@
         <v>449</v>
       </c>
       <c r="M204" s="10" t="str">
-        <f>IF(OR(O204&lt;&gt;"", Q204&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S204" s="2" t="s">
@@ -15620,11 +15622,11 @@
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
       <c r="I205" s="10" t="str">
-        <f>CONCATENATE(A205, B205,C205,D205,E205,F205,G205,H205)</f>
+        <f t="shared" si="6"/>
         <v>idEmpStatistics1</v>
       </c>
       <c r="J205" s="10" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K205" s="2" t="s">
         <v>1413</v>
@@ -15633,7 +15635,7 @@
         <v>1022</v>
       </c>
       <c r="M205" s="10" t="str">
-        <f>IF(OR(O205&lt;&gt;"", Q205&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R205" s="4" t="s">
@@ -15655,7 +15657,7 @@
         <v>456</v>
       </c>
       <c r="I206" s="10" t="str">
-        <f>CONCATENATE(A206, B206,C206,D206,E206,F206,G206,H206)</f>
+        <f t="shared" si="6"/>
         <v>idFather</v>
       </c>
       <c r="J206" s="10" t="s">
@@ -15668,7 +15670,7 @@
         <v>333</v>
       </c>
       <c r="M206" s="10" t="str">
-        <f>IF(OR(O206&lt;&gt;"", Q206&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N206" s="2" t="s">
@@ -15708,11 +15710,11 @@
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="10" t="str">
-        <f>CONCATENATE(A207, B207,C207,D207,E207,F207,G207,H207)</f>
+        <f t="shared" si="6"/>
         <v>idHealthStatistics1</v>
       </c>
       <c r="J207" s="10" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K207" s="2" t="s">
         <v>1413</v>
@@ -15721,7 +15723,7 @@
         <v>1021</v>
       </c>
       <c r="M207" s="10" t="str">
-        <f>IF(OR(O207&lt;&gt;"", Q207&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R207" s="4" t="s">
@@ -15743,18 +15745,18 @@
         <v>1103</v>
       </c>
       <c r="I208" s="10" t="str">
-        <f>CONCATENATE(A208, B208,C208,D208,E208,F208,G208,H208)</f>
+        <f t="shared" si="6"/>
         <v>idHh</v>
       </c>
       <c r="J208" s="10" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K208" s="2" t="s">
         <v>710</v>
       </c>
       <c r="L208" s="10"/>
       <c r="M208" s="10" t="str">
-        <f>IF(OR(O208&lt;&gt;"", Q208&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R208" s="4" t="s">
@@ -15776,11 +15778,11 @@
         <v>1103</v>
       </c>
       <c r="I209" s="10" t="str">
-        <f>CONCATENATE(A209, B209,C209,D209,E209,F209,G209,H209)</f>
+        <f t="shared" si="6"/>
         <v>idHh</v>
       </c>
       <c r="J209" s="10" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K209" s="2" t="s">
         <v>710</v>
@@ -15789,7 +15791,7 @@
         <v>333</v>
       </c>
       <c r="M209" s="10" t="str">
-        <f>IF(OR(O209&lt;&gt;"", Q209&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N209" s="2" t="s">
@@ -15829,11 +15831,11 @@
       <c r="G210" s="10"/>
       <c r="H210" s="10"/>
       <c r="I210" s="10" t="str">
-        <f>CONCATENATE(A210, B210,C210,D210,E210,F210,G210,H210)</f>
+        <f t="shared" si="6"/>
         <v>idHh</v>
       </c>
       <c r="J210" s="10" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K210" s="2" t="s">
         <v>710</v>
@@ -15842,7 +15844,7 @@
         <v>449</v>
       </c>
       <c r="M210" s="10" t="str">
-        <f>IF(OR(O210&lt;&gt;"", Q210&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S210" s="2" t="s">
@@ -15869,11 +15871,11 @@
       <c r="G211" s="10"/>
       <c r="H211" s="10"/>
       <c r="I211" s="10" t="str">
-        <f>CONCATENATE(A211, B211,C211,D211,E211,F211,G211,H211)</f>
+        <f t="shared" si="6"/>
         <v>idHhOriginal</v>
       </c>
       <c r="J211" s="10" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="K211" s="2" t="s">
         <v>710</v>
@@ -15882,7 +15884,7 @@
         <v>449</v>
       </c>
       <c r="M211" s="10" t="str">
-        <f>IF(OR(O211&lt;&gt;"", Q211&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S211" s="2" t="s">
@@ -15907,7 +15909,7 @@
       <c r="G212" s="10"/>
       <c r="H212" s="10"/>
       <c r="I212" s="10" t="str">
-        <f>CONCATENATE(A212, B212,C212,D212,E212,F212,G212,H212)</f>
+        <f t="shared" si="6"/>
         <v>idMother</v>
       </c>
       <c r="J212" s="10" t="s">
@@ -15920,7 +15922,7 @@
         <v>333</v>
       </c>
       <c r="M212" s="10" t="str">
-        <f>IF(OR(O212&lt;&gt;"", Q212&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S212" s="10" t="s">
@@ -15939,7 +15941,7 @@
         <v>457</v>
       </c>
       <c r="I213" s="10" t="str">
-        <f>CONCATENATE(A213, B213,C213,D213,E213,F213,G213,H213)</f>
+        <f t="shared" si="6"/>
         <v>idMother</v>
       </c>
       <c r="J213" s="10" t="s">
@@ -15952,7 +15954,7 @@
         <v>333</v>
       </c>
       <c r="M213" s="10" t="str">
-        <f>IF(OR(O213&lt;&gt;"", Q213&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N213" s="2" t="s">
@@ -15992,7 +15994,7 @@
       <c r="G214" s="10"/>
       <c r="H214" s="10"/>
       <c r="I214" s="10" t="str">
-        <f>CONCATENATE(A214, B214,C214,D214,E214,F214,G214,H214)</f>
+        <f t="shared" si="6"/>
         <v>idMother</v>
       </c>
       <c r="J214" s="10" t="s">
@@ -16005,7 +16007,7 @@
         <v>333</v>
       </c>
       <c r="M214" s="10" t="str">
-        <f>IF(OR(O214&lt;&gt;"", Q214&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S214" s="10" t="s">
@@ -16024,11 +16026,11 @@
         <v>1074</v>
       </c>
       <c r="I215" s="10" t="str">
-        <f>CONCATENATE(A215, B215,C215,D215,E215,F215,G215,H215)</f>
+        <f t="shared" si="6"/>
         <v>idPartner</v>
       </c>
       <c r="J215" s="10" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="K215" s="2" t="s">
         <v>713</v>
@@ -16037,7 +16039,7 @@
         <v>333</v>
       </c>
       <c r="M215" s="10" t="str">
-        <f>IF(OR(O215&lt;&gt;"", Q215&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N215" s="2" t="s">
@@ -16071,11 +16073,11 @@
         <v>1074</v>
       </c>
       <c r="I216" s="10" t="str">
-        <f>CONCATENATE(A216, B216,C216,D216,E216,F216,G216,H216)</f>
+        <f t="shared" si="6"/>
         <v>idPartner</v>
       </c>
       <c r="J216" s="10" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="K216" s="2" t="s">
         <v>652</v>
@@ -16084,7 +16086,7 @@
         <v>170</v>
       </c>
       <c r="M216" s="10" t="str">
-        <f>IF(OR(O216&lt;&gt;"", Q216&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="N216" s="2" t="s">
@@ -16112,11 +16114,11 @@
         <v>1050</v>
       </c>
       <c r="I217" s="10" t="str">
-        <f>CONCATENATE(A217, B217,C217,D217,E217,F217,G217,H217)</f>
+        <f t="shared" si="6"/>
         <v>idPartnerL1</v>
       </c>
       <c r="J217" s="10" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="K217" s="2" t="s">
         <v>860</v>
@@ -16125,7 +16127,7 @@
         <v>333</v>
       </c>
       <c r="M217" s="10" t="str">
-        <f>IF(OR(O217&lt;&gt;"", Q217&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S217" s="2" t="s">
@@ -16144,18 +16146,18 @@
         <v>1165</v>
       </c>
       <c r="I218" s="10" t="str">
-        <f>CONCATENATE(A218, B218,C218,D218,E218,F218,G218,H218)</f>
+        <f t="shared" si="6"/>
         <v>idPers</v>
       </c>
       <c r="J218" s="10" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="K218" s="2" t="s">
         <v>712</v>
       </c>
       <c r="L218" s="10"/>
       <c r="M218" s="10" t="str">
-        <f>IF(OR(O218&lt;&gt;"", Q218&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R218" s="4" t="s">
@@ -16177,11 +16179,11 @@
         <v>1165</v>
       </c>
       <c r="I219" s="10" t="str">
-        <f>CONCATENATE(A219, B219,C219,D219,E219,F219,G219,H219)</f>
+        <f t="shared" si="6"/>
         <v>idPers</v>
       </c>
       <c r="J219" s="10" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="K219" s="2" t="s">
         <v>712</v>
@@ -16190,7 +16192,7 @@
         <v>333</v>
       </c>
       <c r="M219" s="10" t="str">
-        <f>IF(OR(O219&lt;&gt;"", Q219&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N219" s="2" t="s">
@@ -16224,11 +16226,11 @@
         <v>1165</v>
       </c>
       <c r="I220" s="10" t="str">
-        <f>CONCATENATE(A220, B220,C220,D220,E220,F220,G220,H220)</f>
+        <f t="shared" si="6"/>
         <v>idPers</v>
       </c>
       <c r="J220" s="10" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="K220" s="2" t="s">
         <v>651</v>
@@ -16237,7 +16239,7 @@
         <v>170</v>
       </c>
       <c r="M220" s="10" t="str">
-        <f>IF(OR(O220&lt;&gt;"", Q220&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="N220" s="2" t="s">
@@ -16265,11 +16267,11 @@
         <v>1169</v>
       </c>
       <c r="I221" s="10" t="str">
-        <f>CONCATENATE(A221, B221,C221,D221,E221,F221,G221,H221)</f>
+        <f t="shared" si="6"/>
         <v>idPersOriginal</v>
       </c>
       <c r="J221" s="10" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="K221" s="2" t="s">
         <v>712</v>
@@ -16278,7 +16280,7 @@
         <v>333</v>
       </c>
       <c r="M221" s="10" t="str">
-        <f>IF(OR(O221&lt;&gt;"", Q221&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S221" s="2" t="s">
@@ -16303,11 +16305,11 @@
       <c r="G222" s="10"/>
       <c r="H222" s="10"/>
       <c r="I222" s="10" t="str">
-        <f>CONCATENATE(A222, B222,C222,D222,E222,F222,G222,H222)</f>
+        <f t="shared" si="6"/>
         <v>idStatistics1</v>
       </c>
       <c r="J222" s="10" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K222" s="2" t="s">
         <v>1413</v>
@@ -16316,7 +16318,7 @@
         <v>1024</v>
       </c>
       <c r="M222" s="10" t="str">
-        <f>IF(OR(O222&lt;&gt;"", Q222&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R222" s="4" t="s">
@@ -16338,11 +16340,11 @@
         <v>1167</v>
       </c>
       <c r="I223" s="10" t="str">
-        <f>CONCATENATE(A223, B223,C223,D223,E223,F223,G223,H223)</f>
+        <f t="shared" si="6"/>
         <v>idStatistics21</v>
       </c>
       <c r="J223" s="10" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K223" s="2" t="s">
         <v>1413</v>
@@ -16351,7 +16353,7 @@
         <v>1024</v>
       </c>
       <c r="M223" s="10" t="str">
-        <f>IF(OR(O223&lt;&gt;"", Q223&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R223" s="4" t="s">
@@ -16379,11 +16381,11 @@
       <c r="G224" s="10"/>
       <c r="H224" s="10"/>
       <c r="I224" s="10" t="str">
-        <f>CONCATENATE(A224, B224,C224,D224,E224,F224,G224,H224)</f>
+        <f t="shared" si="6"/>
         <v>idStatistics31</v>
       </c>
       <c r="J224" s="10" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K224" s="2" t="s">
         <v>1413</v>
@@ -16392,7 +16394,7 @@
         <v>1024</v>
       </c>
       <c r="M224" s="10" t="str">
-        <f>IF(OR(O224&lt;&gt;"", Q224&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R224" s="4" t="s">
@@ -16417,11 +16419,11 @@
         <v>1202</v>
       </c>
       <c r="I225" s="10" t="str">
-        <f>CONCATENATE(A225, B225,C225,D225,E225,F225,G225,H225)</f>
+        <f t="shared" si="6"/>
         <v>idtaxDbDonor</v>
       </c>
       <c r="J225" s="10" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="K225" s="2" t="s">
         <v>729</v>
@@ -16430,7 +16432,7 @@
         <v>449</v>
       </c>
       <c r="M225" s="10" t="str">
-        <f>IF(OR(O225&lt;&gt;"", Q225&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S225" s="2" t="s">
@@ -16449,11 +16451,11 @@
         <v>1104</v>
       </c>
       <c r="I226" s="10" t="str">
-        <f>CONCATENATE(A226, B226,C226,D226,E226,F226,G226,H226)</f>
+        <f t="shared" si="6"/>
         <v>labC4</v>
       </c>
       <c r="J226" s="10" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="K226" s="2" t="s">
         <v>473</v>
@@ -16462,7 +16464,7 @@
         <v>333</v>
       </c>
       <c r="M226" s="10" t="str">
-        <f>IF(OR(O226&lt;&gt;"", Q226&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N226" s="2" t="s">
@@ -16499,11 +16501,11 @@
         <v>1050</v>
       </c>
       <c r="I227" s="10" t="str">
-        <f>CONCATENATE(A227, B227,C227,D227,E227,F227,G227,H227)</f>
+        <f t="shared" si="6"/>
         <v>labC4L1</v>
       </c>
       <c r="J227" s="10" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="K227" s="2" t="s">
         <v>489</v>
@@ -16512,7 +16514,7 @@
         <v>333</v>
       </c>
       <c r="M227" s="10" t="str">
-        <f>IF(OR(O227&lt;&gt;"", Q227&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S227" s="2" t="s">
@@ -16534,11 +16536,11 @@
         <v>961</v>
       </c>
       <c r="I228" s="10" t="str">
-        <f>CONCATENATE(A228, B228,C228,D228,E228,F228,G228,H228)</f>
+        <f t="shared" si="6"/>
         <v>labC7Covid</v>
       </c>
       <c r="J228" s="10" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="K228" s="6" t="s">
         <v>702</v>
@@ -16547,7 +16549,7 @@
         <v>333</v>
       </c>
       <c r="M228" s="10" t="str">
-        <f>IF(OR(O228&lt;&gt;"", Q228&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="N228" s="6"/>
@@ -16576,11 +16578,11 @@
         <v>1181</v>
       </c>
       <c r="I229" s="10" t="str">
-        <f>CONCATENATE(A229, B229,C229,D229,E229,F229,G229,H229)</f>
+        <f t="shared" si="6"/>
         <v>labC7CovidL1</v>
       </c>
       <c r="J229" s="10" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="K229" s="6" t="s">
         <v>490</v>
@@ -16589,7 +16591,7 @@
         <v>333</v>
       </c>
       <c r="M229" s="10" t="str">
-        <f>IF(OR(O229&lt;&gt;"", Q229&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="N229" s="6"/>
@@ -16621,11 +16623,11 @@
       <c r="G230" s="20"/>
       <c r="H230" s="20"/>
       <c r="I230" s="20" t="str">
-        <f>CONCATENATE(A230, B230,C230,D230,E230,F230,G230,H230)</f>
+        <f t="shared" si="6"/>
         <v>labEmpNyear</v>
       </c>
       <c r="J230" s="20" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="K230" s="20" t="s">
         <v>1316</v>
@@ -16634,7 +16636,7 @@
         <v>333</v>
       </c>
       <c r="M230" s="21" t="str">
-        <f>IF(OR(O230&lt;&gt;"", Q230&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N230" s="20"/>
@@ -16672,11 +16674,11 @@
       </c>
       <c r="H231" s="10"/>
       <c r="I231" s="10" t="str">
-        <f>CONCATENATE(A231, B231,C231,D231,E231,F231,G231,H231)</f>
+        <f t="shared" si="6"/>
         <v>labEmpShare</v>
       </c>
       <c r="J231" s="10" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="K231" s="2" t="s">
         <v>732</v>
@@ -16685,7 +16687,7 @@
         <v>1022</v>
       </c>
       <c r="M231" s="10" t="str">
-        <f>IF(OR(O231&lt;&gt;"", Q231&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R231" s="4" t="s">
@@ -16698,7 +16700,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="232" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A232" s="10"/>
       <c r="B232" s="10" t="str" cm="1">
         <f t="array" ref="B232">_xlfn.IFS(S232 = Modules!$A$2,Modules!$B$2,S232 = Modules!$A$3,Modules!$B$3,S232 = Modules!$A$4,Modules!$B$4,S232 = Modules!$A$5,Modules!$B$5,S232 = Modules!$A$6,Modules!$B$6,S232 = Modules!$A$7,Modules!$B$7,S232 = Modules!$A$8,Modules!$B$8,S232 = Modules!$A$9,Modules!$B$9,S232 = Modules!$A$10,Modules!$B$10,S232 = Modules!$A$11,Modules!$B$11,S232 = Modules!$A$12,Modules!$B$12, S232 = Modules!$A$13,Modules!$B$13)</f>
@@ -16715,7 +16717,7 @@
       </c>
       <c r="H232" s="10"/>
       <c r="I232" s="10" t="str">
-        <f>CONCATENATE(A232, B232,C232,D232,E232,F232,G232,H232)</f>
+        <f t="shared" si="6"/>
         <v>labEmpToNotEmpShare</v>
       </c>
       <c r="J232" s="10" t="s">
@@ -16728,7 +16730,7 @@
         <v>1022</v>
       </c>
       <c r="M232" s="10" t="str">
-        <f>IF(OR(O232&lt;&gt;"", Q232&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R232" s="4" t="s">
@@ -16759,11 +16761,11 @@
         <v>1002</v>
       </c>
       <c r="I233" s="10" t="str">
-        <f>CONCATENATE(A233, B233,C233,D233,E233,F233,G233,H233)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkEnumWeek</v>
       </c>
       <c r="J233" s="10" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="K233" s="2" t="s">
         <v>762</v>
@@ -16772,7 +16774,7 @@
         <v>333</v>
       </c>
       <c r="M233" s="10" t="str">
-        <f>IF(OR(O233&lt;&gt;"", Q233&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S233" s="2" t="s">
@@ -16803,11 +16805,11 @@
         <v>1225</v>
       </c>
       <c r="I234" s="10" t="str">
-        <f>CONCATENATE(A234, B234,C234,D234,E234,F234,G234,H234)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkEnumWeekL1</v>
       </c>
       <c r="J234" s="10" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="K234" s="2" t="s">
         <v>764</v>
@@ -16816,7 +16818,7 @@
         <v>333</v>
       </c>
       <c r="M234" s="10" t="str">
-        <f>IF(OR(O234&lt;&gt;"", Q234&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S234" s="2" t="s">
@@ -16841,11 +16843,11 @@
         <v>1050</v>
       </c>
       <c r="I235" s="10" t="str">
-        <f>CONCATENATE(A235, B235,C235,D235,E235,F235,G235,H235)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkNewL1</v>
       </c>
       <c r="J235" s="10" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="K235" s="2" t="s">
         <v>404</v>
@@ -16854,7 +16856,7 @@
         <v>333</v>
       </c>
       <c r="M235" s="10" t="str">
-        <f>IF(OR(O235&lt;&gt;"", Q235&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S235" s="2" t="s">
@@ -16876,11 +16878,11 @@
         <v>1002</v>
       </c>
       <c r="I236" s="10" t="str">
-        <f>CONCATENATE(A236, B236,C236,D236,E236,F236,G236,H236)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkWeek</v>
       </c>
       <c r="J236" s="10" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="K236" s="2" t="s">
         <v>862</v>
@@ -16889,7 +16891,7 @@
         <v>333</v>
       </c>
       <c r="M236" s="10" t="str">
-        <f>IF(OR(O236&lt;&gt;"", Q236&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S236" s="2" t="s">
@@ -16919,11 +16921,11 @@
         <v>1002</v>
       </c>
       <c r="I237" s="10" t="str">
-        <f>CONCATENATE(A237, B237,C237,D237,E237,F237,G237,H237)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkWeek</v>
       </c>
       <c r="J237" s="10" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="K237" s="2" t="s">
         <v>657</v>
@@ -16932,7 +16934,7 @@
         <v>170</v>
       </c>
       <c r="M237" s="10" t="str">
-        <f>IF(OR(O237&lt;&gt;"", Q237&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N237" s="2" t="s">
@@ -16971,11 +16973,11 @@
         <v>1225</v>
       </c>
       <c r="I238" s="10" t="str">
-        <f>CONCATENATE(A238, B238,C238,D238,E238,F238,G238,H238)</f>
+        <f t="shared" si="6"/>
         <v>labHrsWorkWeekL1</v>
       </c>
       <c r="J238" s="10" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="K238" s="2" t="s">
         <v>659</v>
@@ -16984,7 +16986,7 @@
         <v>333</v>
       </c>
       <c r="M238" s="10" t="str">
-        <f>IF(OR(O238&lt;&gt;"", Q238&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N238" s="2" t="s">
@@ -17000,7 +17002,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="239" spans="1:22" s="23" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:22" s="23" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="10"/>
       <c r="B239" s="10" t="str" cm="1">
         <f t="array" ref="B239">_xlfn.IFS(S239 = Modules!$A$2,Modules!$B$2,S239 = Modules!$A$3,Modules!$B$3,S239 = Modules!$A$4,Modules!$B$4,S239 = Modules!$A$5,Modules!$B$5,S239 = Modules!$A$6,Modules!$B$6,S239 = Modules!$A$7,Modules!$B$7,S239 = Modules!$A$8,Modules!$B$8,S239 = Modules!$A$9,Modules!$B$9,S239 = Modules!$A$10,Modules!$B$10,S239 = Modules!$A$11,Modules!$B$11,S239 = Modules!$A$12,Modules!$B$12, S239 = Modules!$A$13,Modules!$B$13)</f>
@@ -17017,11 +17019,11 @@
       </c>
       <c r="H239" s="10"/>
       <c r="I239" s="10" t="str">
-        <f>CONCATENATE(A239, B239,C239,D239,E239,F239,G239,H239)</f>
+        <f t="shared" si="6"/>
         <v>labNotEmpToEmpShare</v>
       </c>
       <c r="J239" s="10" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="K239" s="2" t="s">
         <v>731</v>
@@ -17030,7 +17032,7 @@
         <v>1022</v>
       </c>
       <c r="M239" s="10" t="str">
-        <f>IF(OR(O239&lt;&gt;"", Q239&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="N239" s="2"/>
@@ -17068,7 +17070,7 @@
       </c>
       <c r="H240" s="10"/>
       <c r="I240" s="10" t="str">
-        <f>CONCATENATE(A240, B240,C240,D240,E240,F240,G240,H240)</f>
+        <f t="shared" si="6"/>
         <v>labNoWork18to29Share</v>
       </c>
       <c r="J240" s="10" t="s">
@@ -17081,7 +17083,7 @@
         <v>1019</v>
       </c>
       <c r="M240" s="10" t="str">
-        <f>IF(OR(O240&lt;&gt;"", Q240&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R240" s="4" t="s">
@@ -17113,7 +17115,7 @@
       </c>
       <c r="H241" s="10"/>
       <c r="I241" s="10" t="str">
-        <f>CONCATENATE(A241, B241,C241,D241,E241,F241,G241,H241)</f>
+        <f t="shared" si="6"/>
         <v>labNoWork18to54Share</v>
       </c>
       <c r="J241" s="10" t="s">
@@ -17126,7 +17128,7 @@
         <v>1019</v>
       </c>
       <c r="M241" s="10" t="str">
-        <f>IF(OR(O241&lt;&gt;"", Q241&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R241" s="4" t="s">
@@ -17139,7 +17141,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="242" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="10"/>
       <c r="B242" s="10" t="str" cm="1">
         <f t="array" ref="B242">_xlfn.IFS(S242 = Modules!$A$2,Modules!$B$2,S242 = Modules!$A$3,Modules!$B$3,S242 = Modules!$A$4,Modules!$B$4,S242 = Modules!$A$5,Modules!$B$5,S242 = Modules!$A$6,Modules!$B$6,S242 = Modules!$A$7,Modules!$B$7,S242 = Modules!$A$8,Modules!$B$8,S242 = Modules!$A$9,Modules!$B$9,S242 = Modules!$A$10,Modules!$B$10,S242 = Modules!$A$11,Modules!$B$11,S242 = Modules!$A$12,Modules!$B$12, S242 = Modules!$A$13,Modules!$B$13)</f>
@@ -17158,7 +17160,7 @@
       </c>
       <c r="H242" s="10"/>
       <c r="I242" s="10" t="str">
-        <f>CONCATENATE(A242, B242,C242,D242,E242,F242,G242,H242)</f>
+        <f t="shared" si="6"/>
         <v>labNoWork30to54Share</v>
       </c>
       <c r="J242" s="10" t="s">
@@ -17171,7 +17173,7 @@
         <v>1019</v>
       </c>
       <c r="M242" s="10" t="str">
-        <f>IF(OR(O242&lt;&gt;"", Q242&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R242" s="4" t="s">
@@ -17184,7 +17186,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="10"/>
       <c r="B243" s="10" t="str" cm="1">
         <f t="array" ref="B243">_xlfn.IFS(S243 = Modules!$A$2,Modules!$B$2,S243 = Modules!$A$3,Modules!$B$3,S243 = Modules!$A$4,Modules!$B$4,S243 = Modules!$A$5,Modules!$B$5,S243 = Modules!$A$6,Modules!$B$6,S243 = Modules!$A$7,Modules!$B$7,S243 = Modules!$A$8,Modules!$B$8,S243 = Modules!$A$9,Modules!$B$9,S243 = Modules!$A$10,Modules!$B$10,S243 = Modules!$A$11,Modules!$B$11,S243 = Modules!$A$12,Modules!$B$12, S243 = Modules!$A$13,Modules!$B$13)</f>
@@ -17203,7 +17205,7 @@
       </c>
       <c r="H243" s="10"/>
       <c r="I243" s="10" t="str">
-        <f>CONCATENATE(A243, B243,C243,D243,E243,F243,G243,H243)</f>
+        <f t="shared" si="6"/>
         <v>labNoWork55to74Share</v>
       </c>
       <c r="J243" s="10" t="s">
@@ -17216,7 +17218,7 @@
         <v>1019</v>
       </c>
       <c r="M243" s="10" t="str">
-        <f>IF(OR(O243&lt;&gt;"", Q243&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R243" s="4" t="s">
@@ -17241,11 +17243,11 @@
         <v>1418</v>
       </c>
       <c r="I244" s="10" t="str">
-        <f>CONCATENATE(A244, B244,C244,D244,E244,F244,G244,H244)</f>
+        <f t="shared" si="6"/>
         <v>labPersistValueLabourInnov</v>
       </c>
       <c r="J244" s="10" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="K244" s="2" t="s">
         <v>1416</v>
@@ -17254,7 +17256,7 @@
         <v>449</v>
       </c>
       <c r="M244" s="10" t="str">
-        <f>IF(OR(O244&lt;&gt;"", Q244&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S244" s="2" t="s">
@@ -17276,7 +17278,7 @@
         <v>968</v>
       </c>
       <c r="I245" s="10" t="str">
-        <f>CONCATENATE(A245, B245,C245,D245,E245,F245,G245,H245)</f>
+        <f t="shared" si="6"/>
         <v>labRtrdFlag</v>
       </c>
       <c r="J245" s="10" t="s">
@@ -17289,7 +17291,7 @@
         <v>170</v>
       </c>
       <c r="M245" s="10" t="str">
-        <f>IF(OR(O245&lt;&gt;"", Q245&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N245" s="2" t="s">
@@ -17330,11 +17332,11 @@
       <c r="G246" s="10"/>
       <c r="H246" s="10"/>
       <c r="I246" s="10" t="str">
-        <f>CONCATENATE(A246, B246,C246,D246,E246,F246,G246,H246)</f>
+        <f t="shared" si="6"/>
         <v>labStatesContObject</v>
       </c>
       <c r="J246" s="10" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="K246" s="2" t="s">
         <v>1422</v>
@@ -17343,7 +17345,7 @@
         <v>449</v>
       </c>
       <c r="M246" s="10" t="str">
-        <f>IF(OR(O246&lt;&gt;"", Q246&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S246" s="2" t="s">
@@ -17362,11 +17364,11 @@
         <v>530</v>
       </c>
       <c r="I247" s="10" t="str">
-        <f>CONCATENATE(A247, B247,C247,D247,E247,F247,G247,H247)</f>
+        <f t="shared" si="6"/>
         <v>labStatus</v>
       </c>
       <c r="J247" s="10" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="K247" s="7" t="s">
         <v>453</v>
@@ -17375,7 +17377,7 @@
         <v>170</v>
       </c>
       <c r="M247" s="10" t="str">
-        <f>IF(OR(O247&lt;&gt;"", Q247&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N247" s="2" t="s">
@@ -17406,11 +17408,11 @@
         <v>1089</v>
       </c>
       <c r="I248" s="2" t="str">
-        <f>CONCATENATE(A248, B248,C248,D248,E248,F248,G248,H248)</f>
+        <f t="shared" si="6"/>
         <v>labStatusC3</v>
       </c>
       <c r="J248" s="2" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="K248" s="2" t="s">
         <v>1314</v>
@@ -17419,7 +17421,7 @@
         <v>170</v>
       </c>
       <c r="M248" s="10" t="str">
-        <f>IF(OR(O248&lt;&gt;"", Q248&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="P248" s="6" t="s">
@@ -17447,11 +17449,11 @@
         <v>1089</v>
       </c>
       <c r="I249" s="10" t="str">
-        <f>CONCATENATE(A249, B249,C249,D249,E249,F249,G249,H249)</f>
+        <f t="shared" si="6"/>
         <v>labStatusC3</v>
       </c>
       <c r="J249" s="10" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="K249" s="6" t="s">
         <v>628</v>
@@ -17460,7 +17462,7 @@
         <v>333</v>
       </c>
       <c r="M249" s="10" t="str">
-        <f>IF(OR(O249&lt;&gt;"", Q249&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N249" s="6" t="s">
@@ -17495,11 +17497,11 @@
         <v>1104</v>
       </c>
       <c r="I250" s="2" t="str">
-        <f>CONCATENATE(A250, B250,C250,D250,E250,F250,G250,H250)</f>
+        <f t="shared" si="6"/>
         <v>labStatusC4</v>
       </c>
       <c r="J250" s="2" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="K250" s="2" t="s">
         <v>489</v>
@@ -17508,7 +17510,7 @@
         <v>170</v>
       </c>
       <c r="M250" s="10" t="str">
-        <f>IF(OR(O250&lt;&gt;"", Q250&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="P250" s="6" t="s">
@@ -17539,11 +17541,11 @@
         <v>1104</v>
       </c>
       <c r="I251" s="10" t="str">
-        <f>CONCATENATE(A251, B251,C251,D251,E251,F251,G251,H251)</f>
+        <f t="shared" si="6"/>
         <v>labStatusPartnerAndOwnC4</v>
       </c>
       <c r="J251" s="10" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="K251" s="2" t="s">
         <v>927</v>
@@ -17552,7 +17554,7 @@
         <v>333</v>
       </c>
       <c r="M251" s="10" t="str">
-        <f>IF(OR(O251&lt;&gt;"", Q251&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N251" s="2" t="s">
@@ -17595,11 +17597,11 @@
         <v>1050</v>
       </c>
       <c r="I252" s="10" t="str">
-        <f>CONCATENATE(A252, B252,C252,D252,E252,F252,G252,H252)</f>
+        <f t="shared" si="6"/>
         <v>labStatusPartnerAndOwnC4L1</v>
       </c>
       <c r="J252" s="10" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="K252" s="2" t="s">
         <v>491</v>
@@ -17608,7 +17610,7 @@
         <v>333</v>
       </c>
       <c r="M252" s="10" t="str">
-        <f>IF(OR(O252&lt;&gt;"", Q252&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="S252" s="2" t="s">
@@ -17633,11 +17635,11 @@
         <v>1089</v>
       </c>
       <c r="I253" s="10" t="str">
-        <f>CONCATENATE(A253, B253,C253,D253,E253,F253,G253,H253)</f>
+        <f t="shared" si="6"/>
         <v>labStatusPartnerC3</v>
       </c>
       <c r="J253" s="10" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="K253" s="6" t="s">
         <v>630</v>
@@ -17646,7 +17648,7 @@
         <v>333</v>
       </c>
       <c r="M253" s="10" t="str">
-        <f>IF(OR(O253&lt;&gt;"", Q253&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N253" s="6" t="s">
@@ -17683,11 +17685,11 @@
         <v>1104</v>
       </c>
       <c r="I254" s="10" t="str">
-        <f>CONCATENATE(A254, B254,C254,D254,E254,F254,G254,H254)</f>
+        <f t="shared" si="6"/>
         <v>labStatusPartnerC4</v>
       </c>
       <c r="J254" s="10" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="K254" s="2" t="s">
         <v>474</v>
@@ -17696,7 +17698,7 @@
         <v>170</v>
       </c>
       <c r="M254" s="10" t="str">
-        <f>IF(OR(O254&lt;&gt;"", Q254&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N254" s="6" t="s">
@@ -17733,17 +17735,17 @@
         <v>968</v>
       </c>
       <c r="I255" s="2" t="str">
-        <f>CONCATENATE(A255, B255,C255,D255,E255,F255,G255,H255)</f>
+        <f t="shared" si="6"/>
         <v>labStudentFlag</v>
       </c>
       <c r="J255" s="2" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="K255" s="2" t="s">
         <v>1321</v>
       </c>
       <c r="M255" s="10" t="str">
-        <f>IF(OR(O255&lt;&gt;"", Q255&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="P255" s="2" t="s">
@@ -17776,11 +17778,11 @@
       </c>
       <c r="H256" s="10"/>
       <c r="I256" s="10" t="str">
-        <f>CONCATENATE(A256, B256,C256,D256,E256,F256,G256,H256)</f>
+        <f t="shared" si="6"/>
         <v>labUnempFlag</v>
       </c>
       <c r="J256" s="10" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="K256" s="2" t="s">
         <v>692</v>
@@ -17789,7 +17791,7 @@
         <v>170</v>
       </c>
       <c r="M256" s="10" t="str">
-        <f>IF(OR(O256&lt;&gt;"", Q256&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>Yes</v>
       </c>
       <c r="N256" s="2" t="s">
@@ -17828,11 +17830,11 @@
       </c>
       <c r="H257" s="10"/>
       <c r="I257" s="10" t="str">
-        <f>CONCATENATE(A257, B257,C257,D257,E257,F257,G257,H257)</f>
+        <f t="shared" si="6"/>
         <v>labUnempShare</v>
       </c>
       <c r="J257" s="10" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="K257" s="2" t="s">
         <v>733</v>
@@ -17841,7 +17843,7 @@
         <v>1022</v>
       </c>
       <c r="M257" s="10" t="str">
-        <f>IF(OR(O257&lt;&gt;"", Q257&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="7"/>
         <v>No</v>
       </c>
       <c r="R257" s="4" t="s">
@@ -17873,11 +17875,11 @@
         <v>1145</v>
       </c>
       <c r="I258" s="10" t="str">
-        <f>CONCATENATE(A258, B258,C258,D258,E258,F258,G258,H258)</f>
+        <f t="shared" ref="I258:I321" si="8">CONCATENATE(A258, B258,C258,D258,E258,F258,G258,H258)</f>
         <v>labWageFullTimeHrly</v>
       </c>
       <c r="J258" s="10" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K258" s="2" t="s">
         <v>664</v>
@@ -17886,7 +17888,7 @@
         <v>333</v>
       </c>
       <c r="M258" s="10" t="str">
-        <f>IF(OR(O258&lt;&gt;"", Q258&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M258:M321" si="9">IF(OR(O258&lt;&gt;"", Q258&lt;&gt;""),"Yes","No")</f>
         <v>No</v>
       </c>
       <c r="N258" s="2"/>
@@ -17924,11 +17926,11 @@
         <v>1177</v>
       </c>
       <c r="I259" s="10" t="str">
-        <f>CONCATENATE(A259, B259,C259,D259,E259,F259,G259,H259)</f>
+        <f t="shared" si="8"/>
         <v>labWageFullTimeHrlyL1</v>
       </c>
       <c r="J259" s="10" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="K259" s="2" t="s">
         <v>740</v>
@@ -17937,7 +17939,7 @@
         <v>333</v>
       </c>
       <c r="M259" s="10" t="str">
-        <f>IF(OR(O259&lt;&gt;"", Q259&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="N259" s="2"/>
@@ -17966,11 +17968,11 @@
         <v>1145</v>
       </c>
       <c r="I260" s="2" t="str">
-        <f>CONCATENATE(A260, B260,C260,D260,E260,F260,G260,H260)</f>
+        <f t="shared" si="8"/>
         <v>labWageHrly</v>
       </c>
       <c r="J260" s="2" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="K260" s="2" t="s">
         <v>1348</v>
@@ -17979,7 +17981,7 @@
         <v>170</v>
       </c>
       <c r="M260" s="10" t="str">
-        <f>IF(OR(O260&lt;&gt;"", Q260&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S260" s="2" t="s">
@@ -18001,11 +18003,11 @@
         <v>1145</v>
       </c>
       <c r="I261" s="10" t="str">
-        <f>CONCATENATE(A261, B261,C261,D261,E261,F261,G261,H261)</f>
+        <f t="shared" si="8"/>
         <v>labWageHrly</v>
       </c>
       <c r="J261" s="10" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="K261" s="2" t="s">
         <v>1364</v>
@@ -18014,7 +18016,7 @@
         <v>333</v>
       </c>
       <c r="M261" s="10" t="str">
-        <f>IF(OR(O261&lt;&gt;"", Q261&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N261" s="2" t="s">
@@ -18051,11 +18053,11 @@
         <v>1177</v>
       </c>
       <c r="I262" s="2" t="str">
-        <f>CONCATENATE(A262, B262,C262,D262,E262,F262,G262,H262)</f>
+        <f t="shared" si="8"/>
         <v>labWageHrlyL1</v>
       </c>
       <c r="J262" s="2" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="K262" s="2" t="s">
         <v>1348</v>
@@ -18064,7 +18066,7 @@
         <v>170</v>
       </c>
       <c r="M262" s="10" t="str">
-        <f>IF(OR(O262&lt;&gt;"", Q262&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S262" s="2" t="s">
@@ -18090,11 +18092,11 @@
         <v>1177</v>
       </c>
       <c r="I263" s="10" t="str">
-        <f>CONCATENATE(A263, B263,C263,D263,E263,F263,G263,H263)</f>
+        <f t="shared" si="8"/>
         <v>labWageHrlyL1</v>
       </c>
       <c r="J263" s="10" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="K263" s="2" t="s">
         <v>668</v>
@@ -18103,7 +18105,7 @@
         <v>333</v>
       </c>
       <c r="M263" s="10" t="str">
-        <f>IF(OR(O263&lt;&gt;"", Q263&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N263" s="2" t="s">
@@ -18134,11 +18136,11 @@
         <v>968</v>
       </c>
       <c r="I264" s="10" t="str">
-        <f>CONCATENATE(A264, B264,C264,D264,E264,F264,G264,H264)</f>
+        <f t="shared" si="8"/>
         <v>labWageOfferLowFlag</v>
       </c>
       <c r="J264" s="10" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="K264" s="2" t="s">
         <v>765</v>
@@ -18147,7 +18149,7 @@
         <v>333</v>
       </c>
       <c r="M264" s="10" t="str">
-        <f>IF(OR(O264&lt;&gt;"", Q264&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S264" s="2" t="s">
@@ -18175,11 +18177,11 @@
         <v>1050</v>
       </c>
       <c r="I265" s="10" t="str">
-        <f>CONCATENATE(A265, B265,C265,D265,E265,F265,G265,H265)</f>
+        <f t="shared" si="8"/>
         <v>labWageOfferLowFlagL1</v>
       </c>
       <c r="J265" s="10" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="K265" s="2" t="s">
         <v>766</v>
@@ -18188,7 +18190,7 @@
         <v>333</v>
       </c>
       <c r="M265" s="10" t="str">
-        <f>IF(OR(O265&lt;&gt;"", Q265&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S265" s="2" t="s">
@@ -18210,11 +18212,11 @@
         <v>1210</v>
       </c>
       <c r="I266" s="10" t="str">
-        <f>CONCATENATE(A266, B266,C266,D266,E266,F266,G266,H266)</f>
+        <f t="shared" si="8"/>
         <v>labWageRegressRandomCompoponentEmp</v>
       </c>
       <c r="J266" s="10" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="K266" s="2" t="s">
         <v>870</v>
@@ -18223,7 +18225,7 @@
         <v>333</v>
       </c>
       <c r="M266" s="10" t="str">
-        <f>IF(OR(O266&lt;&gt;"", Q266&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S266" s="2" t="s">
@@ -18248,11 +18250,11 @@
         <v>1211</v>
       </c>
       <c r="I267" s="10" t="str">
-        <f>CONCATENATE(A267, B267,C267,D267,E267,F267,G267,H267)</f>
+        <f t="shared" si="8"/>
         <v>labWageRegressRandomCompoponentNotEmp</v>
       </c>
       <c r="J267" s="10" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="K267" s="2" t="s">
         <v>871</v>
@@ -18261,7 +18263,7 @@
         <v>333</v>
       </c>
       <c r="M267" s="10" t="str">
-        <f>IF(OR(O267&lt;&gt;"", Q267&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S267" s="2" t="s">
@@ -18293,7 +18295,7 @@
       </c>
       <c r="H268" s="10"/>
       <c r="I268" s="10" t="str">
-        <f>CONCATENATE(A268, B268,C268,D268,E268,F268,G268,H268)</f>
+        <f t="shared" si="8"/>
         <v>labWorkFullTime18to29Share</v>
       </c>
       <c r="J268" s="10" t="s">
@@ -18306,7 +18308,7 @@
         <v>1019</v>
       </c>
       <c r="M268" s="10" t="str">
-        <f>IF(OR(O268&lt;&gt;"", Q268&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R268" s="4" t="s">
@@ -18338,7 +18340,7 @@
       </c>
       <c r="H269" s="10"/>
       <c r="I269" s="10" t="str">
-        <f>CONCATENATE(A269, B269,C269,D269,E269,F269,G269,H269)</f>
+        <f t="shared" si="8"/>
         <v>labWorkFullTime30to54Share</v>
       </c>
       <c r="J269" s="10" t="s">
@@ -18351,7 +18353,7 @@
         <v>1019</v>
       </c>
       <c r="M269" s="10" t="str">
-        <f>IF(OR(O269&lt;&gt;"", Q269&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R269" s="4" t="s">
@@ -18383,7 +18385,7 @@
       </c>
       <c r="H270" s="10"/>
       <c r="I270" s="10" t="str">
-        <f>CONCATENATE(A270, B270,C270,D270,E270,F270,G270,H270)</f>
+        <f t="shared" si="8"/>
         <v>labWorkFullTime55to74Share</v>
       </c>
       <c r="J270" s="10" t="s">
@@ -18396,7 +18398,7 @@
         <v>1019</v>
       </c>
       <c r="M270" s="10" t="str">
-        <f>IF(OR(O270&lt;&gt;"", Q270&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R270" s="4" t="s">
@@ -18424,11 +18426,11 @@
       <c r="G271" s="20"/>
       <c r="H271" s="20"/>
       <c r="I271" s="21" t="str">
-        <f>CONCATENATE(A271, B271,C271,D271,E271,F271,G271,H271)</f>
+        <f t="shared" si="8"/>
         <v>labWorkHist</v>
       </c>
       <c r="J271" s="21" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="K271" s="20" t="s">
         <v>337</v>
@@ -18437,7 +18439,7 @@
         <v>333</v>
       </c>
       <c r="M271" s="21" t="str">
-        <f>IF(OR(O271&lt;&gt;"", Q271&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="N271" s="20"/>
@@ -18469,7 +18471,7 @@
         <v>1040</v>
       </c>
       <c r="I272" s="10" t="str">
-        <f>CONCATENATE(A272, B272,C272,D272,E272,F272,G272,H272)</f>
+        <f t="shared" si="8"/>
         <v>labWorkPartTime18to29Share</v>
       </c>
       <c r="J272" s="10" t="s">
@@ -18482,7 +18484,7 @@
         <v>1019</v>
       </c>
       <c r="M272" s="10" t="str">
-        <f>IF(OR(O272&lt;&gt;"", Q272&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="N272" s="2"/>
@@ -18515,7 +18517,7 @@
         <v>1040</v>
       </c>
       <c r="I273" s="10" t="str">
-        <f>CONCATENATE(A273, B273,C273,D273,E273,F273,G273,H273)</f>
+        <f t="shared" si="8"/>
         <v>labWorkPartTime30to54Share</v>
       </c>
       <c r="J273" s="10" t="s">
@@ -18528,7 +18530,7 @@
         <v>1019</v>
       </c>
       <c r="M273" s="10" t="str">
-        <f>IF(OR(O273&lt;&gt;"", Q273&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="N273" s="2"/>
@@ -18565,7 +18567,7 @@
       </c>
       <c r="H274" s="10"/>
       <c r="I274" s="10" t="str">
-        <f>CONCATENATE(A274, B274,C274,D274,E274,F274,G274,H274)</f>
+        <f t="shared" si="8"/>
         <v>labWorkPartTime55to74Share</v>
       </c>
       <c r="J274" s="10" t="s">
@@ -18578,7 +18580,7 @@
         <v>1019</v>
       </c>
       <c r="M274" s="10" t="str">
-        <f>IF(OR(O274&lt;&gt;"", Q274&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R274" s="4" t="s">
@@ -18591,7 +18593,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="275" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B275" s="10" t="str" cm="1">
         <f t="array" ref="B275">_xlfn.IFS(S275 = Modules!$A$2,Modules!$B$2,S275 = Modules!$A$3,Modules!$B$3,S275 = Modules!$A$4,Modules!$B$4,S275 = Modules!$A$5,Modules!$B$5,S275 = Modules!$A$6,Modules!$B$6,S275 = Modules!$A$7,Modules!$B$7,S275 = Modules!$A$8,Modules!$B$8,S275 = Modules!$A$9,Modules!$B$9,S275 = Modules!$A$10,Modules!$B$10,S275 = Modules!$A$11,Modules!$B$11,S275 = Modules!$A$12,Modules!$B$12, S275 = Modules!$A$13,Modules!$B$13)</f>
         <v>stat</v>
@@ -18600,11 +18602,11 @@
         <v>1396</v>
       </c>
       <c r="I275" s="10" t="str">
-        <f>CONCATENATE(A275, B275,C275,D275,E275,F275,G275,H275)</f>
+        <f t="shared" si="8"/>
         <v>statCollectionWave</v>
       </c>
       <c r="J275" s="10" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="K275" s="2" t="s">
         <v>478</v>
@@ -18613,7 +18615,7 @@
         <v>170</v>
       </c>
       <c r="M275" s="10" t="str">
-        <f>IF(OR(O275&lt;&gt;"", Q275&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N275" s="2" t="s">
@@ -18647,11 +18649,11 @@
         <v>1110</v>
       </c>
       <c r="I276" s="10" t="str">
-        <f>CONCATENATE(A276, B276,C276,D276,E276,F276,G276,H276)</f>
+        <f t="shared" si="8"/>
         <v>statFScore</v>
       </c>
       <c r="J276" s="10" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="K276" s="2" t="s">
         <v>1378</v>
@@ -18660,7 +18662,7 @@
         <v>333</v>
       </c>
       <c r="M276" s="10" t="str">
-        <f>IF(OR(O276&lt;&gt;"", Q276&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S276" s="2" t="s">
@@ -18679,11 +18681,11 @@
         <v>1394</v>
       </c>
       <c r="I277" s="10" t="str">
-        <f>CONCATENATE(A277, B277,C277,D277,E277,F277,G277,H277)</f>
+        <f t="shared" si="8"/>
         <v>statInnovations</v>
       </c>
       <c r="J277" s="10" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="K277" s="2" t="s">
         <v>1393</v>
@@ -18692,7 +18694,7 @@
         <v>333</v>
       </c>
       <c r="M277" s="10" t="str">
-        <f>IF(OR(O277&lt;&gt;"", Q277&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S277" s="2" t="s">
@@ -18714,11 +18716,11 @@
         <v>697</v>
       </c>
       <c r="I278" s="10" t="str">
-        <f>CONCATENATE(A278, B278,C278,D278,E278,F278,G278,H278)</f>
+        <f t="shared" si="8"/>
         <v>statInterviewYear</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="K278" s="2" t="s">
         <v>646</v>
@@ -18727,7 +18729,7 @@
         <v>170</v>
       </c>
       <c r="M278" s="10" t="str">
-        <f>IF(OR(O278&lt;&gt;"", Q278&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N278" s="2" t="s">
@@ -18764,11 +18766,11 @@
         <v>1068</v>
       </c>
       <c r="I279" s="10" t="str">
-        <f>CONCATENATE(A279, B279,C279,D279,E279,F279,G279,H279)</f>
+        <f t="shared" si="8"/>
         <v>statInverseMillsRatioMaxF</v>
       </c>
       <c r="J279" s="10" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="K279" s="6" t="s">
         <v>886</v>
@@ -18777,7 +18779,7 @@
         <v>333</v>
       </c>
       <c r="M279" s="10" t="str">
-        <f>IF(OR(O279&lt;&gt;"", Q279&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S279" s="10" t="s">
@@ -18802,11 +18804,11 @@
         <v>1069</v>
       </c>
       <c r="I280" s="10" t="str">
-        <f>CONCATENATE(A280, B280,C280,D280,E280,F280,G280,H280)</f>
+        <f t="shared" si="8"/>
         <v>statInverseMillsRatioMaxM</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="K280" s="2" t="s">
         <v>884</v>
@@ -18815,7 +18817,7 @@
         <v>333</v>
       </c>
       <c r="M280" s="10" t="str">
-        <f>IF(OR(O280&lt;&gt;"", Q280&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S280" s="10" t="s">
@@ -18840,11 +18842,11 @@
         <v>1068</v>
       </c>
       <c r="I281" s="10" t="str">
-        <f>CONCATENATE(A281, B281,C281,D281,E281,F281,G281,H281)</f>
+        <f t="shared" si="8"/>
         <v>statInverseMillsRatioMinF</v>
       </c>
       <c r="J281" s="10" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="K281" s="6" t="s">
         <v>887</v>
@@ -18853,7 +18855,7 @@
         <v>333</v>
       </c>
       <c r="M281" s="10" t="str">
-        <f>IF(OR(O281&lt;&gt;"", Q281&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S281" s="10" t="s">
@@ -18878,11 +18880,11 @@
         <v>1069</v>
       </c>
       <c r="I282" s="10" t="str">
-        <f>CONCATENATE(A282, B282,C282,D282,E282,F282,G282,H282)</f>
+        <f t="shared" si="8"/>
         <v>statInverseMillsRatioMinM</v>
       </c>
       <c r="J282" s="10" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="K282" s="2" t="s">
         <v>885</v>
@@ -18891,7 +18893,7 @@
         <v>333</v>
       </c>
       <c r="M282" s="10" t="str">
-        <f>IF(OR(O282&lt;&gt;"", Q282&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S282" s="10" t="s">
@@ -18922,11 +18924,11 @@
       </c>
       <c r="H283" s="10"/>
       <c r="I283" s="10" t="str">
-        <f>CONCATENATE(A283, B283,C283,D283,E283,F283,G283,H283)</f>
+        <f t="shared" si="8"/>
         <v>statInvestLoss18to29Avg</v>
       </c>
       <c r="J283" s="10" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="K283" s="6" t="s">
         <v>823</v>
@@ -18935,7 +18937,7 @@
         <v>1019</v>
       </c>
       <c r="M283" s="10" t="str">
-        <f>IF(OR(O283&lt;&gt;"", Q283&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R283" s="4" t="s">
@@ -18969,11 +18971,11 @@
       </c>
       <c r="H284" s="10"/>
       <c r="I284" s="10" t="str">
-        <f>CONCATENATE(A284, B284,C284,D284,E284,F284,G284,H284)</f>
+        <f t="shared" si="8"/>
         <v>statInvestLoss30to54Avg</v>
       </c>
       <c r="J284" s="10" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="K284" s="6" t="s">
         <v>824</v>
@@ -18982,7 +18984,7 @@
         <v>1019</v>
       </c>
       <c r="M284" s="10" t="str">
-        <f>IF(OR(O284&lt;&gt;"", Q284&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R284" s="4" t="s">
@@ -19016,11 +19018,11 @@
       </c>
       <c r="H285" s="10"/>
       <c r="I285" s="10" t="str">
-        <f>CONCATENATE(A285, B285,C285,D285,E285,F285,G285,H285)</f>
+        <f t="shared" si="8"/>
         <v>statInvestLoss55to74Avg</v>
       </c>
       <c r="J285" s="10" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="K285" s="6" t="s">
         <v>825</v>
@@ -19029,7 +19031,7 @@
         <v>1019</v>
       </c>
       <c r="M285" s="10" t="str">
-        <f>IF(OR(O285&lt;&gt;"", Q285&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R285" s="4" t="s">
@@ -19054,11 +19056,11 @@
         <v>1110</v>
       </c>
       <c r="I286" s="10" t="str">
-        <f>CONCATENATE(A286, B286,C286,D286,E286,F286,G286,H286)</f>
+        <f t="shared" si="8"/>
         <v>statMScore</v>
       </c>
       <c r="J286" s="10" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="K286" s="2" t="s">
         <v>1379</v>
@@ -19067,7 +19069,7 @@
         <v>333</v>
       </c>
       <c r="M286" s="10" t="str">
-        <f>IF(OR(O286&lt;&gt;"", Q286&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S286" s="2" t="s">
@@ -19086,18 +19088,18 @@
         <v>1232</v>
       </c>
       <c r="I287" s="10" t="str">
-        <f>CONCATENATE(A287, B287,C287,D287,E287,F287,G287,H287)</f>
+        <f t="shared" si="8"/>
         <v>statRun</v>
       </c>
       <c r="J287" s="10" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="K287" s="2" t="s">
         <v>696</v>
       </c>
       <c r="L287" s="10"/>
       <c r="M287" s="10" t="str">
-        <f>IF(OR(O287&lt;&gt;"", Q287&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R287" s="4" t="s">
@@ -19119,11 +19121,11 @@
         <v>724</v>
       </c>
       <c r="I288" s="10" t="str">
-        <f>CONCATENATE(A288, B288,C288,D288,E288,F288,G288,H288)</f>
+        <f t="shared" si="8"/>
         <v>statSeed</v>
       </c>
       <c r="J288" s="10" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="K288" s="2" t="s">
         <v>724</v>
@@ -19132,7 +19134,7 @@
         <v>449</v>
       </c>
       <c r="M288" s="10" t="str">
-        <f>IF(OR(O288&lt;&gt;"", Q288&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S288" s="2" t="s">
@@ -19156,11 +19158,11 @@
       <c r="G289" s="10"/>
       <c r="H289" s="10"/>
       <c r="I289" s="10" t="str">
-        <f>CONCATENATE(A289, B289,C289,D289,E289,F289,G289,H289)</f>
+        <f t="shared" si="8"/>
         <v>statSIndex</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="K289" s="2" t="s">
         <v>1452</v>
@@ -19169,7 +19171,7 @@
         <v>333</v>
       </c>
       <c r="M289" s="10" t="str">
-        <f>IF(OR(O289&lt;&gt;"", Q289&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S289" s="2" t="s">
@@ -19196,11 +19198,11 @@
       <c r="G290" s="10"/>
       <c r="H290" s="10"/>
       <c r="I290" s="10" t="str">
-        <f>CONCATENATE(A290, B290,C290,D290,E290,F290,G290,H290)</f>
+        <f t="shared" si="8"/>
         <v>statSIndexNormal</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="K290" s="2" t="s">
         <v>1453</v>
@@ -19209,7 +19211,7 @@
         <v>333</v>
       </c>
       <c r="M290" s="10" t="str">
-        <f>IF(OR(O290&lt;&gt;"", Q290&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S290" s="2" t="s">
@@ -19240,7 +19242,7 @@
       </c>
       <c r="H291" s="10"/>
       <c r="I291" s="10" t="str">
-        <f>CONCATENATE(A291, B291,C291,D291,E291,F291,G291,H291)</f>
+        <f t="shared" si="8"/>
         <v>statYDisp18to29Avg</v>
       </c>
       <c r="J291" s="10" t="s">
@@ -19253,7 +19255,7 @@
         <v>1019</v>
       </c>
       <c r="M291" s="10" t="str">
-        <f>IF(OR(O291&lt;&gt;"", Q291&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R291" s="4" t="s">
@@ -19287,7 +19289,7 @@
       </c>
       <c r="H292" s="10"/>
       <c r="I292" s="10" t="str">
-        <f>CONCATENATE(A292, B292,C292,D292,E292,F292,G292,H292)</f>
+        <f t="shared" si="8"/>
         <v>statYDisp30to54Avg</v>
       </c>
       <c r="J292" s="10" t="s">
@@ -19300,7 +19302,7 @@
         <v>1019</v>
       </c>
       <c r="M292" s="10" t="str">
-        <f>IF(OR(O292&lt;&gt;"", Q292&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R292" s="4" t="s">
@@ -19334,7 +19336,7 @@
       </c>
       <c r="H293" s="10"/>
       <c r="I293" s="10" t="str">
-        <f>CONCATENATE(A293, B293,C293,D293,E293,F293,G293,H293)</f>
+        <f t="shared" si="8"/>
         <v>statYDisp55to74Avg</v>
       </c>
       <c r="J293" s="10" t="s">
@@ -19347,7 +19349,7 @@
         <v>1019</v>
       </c>
       <c r="M293" s="10" t="str">
-        <f>IF(OR(O293&lt;&gt;"", Q293&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R293" s="4" t="s">
@@ -19381,7 +19383,7 @@
       </c>
       <c r="H294" s="10"/>
       <c r="I294" s="10" t="str">
-        <f>CONCATENATE(A294, B294,C294,D294,E294,F294,G294,H294)</f>
+        <f t="shared" si="8"/>
         <v>statYDispGrossOfLosses18to29Avg</v>
       </c>
       <c r="J294" s="10" t="s">
@@ -19394,7 +19396,7 @@
         <v>1019</v>
       </c>
       <c r="M294" s="10" t="str">
-        <f>IF(OR(O294&lt;&gt;"", Q294&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S294" s="2" t="s">
@@ -19428,7 +19430,7 @@
       </c>
       <c r="H295" s="10"/>
       <c r="I295" s="10" t="str">
-        <f>CONCATENATE(A295, B295,C295,D295,E295,F295,G295,H295)</f>
+        <f t="shared" si="8"/>
         <v>statYDispGrossOfLosses30to54Avg</v>
       </c>
       <c r="J295" s="10" t="s">
@@ -19441,7 +19443,7 @@
         <v>1019</v>
       </c>
       <c r="M295" s="10" t="str">
-        <f>IF(OR(O295&lt;&gt;"", Q295&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S295" s="2" t="s">
@@ -19475,7 +19477,7 @@
       </c>
       <c r="H296" s="10"/>
       <c r="I296" s="10" t="str">
-        <f>CONCATENATE(A296, B296,C296,D296,E296,F296,G296,H296)</f>
+        <f t="shared" si="8"/>
         <v>statYDispGrossOfLosses55to75Avg</v>
       </c>
       <c r="J296" s="10" t="s">
@@ -19488,7 +19490,7 @@
         <v>1019</v>
       </c>
       <c r="M296" s="10" t="str">
-        <f>IF(OR(O296&lt;&gt;"", Q296&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S296" s="2" t="s">
@@ -19524,11 +19526,11 @@
       </c>
       <c r="H297" s="4"/>
       <c r="I297" s="10" t="str">
-        <f>CONCATENATE(A297, B297,C297,D297,E297,F297,G297,H297)</f>
+        <f t="shared" si="8"/>
         <v>statYHhDispEquivNatGini</v>
       </c>
       <c r="J297" s="10" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="K297" s="2" t="s">
         <v>1226</v>
@@ -19537,7 +19539,7 @@
         <v>1024</v>
       </c>
       <c r="M297" s="10" t="str">
-        <f>IF(OR(O297&lt;&gt;"", Q297&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R297" s="4" t="s">
@@ -19571,11 +19573,11 @@
       </c>
       <c r="H298" s="10"/>
       <c r="I298" s="10" t="str">
-        <f>CONCATENATE(A298, B298,C298,D298,E298,F298,G298,H298)</f>
+        <f t="shared" si="8"/>
         <v>statYInvest18to29Avg</v>
       </c>
       <c r="J298" s="10" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="K298" s="6" t="s">
         <v>820</v>
@@ -19584,7 +19586,7 @@
         <v>1019</v>
       </c>
       <c r="M298" s="10" t="str">
-        <f>IF(OR(O298&lt;&gt;"", Q298&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R298" s="4" t="s">
@@ -19618,11 +19620,11 @@
       </c>
       <c r="H299" s="10"/>
       <c r="I299" s="10" t="str">
-        <f>CONCATENATE(A299, B299,C299,D299,E299,F299,G299,H299)</f>
+        <f t="shared" si="8"/>
         <v>statYInvest30to54Avg</v>
       </c>
       <c r="J299" s="10" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="K299" s="6" t="s">
         <v>821</v>
@@ -19631,7 +19633,7 @@
         <v>1019</v>
       </c>
       <c r="M299" s="10" t="str">
-        <f>IF(OR(O299&lt;&gt;"", Q299&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R299" s="4" t="s">
@@ -19665,11 +19667,11 @@
       </c>
       <c r="H300" s="10"/>
       <c r="I300" s="10" t="str">
-        <f>CONCATENATE(A300, B300,C300,D300,E300,F300,G300,H300)</f>
+        <f t="shared" si="8"/>
         <v>statYInvest55to74Avg</v>
       </c>
       <c r="J300" s="10" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="K300" s="6" t="s">
         <v>822</v>
@@ -19678,7 +19680,7 @@
         <v>1019</v>
       </c>
       <c r="M300" s="10" t="str">
-        <f>IF(OR(O300&lt;&gt;"", Q300&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R300" s="4" t="s">
@@ -19712,11 +19714,11 @@
       </c>
       <c r="H301" s="10"/>
       <c r="I301" s="10" t="str">
-        <f>CONCATENATE(A301, B301,C301,D301,E301,F301,G301,H301)</f>
+        <f t="shared" si="8"/>
         <v>statYLab18to29Avg</v>
       </c>
       <c r="J301" s="10" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="K301" s="6" t="s">
         <v>826</v>
@@ -19725,7 +19727,7 @@
         <v>1019</v>
       </c>
       <c r="M301" s="10" t="str">
-        <f>IF(OR(O301&lt;&gt;"", Q301&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R301" s="4" t="s">
@@ -19759,11 +19761,11 @@
       </c>
       <c r="H302" s="10"/>
       <c r="I302" s="10" t="str">
-        <f>CONCATENATE(A302, B302,C302,D302,E302,F302,G302,H302)</f>
+        <f t="shared" si="8"/>
         <v>statYLab30to54Avg</v>
       </c>
       <c r="J302" s="10" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="K302" s="6" t="s">
         <v>827</v>
@@ -19772,7 +19774,7 @@
         <v>1019</v>
       </c>
       <c r="M302" s="10" t="str">
-        <f>IF(OR(O302&lt;&gt;"", Q302&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R302" s="4" t="s">
@@ -19785,7 +19787,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="303" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="10"/>
       <c r="B303" s="10" t="str" cm="1">
         <f t="array" ref="B303">_xlfn.IFS(S303 = Modules!$A$2,Modules!$B$2,S303 = Modules!$A$3,Modules!$B$3,S303 = Modules!$A$4,Modules!$B$4,S303 = Modules!$A$5,Modules!$B$5,S303 = Modules!$A$6,Modules!$B$6,S303 = Modules!$A$7,Modules!$B$7,S303 = Modules!$A$8,Modules!$B$8,S303 = Modules!$A$9,Modules!$B$9,S303 = Modules!$A$10,Modules!$B$10,S303 = Modules!$A$11,Modules!$B$11,S303 = Modules!$A$12,Modules!$B$12, S303 = Modules!$A$13,Modules!$B$13)</f>
@@ -19806,11 +19808,11 @@
       </c>
       <c r="H303" s="10"/>
       <c r="I303" s="10" t="str">
-        <f>CONCATENATE(A303, B303,C303,D303,E303,F303,G303,H303)</f>
+        <f t="shared" si="8"/>
         <v>statYLab55to74Avg</v>
       </c>
       <c r="J303" s="10" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="K303" s="6" t="s">
         <v>828</v>
@@ -19819,7 +19821,7 @@
         <v>1019</v>
       </c>
       <c r="M303" s="10" t="str">
-        <f>IF(OR(O303&lt;&gt;"", Q303&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R303" s="4" t="s">
@@ -19851,11 +19853,11 @@
       </c>
       <c r="H304" s="10"/>
       <c r="I304" s="10" t="str">
-        <f>CONCATENATE(A304, B304,C304,D304,E304,F304,G304,H304)</f>
+        <f t="shared" si="8"/>
         <v>statYMktNatGini</v>
       </c>
       <c r="J304" s="10" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="K304" s="2" t="s">
         <v>1227</v>
@@ -19864,7 +19866,7 @@
         <v>1024</v>
       </c>
       <c r="M304" s="10" t="str">
-        <f>IF(OR(O304&lt;&gt;"", Q304&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R304" s="4" t="s">
@@ -19877,7 +19879,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="305" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="10"/>
       <c r="B305" s="10" t="str" cm="1">
         <f t="array" ref="B305">_xlfn.IFS(S305 = Modules!$A$2,Modules!$B$2,S305 = Modules!$A$3,Modules!$B$3,S305 = Modules!$A$4,Modules!$B$4,S305 = Modules!$A$5,Modules!$B$5,S305 = Modules!$A$6,Modules!$B$6,S305 = Modules!$A$7,Modules!$B$7,S305 = Modules!$A$8,Modules!$B$8,S305 = Modules!$A$9,Modules!$B$9,S305 = Modules!$A$10,Modules!$B$10,S305 = Modules!$A$11,Modules!$B$11,S305 = Modules!$A$12,Modules!$B$12, S305 = Modules!$A$13,Modules!$B$13)</f>
@@ -19898,11 +19900,11 @@
       </c>
       <c r="H305" s="10"/>
       <c r="I305" s="10" t="str">
-        <f>CONCATENATE(A305, B305,C305,D305,E305,F305,G305,H305)</f>
+        <f t="shared" si="8"/>
         <v>statYPens18to29Avg</v>
       </c>
       <c r="J305" s="10" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="K305" s="6" t="s">
         <v>829</v>
@@ -19911,7 +19913,7 @@
         <v>1019</v>
       </c>
       <c r="M305" s="10" t="str">
-        <f>IF(OR(O305&lt;&gt;"", Q305&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R305" s="4" t="s">
@@ -19945,11 +19947,11 @@
       </c>
       <c r="H306" s="10"/>
       <c r="I306" s="10" t="str">
-        <f>CONCATENATE(A306, B306,C306,D306,E306,F306,G306,H306)</f>
+        <f t="shared" si="8"/>
         <v>statYPens30to54Avg</v>
       </c>
       <c r="J306" s="10" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="K306" s="6" t="s">
         <v>830</v>
@@ -19958,7 +19960,7 @@
         <v>1019</v>
       </c>
       <c r="M306" s="10" t="str">
-        <f>IF(OR(O306&lt;&gt;"", Q306&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R306" s="4" t="s">
@@ -19992,11 +19994,11 @@
       </c>
       <c r="H307" s="10"/>
       <c r="I307" s="10" t="str">
-        <f>CONCATENATE(A307, B307,C307,D307,E307,F307,G307,H307)</f>
+        <f t="shared" si="8"/>
         <v>statYPens55to74Avg</v>
       </c>
       <c r="J307" s="10" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="K307" s="6" t="s">
         <v>831</v>
@@ -20005,7 +20007,7 @@
         <v>1019</v>
       </c>
       <c r="M307" s="10" t="str">
-        <f>IF(OR(O307&lt;&gt;"", Q307&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R307" s="4" t="s">
@@ -20035,11 +20037,11 @@
       </c>
       <c r="H308" s="10"/>
       <c r="I308" s="10" t="str">
-        <f>CONCATENATE(A308, B308,C308,D308,E308,F308,G308,H308)</f>
+        <f t="shared" si="8"/>
         <v>wealth18to29Avg</v>
       </c>
       <c r="J308" s="10" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="K308" s="6" t="s">
         <v>841</v>
@@ -20048,7 +20050,7 @@
         <v>1019</v>
       </c>
       <c r="M308" s="10" t="str">
-        <f>IF(OR(O308&lt;&gt;"", Q308&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R308" s="4" t="s">
@@ -20078,11 +20080,11 @@
       </c>
       <c r="H309" s="10"/>
       <c r="I309" s="10" t="str">
-        <f>CONCATENATE(A309, B309,C309,D309,E309,F309,G309,H309)</f>
+        <f t="shared" si="8"/>
         <v>wealth30to54Avg</v>
       </c>
       <c r="J309" s="10" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="K309" s="6" t="s">
         <v>842</v>
@@ -20091,7 +20093,7 @@
         <v>1019</v>
       </c>
       <c r="M309" s="10" t="str">
-        <f>IF(OR(O309&lt;&gt;"", Q309&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R309" s="4" t="s">
@@ -20121,11 +20123,11 @@
       </c>
       <c r="H310" s="10"/>
       <c r="I310" s="10" t="str">
-        <f>CONCATENATE(A310, B310,C310,D310,E310,F310,G310,H310)</f>
+        <f t="shared" si="8"/>
         <v>wealth55to74Avg</v>
       </c>
       <c r="J310" s="10" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="K310" s="6" t="s">
         <v>843</v>
@@ -20134,7 +20136,7 @@
         <v>1019</v>
       </c>
       <c r="M310" s="10" t="str">
-        <f>IF(OR(O310&lt;&gt;"", Q310&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="R310" s="4" t="s">
@@ -20159,11 +20161,11 @@
         <v>1161</v>
       </c>
       <c r="I311" s="10" t="str">
-        <f>CONCATENATE(A311, B311,C311,D311,E311,F311,G311,H311)</f>
+        <f t="shared" si="8"/>
         <v>wealthLiqValue</v>
       </c>
       <c r="J311" s="10" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="K311" s="2" t="s">
         <v>717</v>
@@ -20172,7 +20174,7 @@
         <v>449</v>
       </c>
       <c r="M311" s="10" t="str">
-        <f>IF(OR(O311&lt;&gt;"", Q311&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S311" s="2" t="s">
@@ -20197,11 +20199,11 @@
         <v>1161</v>
       </c>
       <c r="I312" s="10" t="str">
-        <f>CONCATENATE(A312, B312,C312,D312,E312,F312,G312,H312)</f>
+        <f t="shared" si="8"/>
         <v>wealthMortgageDebtValue</v>
       </c>
       <c r="J312" s="10" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="K312" s="2" t="s">
         <v>1440</v>
@@ -20210,7 +20212,7 @@
         <v>449</v>
       </c>
       <c r="M312" s="10" t="str">
-        <f>IF(OR(O312&lt;&gt;"", Q312&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N312" s="2" t="s">
@@ -20238,11 +20240,11 @@
         <v>1161</v>
       </c>
       <c r="I313" s="10" t="str">
-        <f>CONCATENATE(A313, B313,C313,D313,E313,F313,G313,H313)</f>
+        <f t="shared" si="8"/>
         <v>wealthPensValue</v>
       </c>
       <c r="J313" s="10" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="K313" s="2" t="s">
         <v>669</v>
@@ -20251,7 +20253,7 @@
         <v>449</v>
       </c>
       <c r="M313" s="10" t="str">
-        <f>IF(OR(O313&lt;&gt;"", Q313&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S313" s="2" t="s">
@@ -20276,11 +20278,11 @@
         <v>1161</v>
       </c>
       <c r="I314" s="10" t="str">
-        <f>CONCATENATE(A314, B314,C314,D314,E314,F314,G314,H314)</f>
+        <f t="shared" si="8"/>
         <v>wealthPensValue</v>
       </c>
       <c r="J314" s="10" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="K314" s="2" t="s">
         <v>1429</v>
@@ -20289,7 +20291,7 @@
         <v>449</v>
       </c>
       <c r="M314" s="10" t="str">
-        <f>IF(OR(O314&lt;&gt;"", Q314&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N314" s="2" t="s">
@@ -20317,7 +20319,7 @@
         <v>968</v>
       </c>
       <c r="I315" s="10" t="str">
-        <f>CONCATENATE(A315, B315,C315,D315,E315,F315,G315,H315)</f>
+        <f t="shared" si="8"/>
         <v>wealthPrptyFlag</v>
       </c>
       <c r="J315" s="10" t="s">
@@ -20330,7 +20332,7 @@
         <v>333</v>
       </c>
       <c r="M315" s="10" t="str">
-        <f>IF(OR(O315&lt;&gt;"", Q315&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N315" s="2" t="s">
@@ -20369,7 +20371,7 @@
       </c>
       <c r="H316" s="10"/>
       <c r="I316" s="10" t="str">
-        <f>CONCATENATE(A316, B316,C316,D316,E316,F316,G316,H316)</f>
+        <f t="shared" si="8"/>
         <v>wealthPrptyFlag</v>
       </c>
       <c r="J316" s="10" t="s">
@@ -20382,7 +20384,7 @@
         <v>449</v>
       </c>
       <c r="M316" s="10" t="str">
-        <f>IF(OR(O316&lt;&gt;"", Q316&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S316" s="2" t="s">
@@ -20404,11 +20406,11 @@
         <v>1161</v>
       </c>
       <c r="I317" s="10" t="str">
-        <f>CONCATENATE(A317, B317,C317,D317,E317,F317,G317,H317)</f>
+        <f t="shared" si="8"/>
         <v>wealthPrptyValue</v>
       </c>
       <c r="J317" s="10" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="K317" s="2" t="s">
         <v>1435</v>
@@ -20417,7 +20419,7 @@
         <v>449</v>
       </c>
       <c r="M317" s="10" t="str">
-        <f>IF(OR(O317&lt;&gt;"", Q317&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N317" s="2" t="s">
@@ -20445,11 +20447,11 @@
         <v>1161</v>
       </c>
       <c r="I318" s="10" t="str">
-        <f>CONCATENATE(A318, B318,C318,D318,E318,F318,G318,H318)</f>
+        <f t="shared" si="8"/>
         <v>wealthPrptyValue</v>
       </c>
       <c r="J318" s="10" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="K318" s="2" t="s">
         <v>889</v>
@@ -20458,7 +20460,7 @@
         <v>449</v>
       </c>
       <c r="M318" s="10" t="str">
-        <f>IF(OR(O318&lt;&gt;"", Q318&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S318" s="2" t="s">
@@ -20471,7 +20473,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="319" spans="1:22" ht="64" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="B319" s="10" t="str" cm="1">
         <f t="array" ref="B319">_xlfn.IFS(S319 = Modules!$A$2,Modules!$B$2,S319 = Modules!$A$3,Modules!$B$3,S319 = Modules!$A$4,Modules!$B$4,S319 = Modules!$A$5,Modules!$B$5,S319 = Modules!$A$6,Modules!$B$6,S319 = Modules!$A$7,Modules!$B$7,S319 = Modules!$A$8,Modules!$B$8,S319 = Modules!$A$9,Modules!$B$9,S319 = Modules!$A$10,Modules!$B$10,S319 = Modules!$A$11,Modules!$B$11,S319 = Modules!$A$12,Modules!$B$12, S319 = Modules!$A$13,Modules!$B$13)</f>
         <v>wealth</v>
@@ -20483,11 +20485,11 @@
         <v>1161</v>
       </c>
       <c r="I319" s="10" t="str">
-        <f>CONCATENATE(A319, B319,C319,D319,E319,F319,G319,H319)</f>
+        <f t="shared" si="8"/>
         <v>wealthTotValue</v>
       </c>
       <c r="J319" s="10" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="K319" s="2" t="s">
         <v>1433</v>
@@ -20496,7 +20498,7 @@
         <v>449</v>
       </c>
       <c r="M319" s="10" t="str">
-        <f>IF(OR(O319&lt;&gt;"", Q319&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N319" s="2" t="s">
@@ -20515,7 +20517,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="320" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="10"/>
       <c r="B320" s="10" t="str" cm="1">
         <f t="array" ref="B320">_xlfn.IFS(S320 = Modules!$A$2,Modules!$B$2,S320 = Modules!$A$3,Modules!$B$3,S320 = Modules!$A$4,Modules!$B$4,S320 = Modules!$A$5,Modules!$B$5,S320 = Modules!$A$6,Modules!$B$6,S320 = Modules!$A$7,Modules!$B$7,S320 = Modules!$A$8,Modules!$B$8,S320 = Modules!$A$9,Modules!$B$9,S320 = Modules!$A$10,Modules!$B$10,S320 = Modules!$A$11,Modules!$B$11,S320 = Modules!$A$12,Modules!$B$12, S320 = Modules!$A$13,Modules!$B$13)</f>
@@ -20528,7 +20530,7 @@
       <c r="G320" s="10"/>
       <c r="H320" s="10"/>
       <c r="I320" s="10" t="str">
-        <f>CONCATENATE(A320, B320,C320,D320,E320,F320,G320,H320)</f>
+        <f t="shared" si="8"/>
         <v>wgt</v>
       </c>
       <c r="J320" s="10" t="s">
@@ -20541,7 +20543,7 @@
         <v>333</v>
       </c>
       <c r="M320" s="10" t="str">
-        <f>IF(OR(O320&lt;&gt;"", Q320&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="S320" s="2" t="s">
@@ -20551,7 +20553,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="321" spans="1:22" ht="96" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B321" s="10" t="str" cm="1">
         <f t="array" ref="B321">_xlfn.IFS(S321 = Modules!$A$2,Modules!$B$2,S321 = Modules!$A$3,Modules!$B$3,S321 = Modules!$A$4,Modules!$B$4,S321 = Modules!$A$5,Modules!$B$5,S321 = Modules!$A$6,Modules!$B$6,S321 = Modules!$A$7,Modules!$B$7,S321 = Modules!$A$8,Modules!$B$8,S321 = Modules!$A$9,Modules!$B$9,S321 = Modules!$A$10,Modules!$B$10,S321 = Modules!$A$11,Modules!$B$11,S321 = Modules!$A$12,Modules!$B$12, S321 = Modules!$A$13,Modules!$B$13)</f>
         <v>wgt</v>
@@ -20563,7 +20565,7 @@
         <v>1114</v>
       </c>
       <c r="I321" s="10" t="str">
-        <f>CONCATENATE(A321, B321,C321,D321,E321,F321,G321,H321)</f>
+        <f t="shared" si="8"/>
         <v>wgtCrossMainSurvey</v>
       </c>
       <c r="J321" s="10" t="s">
@@ -20576,7 +20578,7 @@
         <v>170</v>
       </c>
       <c r="M321" s="10" t="str">
-        <f>IF(OR(O321&lt;&gt;"", Q321&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="N321" s="2" t="s">
@@ -20601,7 +20603,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="322" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B322" s="10" t="str" cm="1">
         <f t="array" ref="B322">_xlfn.IFS(S322 = Modules!$A$2,Modules!$B$2,S322 = Modules!$A$3,Modules!$B$3,S322 = Modules!$A$4,Modules!$B$4,S322 = Modules!$A$5,Modules!$B$5,S322 = Modules!$A$6,Modules!$B$6,S322 = Modules!$A$7,Modules!$B$7,S322 = Modules!$A$8,Modules!$B$8,S322 = Modules!$A$9,Modules!$B$9,S322 = Modules!$A$10,Modules!$B$10,S322 = Modules!$A$11,Modules!$B$11,S322 = Modules!$A$12,Modules!$B$12, S322 = Modules!$A$13,Modules!$B$13)</f>
         <v>wgt</v>
@@ -20613,7 +20615,7 @@
         <v>1108</v>
       </c>
       <c r="I322" s="10" t="str">
-        <f>CONCATENATE(A322, B322,C322,D322,E322,F322,G322,H322)</f>
+        <f t="shared" ref="I322:I385" si="10">CONCATENATE(A322, B322,C322,D322,E322,F322,G322,H322)</f>
         <v>wgtHhCross</v>
       </c>
       <c r="J322" s="10" t="s">
@@ -20626,7 +20628,7 @@
         <v>170</v>
       </c>
       <c r="M322" s="10" t="str">
-        <f>IF(OR(O322&lt;&gt;"", Q322&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M322:M385" si="11">IF(OR(O322&lt;&gt;"", Q322&lt;&gt;""),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="N322" s="2" t="s">
@@ -20667,7 +20669,7 @@
       <c r="G323" s="10"/>
       <c r="H323" s="10"/>
       <c r="I323" s="10" t="str">
-        <f>CONCATENATE(A323, B323,C323,D323,E323,F323,G323,H323)</f>
+        <f t="shared" si="10"/>
         <v>wgtHhCross</v>
       </c>
       <c r="J323" s="10" t="s">
@@ -20680,7 +20682,7 @@
         <v>170</v>
       </c>
       <c r="M323" s="10" t="str">
-        <f>IF(OR(O323&lt;&gt;"", Q323&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N323" s="2" t="s">
@@ -20714,7 +20716,7 @@
         <v>1108</v>
       </c>
       <c r="I324" s="10" t="str">
-        <f>CONCATENATE(A324, B324,C324,D324,E324,F324,G324,H324)</f>
+        <f t="shared" si="10"/>
         <v>wgtHhCross</v>
       </c>
       <c r="J324" s="10" t="s">
@@ -20727,7 +20729,7 @@
         <v>170</v>
       </c>
       <c r="M324" s="10" t="str">
-        <f>IF(OR(O324&lt;&gt;"", Q324&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N324" s="2" t="s">
@@ -20761,7 +20763,7 @@
         <v>1114</v>
       </c>
       <c r="I325" s="10" t="str">
-        <f>CONCATENATE(A325, B325,C325,D325,E325,F325,G325,H325)</f>
+        <f t="shared" si="10"/>
         <v>wgtLongMainSurvey</v>
       </c>
       <c r="J325" s="10" t="s">
@@ -20774,7 +20776,7 @@
         <v>170</v>
       </c>
       <c r="M325" s="10" t="str">
-        <f>IF(OR(O325&lt;&gt;"", Q325&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N325" s="4" t="s">
@@ -20811,7 +20813,7 @@
         <v>1115</v>
       </c>
       <c r="I326" s="10" t="str">
-        <f>CONCATENATE(A326, B326,C326,D326,E326,F326,G326,H326)</f>
+        <f t="shared" si="10"/>
         <v>wgtLongSelfCompletion</v>
       </c>
       <c r="J326" s="10" t="s">
@@ -20824,7 +20826,7 @@
         <v>170</v>
       </c>
       <c r="M326" s="10" t="str">
-        <f>IF(OR(O326&lt;&gt;"", Q326&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N326" s="2" t="s">
@@ -20862,7 +20864,7 @@
       </c>
       <c r="H327" s="10"/>
       <c r="I327" s="10" t="str">
-        <f>CONCATENATE(A327, B327,C327,D327,E327,F327,G327,H327)</f>
+        <f t="shared" si="10"/>
         <v>x18to29Avg</v>
       </c>
       <c r="J327" s="10" t="s">
@@ -20875,7 +20877,7 @@
         <v>1019</v>
       </c>
       <c r="M327" s="10" t="str">
-        <f>IF(OR(O327&lt;&gt;"", Q327&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R327" s="4" t="s">
@@ -20905,7 +20907,7 @@
       </c>
       <c r="H328" s="10"/>
       <c r="I328" s="10" t="str">
-        <f>CONCATENATE(A328, B328,C328,D328,E328,F328,G328,H328)</f>
+        <f t="shared" si="10"/>
         <v>x18to54Avg</v>
       </c>
       <c r="J328" s="10" t="s">
@@ -20918,7 +20920,7 @@
         <v>1019</v>
       </c>
       <c r="M328" s="10" t="str">
-        <f>IF(OR(O328&lt;&gt;"", Q328&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R328" s="4" t="s">
@@ -20948,7 +20950,7 @@
       </c>
       <c r="H329" s="10"/>
       <c r="I329" s="10" t="str">
-        <f>CONCATENATE(A329, B329,C329,D329,E329,F329,G329,H329)</f>
+        <f t="shared" si="10"/>
         <v>x30to54Avg</v>
       </c>
       <c r="J329" s="10" t="s">
@@ -20961,7 +20963,7 @@
         <v>1019</v>
       </c>
       <c r="M329" s="10" t="str">
-        <f>IF(OR(O329&lt;&gt;"", Q329&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R329" s="4" t="s">
@@ -20991,7 +20993,7 @@
       </c>
       <c r="H330" s="10"/>
       <c r="I330" s="10" t="str">
-        <f>CONCATENATE(A330, B330,C330,D330,E330,F330,G330,H330)</f>
+        <f t="shared" si="10"/>
         <v>x55to74Avg</v>
       </c>
       <c r="J330" s="10" t="s">
@@ -21004,7 +21006,7 @@
         <v>1019</v>
       </c>
       <c r="M330" s="10" t="str">
-        <f>IF(OR(O330&lt;&gt;"", Q330&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R330" s="4" t="s">
@@ -21036,7 +21038,7 @@
         <v>1002</v>
       </c>
       <c r="I331" s="10" t="str">
-        <f>CONCATENATE(A331, B331,C331,D331,E331,F331,G331,H331)</f>
+        <f t="shared" si="10"/>
         <v>xCareFormalWeek</v>
       </c>
       <c r="J331" s="10" t="s">
@@ -21049,7 +21051,7 @@
         <v>333</v>
       </c>
       <c r="M331" s="10" t="str">
-        <f>IF(OR(O331&lt;&gt;"", Q331&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S331" s="2" t="s">
@@ -21076,11 +21078,11 @@
         <v>1002</v>
       </c>
       <c r="I332" s="10" t="str">
-        <f>CONCATENATE(A332, B332,C332,D332,E332,F332,G332,H332)</f>
+        <f t="shared" si="10"/>
         <v>xCareWeek</v>
       </c>
       <c r="J332" s="10" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="K332" s="2" t="s">
         <v>725</v>
@@ -21089,7 +21091,7 @@
         <v>449</v>
       </c>
       <c r="M332" s="10" t="str">
-        <f>IF(OR(O332&lt;&gt;"", Q332&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S332" s="2" t="s">
@@ -21111,7 +21113,7 @@
         <v>1002</v>
       </c>
       <c r="I333" s="10" t="str">
-        <f>CONCATENATE(A333, B333,C333,D333,E333,F333,G333,H333)</f>
+        <f t="shared" si="10"/>
         <v>xChildCareWeek</v>
       </c>
       <c r="J333" s="10" t="s">
@@ -21124,7 +21126,7 @@
         <v>449</v>
       </c>
       <c r="M333" s="10" t="str">
-        <f>IF(OR(O333&lt;&gt;"", Q333&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S333" s="2" t="s">
@@ -21146,7 +21148,7 @@
         <v>697</v>
       </c>
       <c r="I334" s="10" t="str">
-        <f>CONCATENATE(A334, B334,C334,D334,E334,F334,G334,H334)</f>
+        <f t="shared" si="10"/>
         <v>xDiscretionaryYear</v>
       </c>
       <c r="J334" s="10" t="s">
@@ -21159,7 +21161,7 @@
         <v>449</v>
       </c>
       <c r="M334" s="10" t="str">
-        <f>IF(OR(O334&lt;&gt;"", Q334&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S334" s="2" t="s">
@@ -21181,11 +21183,11 @@
         <v>697</v>
       </c>
       <c r="I335" s="10" t="str">
-        <f>CONCATENATE(A335, B335,C335,D335,E335,F335,G335,H335)</f>
+        <f t="shared" si="10"/>
         <v>xEquivYear</v>
       </c>
       <c r="J335" s="10" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="K335" s="2" t="s">
         <v>781</v>
@@ -21194,7 +21196,7 @@
         <v>333</v>
       </c>
       <c r="M335" s="10" t="str">
-        <f>IF(OR(O335&lt;&gt;"", Q335&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S335" s="2" t="s">
@@ -21216,11 +21218,11 @@
         <v>1137</v>
       </c>
       <c r="I336" s="10" t="str">
-        <f>CONCATENATE(A336, B336,C336,D336,E336,F336,G336,H336)</f>
+        <f t="shared" si="10"/>
         <v>xEquivYearL1</v>
       </c>
       <c r="J336" s="10" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="K336" s="2" t="s">
         <v>782</v>
@@ -21229,7 +21231,7 @@
         <v>333</v>
       </c>
       <c r="M336" s="10" t="str">
-        <f>IF(OR(O336&lt;&gt;"", Q336&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S336" s="2" t="s">
@@ -21256,7 +21258,7 @@
       </c>
       <c r="H337" s="10"/>
       <c r="I337" s="10" t="str">
-        <f>CONCATENATE(A337, B337,C337,D337,E337,F337,G337,H337)</f>
+        <f t="shared" si="10"/>
         <v>xToLeisureRatio</v>
       </c>
       <c r="J337" s="10" t="s">
@@ -21269,7 +21271,7 @@
         <v>1019</v>
       </c>
       <c r="M337" s="10" t="str">
-        <f>IF(OR(O337&lt;&gt;"", Q337&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R337" s="4" t="s">
@@ -21297,7 +21299,7 @@
         <v>1056</v>
       </c>
       <c r="I338" s="10" t="str">
-        <f>CONCATENATE(A338, B338,C338,D338,E338,F338,G338,H338)</f>
+        <f t="shared" si="10"/>
         <v>yBenAmountMonth</v>
       </c>
       <c r="J338" s="10" t="s">
@@ -21310,7 +21312,7 @@
         <v>449</v>
       </c>
       <c r="M338" s="10" t="str">
-        <f>IF(OR(O338&lt;&gt;"", Q338&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S338" s="2" t="s">
@@ -21338,11 +21340,11 @@
         <v>968</v>
       </c>
       <c r="I339" s="10" t="str">
-        <f>CONCATENATE(A339, B339,C339,D339,E339,F339,G339,H339)</f>
+        <f t="shared" si="10"/>
         <v>yBenLegacyReceivedFlag</v>
       </c>
       <c r="J339" s="10" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="K339" s="6" t="s">
         <v>890</v>
@@ -21351,7 +21353,7 @@
         <v>449</v>
       </c>
       <c r="M339" s="10" t="str">
-        <f>IF(OR(O339&lt;&gt;"", Q339&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S339" s="2" t="s">
@@ -21381,7 +21383,7 @@
         <v>968</v>
       </c>
       <c r="I340" s="10" t="str">
-        <f>CONCATENATE(A340, B340,C340,D340,E340,F340,G340,H340)</f>
+        <f t="shared" si="10"/>
         <v>yBenNonUCReceivedFlag</v>
       </c>
       <c r="J340" s="10" t="s">
@@ -21394,7 +21396,7 @@
         <v>333</v>
       </c>
       <c r="M340" s="10" t="str">
-        <f>IF(OR(O340&lt;&gt;"", Q340&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N340" s="2" t="s">
@@ -21428,7 +21430,7 @@
         <v>968</v>
       </c>
       <c r="I341" s="10" t="str">
-        <f>CONCATENATE(A341, B341,C341,D341,E341,F341,G341,H341)</f>
+        <f t="shared" si="10"/>
         <v>yBenNonUCReceivedFlag</v>
       </c>
       <c r="J341" s="10" t="s">
@@ -21441,7 +21443,7 @@
         <v>333</v>
       </c>
       <c r="M341" s="10" t="str">
-        <f>IF(OR(O341&lt;&gt;"", Q341&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S341" s="2" t="s">
@@ -21475,11 +21477,11 @@
         <v>1050</v>
       </c>
       <c r="I342" s="10" t="str">
-        <f>CONCATENATE(A342, B342,C342,D342,E342,F342,G342,H342)</f>
+        <f t="shared" si="10"/>
         <v>yBenNonUCReceivedFlagL1</v>
       </c>
       <c r="J342" s="10" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="K342" s="2" t="s">
         <v>776</v>
@@ -21488,7 +21490,7 @@
         <v>333</v>
       </c>
       <c r="M342" s="10" t="str">
-        <f>IF(OR(O342&lt;&gt;"", Q342&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S342" s="2" t="s">
@@ -21513,7 +21515,7 @@
         <v>968</v>
       </c>
       <c r="I343" s="10" t="str">
-        <f>CONCATENATE(A343, B343,C343,D343,E343,F343,G343,H343)</f>
+        <f t="shared" si="10"/>
         <v>yBenReceivedFlag</v>
       </c>
       <c r="J343" s="10" t="s">
@@ -21526,7 +21528,7 @@
         <v>333</v>
       </c>
       <c r="M343" s="10" t="str">
-        <f>IF(OR(O343&lt;&gt;"", Q343&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N343" s="2" t="s">
@@ -21560,7 +21562,7 @@
         <v>968</v>
       </c>
       <c r="I344" s="10" t="str">
-        <f>CONCATENATE(A344, B344,C344,D344,E344,F344,G344,H344)</f>
+        <f t="shared" si="10"/>
         <v>yBenReceivedFlag</v>
       </c>
       <c r="J344" s="10" t="s">
@@ -21573,7 +21575,7 @@
         <v>333</v>
       </c>
       <c r="M344" s="10" t="str">
-        <f>IF(OR(O344&lt;&gt;"", Q344&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S344" s="2" t="s">
@@ -21604,11 +21606,11 @@
         <v>1050</v>
       </c>
       <c r="I345" s="10" t="str">
-        <f>CONCATENATE(A345, B345,C345,D345,E345,F345,G345,H345)</f>
+        <f t="shared" si="10"/>
         <v>yBenReceivedFlagL1</v>
       </c>
       <c r="J345" s="10" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="K345" s="2" t="s">
         <v>775</v>
@@ -21617,7 +21619,7 @@
         <v>333</v>
       </c>
       <c r="M345" s="10" t="str">
-        <f>IF(OR(O345&lt;&gt;"", Q345&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S345" s="2" t="s">
@@ -21646,7 +21648,7 @@
         <v>968</v>
       </c>
       <c r="I346" s="10" t="str">
-        <f>CONCATENATE(A346, B346,C346,D346,E346,F346,G346,H346)</f>
+        <f t="shared" si="10"/>
         <v>yBenUCReceivedFlag</v>
       </c>
       <c r="J346" s="10" t="s">
@@ -21659,7 +21661,7 @@
         <v>333</v>
       </c>
       <c r="M346" s="10" t="str">
-        <f>IF(OR(O346&lt;&gt;"", Q346&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N346" s="2" t="s">
@@ -21693,7 +21695,7 @@
         <v>968</v>
       </c>
       <c r="I347" s="10" t="str">
-        <f>CONCATENATE(A347, B347,C347,D347,E347,F347,G347,H347)</f>
+        <f t="shared" si="10"/>
         <v>yBenUCReceivedFlag</v>
       </c>
       <c r="J347" s="10" t="s">
@@ -21706,7 +21708,7 @@
         <v>449</v>
       </c>
       <c r="M347" s="10" t="str">
-        <f>IF(OR(O347&lt;&gt;"", Q347&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S347" s="2" t="s">
@@ -21737,7 +21739,7 @@
         <v>968</v>
       </c>
       <c r="I348" s="10" t="str">
-        <f>CONCATENATE(A348, B348,C348,D348,E348,F348,G348,H348)</f>
+        <f t="shared" si="10"/>
         <v>yBenUCReceivedFlag</v>
       </c>
       <c r="J348" s="10" t="s">
@@ -21750,7 +21752,7 @@
         <v>333</v>
       </c>
       <c r="M348" s="10" t="str">
-        <f>IF(OR(O348&lt;&gt;"", Q348&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S348" s="2" t="s">
@@ -21784,11 +21786,11 @@
         <v>1050</v>
       </c>
       <c r="I349" s="10" t="str">
-        <f>CONCATENATE(A349, B349,C349,D349,E349,F349,G349,H349)</f>
+        <f t="shared" si="10"/>
         <v>yBenUCReceivedFlagL1</v>
       </c>
       <c r="J349" s="10" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="K349" s="2" t="s">
         <v>777</v>
@@ -21797,7 +21799,7 @@
         <v>333</v>
       </c>
       <c r="M349" s="10" t="str">
-        <f>IF(OR(O349&lt;&gt;"", Q349&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S349" s="2" t="s">
@@ -21822,11 +21824,11 @@
         <v>1056</v>
       </c>
       <c r="I350" s="10" t="str">
-        <f>CONCATENATE(A350, B350,C350,D350,E350,F350,G350,H350)</f>
+        <f t="shared" si="10"/>
         <v>yCapitalPersMonth</v>
       </c>
       <c r="J350" s="10" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="K350" s="2" t="s">
         <v>1366</v>
@@ -21835,7 +21837,7 @@
         <v>333</v>
       </c>
       <c r="M350" s="10" t="str">
-        <f>IF(OR(O350&lt;&gt;"", Q350&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N350" s="2" t="s">
@@ -21872,11 +21874,11 @@
         <v>1367</v>
       </c>
       <c r="I351" s="10" t="str">
-        <f>CONCATENATE(A351, B351,C351,D351,E351,F351,G351,H351)</f>
+        <f t="shared" si="10"/>
         <v>yCapitalPersMonthL1</v>
       </c>
       <c r="J351" s="10" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="K351" s="2" t="s">
         <v>388</v>
@@ -21885,7 +21887,7 @@
         <v>333</v>
       </c>
       <c r="M351" s="10" t="str">
-        <f>IF(OR(O351&lt;&gt;"", Q351&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S351" s="2" t="s">
@@ -21910,11 +21912,11 @@
         <v>1368</v>
       </c>
       <c r="I352" s="10" t="str">
-        <f>CONCATENATE(A352, B352,C352,D352,E352,F352,G352,H352)</f>
+        <f t="shared" si="10"/>
         <v>yCapitalPersMonthL2</v>
       </c>
       <c r="J352" s="10" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="K352" s="2" t="s">
         <v>493</v>
@@ -21923,7 +21925,7 @@
         <v>333</v>
       </c>
       <c r="M352" s="10" t="str">
-        <f>IF(OR(O352&lt;&gt;"", Q352&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S352" s="2" t="s">
@@ -21948,11 +21950,11 @@
         <v>1412</v>
       </c>
       <c r="I353" s="10" t="str">
-        <f>CONCATENATE(A353, B353,C353,D353,E353,F353,G353,H353)</f>
+        <f t="shared" si="10"/>
         <v>yDiffDispEquivPrevYear</v>
       </c>
       <c r="J353" s="10" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="K353" s="2" t="s">
         <v>1409</v>
@@ -21961,7 +21963,7 @@
         <v>449</v>
       </c>
       <c r="M353" s="10" t="str">
-        <f>IF(OR(O353&lt;&gt;"", Q353&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S353" s="2" t="s">
@@ -21987,7 +21989,7 @@
         <v>697</v>
       </c>
       <c r="I354" s="10" t="str">
-        <f>CONCATENATE(A354, B354,C354,D354,E354,F354,G354,H354)</f>
+        <f t="shared" si="10"/>
         <v>yDispEquivYear</v>
       </c>
       <c r="J354" s="10" t="s">
@@ -22000,7 +22002,7 @@
         <v>449</v>
       </c>
       <c r="M354" s="10" t="str">
-        <f>IF(OR(O354&lt;&gt;"", Q354&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S354" s="2" t="s">
@@ -22022,7 +22024,7 @@
         <v>697</v>
       </c>
       <c r="I355" s="10" t="str">
-        <f>CONCATENATE(A355, B355,C355,D355,E355,F355,G355,H355)</f>
+        <f t="shared" si="10"/>
         <v>yDispEquivYear</v>
       </c>
       <c r="J355" s="10" t="s">
@@ -22035,7 +22037,7 @@
         <v>333</v>
       </c>
       <c r="M355" s="10" t="str">
-        <f>IF(OR(O355&lt;&gt;"", Q355&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S355" s="2" t="s">
@@ -22061,7 +22063,7 @@
         <v>1137</v>
       </c>
       <c r="I356" s="10" t="str">
-        <f>CONCATENATE(A356, B356,C356,D356,E356,F356,G356,H356)</f>
+        <f t="shared" si="10"/>
         <v>yDispEquivYearL1</v>
       </c>
       <c r="J356" s="10" t="s">
@@ -22074,7 +22076,7 @@
         <v>449</v>
       </c>
       <c r="M356" s="10" t="str">
-        <f>IF(OR(O356&lt;&gt;"", Q356&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S356" s="2" t="s">
@@ -22101,7 +22103,7 @@
         <v>1056</v>
       </c>
       <c r="I357" s="10" t="str">
-        <f>CONCATENATE(A357, B357,C357,D357,E357,F357,G357,H357)</f>
+        <f t="shared" si="10"/>
         <v>yDispMonth</v>
       </c>
       <c r="J357" s="10" t="s">
@@ -22114,7 +22116,7 @@
         <v>170</v>
       </c>
       <c r="M357" s="10" t="str">
-        <f>IF(OR(O357&lt;&gt;"", Q357&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N357" s="2" t="s">
@@ -22147,7 +22149,7 @@
         <v>1056</v>
       </c>
       <c r="I358" s="10" t="str">
-        <f>CONCATENATE(A358, B358,C358,D358,E358,F358,G358,H358)</f>
+        <f t="shared" si="10"/>
         <v>yDispMonth</v>
       </c>
       <c r="J358" s="10" t="s">
@@ -22160,7 +22162,7 @@
         <v>449</v>
       </c>
       <c r="M358" s="10" t="str">
-        <f>IF(OR(O358&lt;&gt;"", Q358&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S358" s="2" t="s">
@@ -22170,7 +22172,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="359" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B359" s="10" t="str" cm="1">
         <f t="array" ref="B359">_xlfn.IFS(S359 = Modules!$A$2,Modules!$B$2,S359 = Modules!$A$3,Modules!$B$3,S359 = Modules!$A$4,Modules!$B$4,S359 = Modules!$A$5,Modules!$B$5,S359 = Modules!$A$6,Modules!$B$6,S359 = Modules!$A$7,Modules!$B$7,S359 = Modules!$A$8,Modules!$B$8,S359 = Modules!$A$9,Modules!$B$9,S359 = Modules!$A$10,Modules!$B$10,S359 = Modules!$A$11,Modules!$B$11,S359 = Modules!$A$12,Modules!$B$12, S359 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -22188,11 +22190,11 @@
         <v>1056</v>
       </c>
       <c r="I359" s="10" t="str">
-        <f>CONCATENATE(A359, B359,C359,D359,E359,F359,G359,H359)</f>
+        <f t="shared" si="10"/>
         <v>yEmpPersGrossMonth</v>
       </c>
       <c r="J359" s="10" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="K359" s="2" t="s">
         <v>1373</v>
@@ -22201,7 +22203,7 @@
         <v>333</v>
       </c>
       <c r="M359" s="10" t="str">
-        <f>IF(OR(O359&lt;&gt;"", Q359&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N359" s="2" t="s">
@@ -22244,11 +22246,11 @@
         <v>1367</v>
       </c>
       <c r="I360" s="10" t="str">
-        <f>CONCATENATE(A360, B360,C360,D360,E360,F360,G360,H360)</f>
+        <f t="shared" si="10"/>
         <v>yEmpPersGrossMonthL1</v>
       </c>
       <c r="J360" s="10" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="K360" s="2" t="s">
         <v>499</v>
@@ -22257,7 +22259,7 @@
         <v>333</v>
       </c>
       <c r="M360" s="10" t="str">
-        <f>IF(OR(O360&lt;&gt;"", Q360&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S360" s="2" t="s">
@@ -22285,11 +22287,11 @@
         <v>1368</v>
       </c>
       <c r="I361" s="10" t="str">
-        <f>CONCATENATE(A361, B361,C361,D361,E361,F361,G361,H361)</f>
+        <f t="shared" si="10"/>
         <v>yEmpPersGrossMonthL2</v>
       </c>
       <c r="J361" s="10" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="K361" s="2" t="s">
         <v>500</v>
@@ -22298,7 +22300,7 @@
         <v>333</v>
       </c>
       <c r="M361" s="10" t="str">
-        <f>IF(OR(O361&lt;&gt;"", Q361&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S361" s="2" t="s">
@@ -22326,11 +22328,11 @@
         <v>1371</v>
       </c>
       <c r="I362" s="10" t="str">
-        <f>CONCATENATE(A362, B362,C362,D362,E362,F362,G362,H362)</f>
+        <f t="shared" si="10"/>
         <v>yEmpPersGrossMonthL3</v>
       </c>
       <c r="J362" s="10" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="K362" s="2" t="s">
         <v>501</v>
@@ -22339,7 +22341,7 @@
         <v>333</v>
       </c>
       <c r="M362" s="10" t="str">
-        <f>IF(OR(O362&lt;&gt;"", Q362&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S362" s="2" t="s">
@@ -22366,7 +22368,7 @@
       </c>
       <c r="H363" s="10"/>
       <c r="I363" s="10" t="str">
-        <f>CONCATENATE(A363, B363,C363,D363,E363,F363,G363,H363)</f>
+        <f t="shared" si="10"/>
         <v>yFinDstrssFlag</v>
       </c>
       <c r="J363" s="10" t="s">
@@ -22379,7 +22381,7 @@
         <v>333</v>
       </c>
       <c r="M363" s="10" t="str">
-        <f>IF(OR(O363&lt;&gt;"", Q363&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N363" s="2" t="s">
@@ -22412,7 +22414,7 @@
       </c>
       <c r="H364" s="10"/>
       <c r="I364" s="10" t="str">
-        <f>CONCATENATE(A364, B364,C364,D364,E364,F364,G364,H364)</f>
+        <f t="shared" si="10"/>
         <v>yFinDstrssFlag</v>
       </c>
       <c r="J364" s="10" t="s">
@@ -22425,7 +22427,7 @@
         <v>333</v>
       </c>
       <c r="M364" s="10" t="str">
-        <f>IF(OR(O364&lt;&gt;"", Q364&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S364" s="2" t="s">
@@ -22455,11 +22457,11 @@
         <v>1056</v>
       </c>
       <c r="I365" s="10" t="str">
-        <f>CONCATENATE(A365, B365,C365,D365,E365,F365,G365,H365)</f>
+        <f t="shared" si="10"/>
         <v>yGrossMonth</v>
       </c>
       <c r="J365" s="10" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K365" s="2" t="s">
         <v>709</v>
@@ -22468,7 +22470,7 @@
         <v>449</v>
       </c>
       <c r="M365" s="10" t="str">
-        <f>IF(OR(O365&lt;&gt;"", Q365&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S365" s="2" t="s">
@@ -22493,11 +22495,11 @@
         <v>1092</v>
       </c>
       <c r="I366" s="10" t="str">
-        <f>CONCATENATE(A366, B366,C366,D366,E366,F366,G366,H366)</f>
+        <f t="shared" si="10"/>
         <v>yHhDispEquivP50</v>
       </c>
       <c r="J366" s="10" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="K366" s="2" t="s">
         <v>789</v>
@@ -22506,7 +22508,7 @@
         <v>1019</v>
       </c>
       <c r="M366" s="10" t="str">
-        <f>IF(OR(O366&lt;&gt;"", Q366&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R366" s="4" t="s">
@@ -22537,11 +22539,11 @@
         <v>1050</v>
       </c>
       <c r="I367" s="10" t="str">
-        <f>CONCATENATE(A367, B367,C367,D367,E367,F367,G367,H367)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesC5L1</v>
       </c>
       <c r="J367" s="10" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="K367" s="2" t="s">
         <v>635</v>
@@ -22550,7 +22552,7 @@
         <v>449</v>
       </c>
       <c r="M367" s="10" t="str">
-        <f>IF(OR(O367&lt;&gt;"", Q367&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S367" s="2" t="s">
@@ -22576,11 +22578,11 @@
         <v>1212</v>
       </c>
       <c r="I368" s="10" t="str">
-        <f>CONCATENATE(A368, B368,C368,D368,E368,F368,G368,H368)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesC5P20</v>
       </c>
       <c r="J368" s="10" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="K368" s="2" t="s">
         <v>1228</v>
@@ -22589,7 +22591,7 @@
         <v>1024</v>
       </c>
       <c r="M368" s="10" t="str">
-        <f>IF(OR(O368&lt;&gt;"", Q368&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R368" s="4" t="s">
@@ -22618,11 +22620,11 @@
         <v>1213</v>
       </c>
       <c r="I369" s="10" t="str">
-        <f>CONCATENATE(A369, B369,C369,D369,E369,F369,G369,H369)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesC5P40</v>
       </c>
       <c r="J369" s="10" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="K369" s="2" t="s">
         <v>1229</v>
@@ -22631,7 +22633,7 @@
         <v>1024</v>
       </c>
       <c r="M369" s="10" t="str">
-        <f>IF(OR(O369&lt;&gt;"", Q369&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R369" s="4" t="s">
@@ -22660,11 +22662,11 @@
         <v>1214</v>
       </c>
       <c r="I370" s="10" t="str">
-        <f>CONCATENATE(A370, B370,C370,D370,E370,F370,G370,H370)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesC5P80</v>
       </c>
       <c r="J370" s="10" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="K370" s="2" t="s">
         <v>1230</v>
@@ -22673,7 +22675,7 @@
         <v>1024</v>
       </c>
       <c r="M370" s="10" t="str">
-        <f>IF(OR(O370&lt;&gt;"", Q370&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R370" s="4" t="s">
@@ -22702,11 +22704,11 @@
         <v>1214</v>
       </c>
       <c r="I371" s="10" t="str">
-        <f>CONCATENATE(A371, B371,C371,D371,E371,F371,G371,H371)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesC5P80</v>
       </c>
       <c r="J371" s="10" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="K371" s="2" t="s">
         <v>1231</v>
@@ -22715,7 +22717,7 @@
         <v>1024</v>
       </c>
       <c r="M371" s="10" t="str">
-        <f>IF(OR(O371&lt;&gt;"", Q371&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R371" s="4" t="s">
@@ -22743,11 +22745,11 @@
         <v>1375</v>
       </c>
       <c r="I372" s="10" t="str">
-        <f>CONCATENATE(A372, B372,C372,D372,E372,F372,G372,H372)</f>
+        <f t="shared" si="10"/>
         <v>yHhQuintilesMonthC5</v>
       </c>
       <c r="J372" s="10" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="K372" s="2" t="s">
         <v>476</v>
@@ -22756,7 +22758,7 @@
         <v>449</v>
       </c>
       <c r="M372" s="10" t="str">
-        <f>IF(OR(O372&lt;&gt;"", Q372&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N372" s="2" t="s">
@@ -22793,11 +22795,11 @@
         <v>697</v>
       </c>
       <c r="I373" s="10" t="str">
-        <f>CONCATENATE(A373, B373,C373,D373,E373,F373,G373,H373)</f>
+        <f t="shared" si="10"/>
         <v>yInvestYear</v>
       </c>
       <c r="J373" s="10" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="K373" s="2" t="s">
         <v>716</v>
@@ -22806,7 +22808,7 @@
         <v>449</v>
       </c>
       <c r="M373" s="10" t="str">
-        <f>IF(OR(O373&lt;&gt;"", Q373&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S373" s="2" t="s">
@@ -22833,11 +22835,11 @@
       </c>
       <c r="H374" s="10"/>
       <c r="I374" s="10" t="str">
-        <f>CONCATENATE(A374, B374,C374,D374,E374,F374,G374,H374)</f>
+        <f t="shared" si="10"/>
         <v>yLabP20</v>
       </c>
       <c r="J374" s="10" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K374" s="6" t="s">
         <v>785</v>
@@ -22846,7 +22848,7 @@
         <v>1024</v>
       </c>
       <c r="M374" s="10" t="str">
-        <f>IF(OR(O374&lt;&gt;"", Q374&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R374" s="4" t="s">
@@ -22876,11 +22878,11 @@
       </c>
       <c r="H375" s="10"/>
       <c r="I375" s="10" t="str">
-        <f>CONCATENATE(A375, B375,C375,D375,E375,F375,G375,H375)</f>
+        <f t="shared" si="10"/>
         <v>yLabP40</v>
       </c>
       <c r="J375" s="10" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="K375" s="6" t="s">
         <v>786</v>
@@ -22889,7 +22891,7 @@
         <v>1024</v>
       </c>
       <c r="M375" s="10" t="str">
-        <f>IF(OR(O375&lt;&gt;"", Q375&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R375" s="4" t="s">
@@ -22919,11 +22921,11 @@
       </c>
       <c r="H376" s="10"/>
       <c r="I376" s="10" t="str">
-        <f>CONCATENATE(A376, B376,C376,D376,E376,F376,G376,H376)</f>
+        <f t="shared" si="10"/>
         <v>yLabP60</v>
       </c>
       <c r="J376" s="10" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="K376" s="6" t="s">
         <v>787</v>
@@ -22932,7 +22934,7 @@
         <v>1024</v>
       </c>
       <c r="M376" s="10" t="str">
-        <f>IF(OR(O376&lt;&gt;"", Q376&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R376" s="4" t="s">
@@ -22962,11 +22964,11 @@
       </c>
       <c r="H377" s="10"/>
       <c r="I377" s="10" t="str">
-        <f>CONCATENATE(A377, B377,C377,D377,E377,F377,G377,H377)</f>
+        <f t="shared" si="10"/>
         <v>yLabP80</v>
       </c>
       <c r="J377" s="10" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="K377" s="6" t="s">
         <v>788</v>
@@ -22975,7 +22977,7 @@
         <v>1024</v>
       </c>
       <c r="M377" s="10" t="str">
-        <f>IF(OR(O377&lt;&gt;"", Q377&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="R377" s="4" t="s">
@@ -23003,11 +23005,11 @@
       <c r="G378" s="10"/>
       <c r="H378" s="10"/>
       <c r="I378" s="10" t="str">
-        <f>CONCATENATE(A378, B378,C378,D378,E378,F378,G378,H378)</f>
+        <f t="shared" si="10"/>
         <v>yLifeTime</v>
       </c>
       <c r="J378" s="10" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="K378" s="2" t="s">
         <v>1447</v>
@@ -23016,7 +23018,7 @@
         <v>333</v>
       </c>
       <c r="M378" s="10" t="str">
-        <f>IF(OR(O378&lt;&gt;"", Q378&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="Q378" s="6"/>
@@ -23027,7 +23029,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="379" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:22" ht="112" x14ac:dyDescent="0.2">
       <c r="B379" s="10" t="str" cm="1">
         <f t="array" ref="B379">_xlfn.IFS(S379 = Modules!$A$2,Modules!$B$2,S379 = Modules!$A$3,Modules!$B$3,S379 = Modules!$A$4,Modules!$B$4,S379 = Modules!$A$5,Modules!$B$5,S379 = Modules!$A$6,Modules!$B$6,S379 = Modules!$A$7,Modules!$B$7,S379 = Modules!$A$8,Modules!$B$8,S379 = Modules!$A$9,Modules!$B$9,S379 = Modules!$A$10,Modules!$B$10,S379 = Modules!$A$11,Modules!$B$11,S379 = Modules!$A$12,Modules!$B$12, S379 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23045,11 +23047,11 @@
         <v>1056</v>
       </c>
       <c r="I379" s="10" t="str">
-        <f>CONCATENATE(A379, B379,C379,D379,E379,F379,G379,H379)</f>
+        <f t="shared" si="10"/>
         <v>yMiscPersGrossMonth</v>
       </c>
       <c r="J379" s="10" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="K379" s="2" t="s">
         <v>1370</v>
@@ -23058,7 +23060,7 @@
         <v>170</v>
       </c>
       <c r="M379" s="10" t="str">
-        <f>IF(OR(O379&lt;&gt;"", Q379&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N379" s="2" t="s">
@@ -23101,11 +23103,11 @@
         <v>1367</v>
       </c>
       <c r="I380" s="10" t="str">
-        <f>CONCATENATE(A380, B380,C380,D380,E380,F380,G380,H380)</f>
+        <f t="shared" si="10"/>
         <v>yMiscPersGrossMonthL1</v>
       </c>
       <c r="J380" s="10" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="K380" s="2" t="s">
         <v>496</v>
@@ -23114,7 +23116,7 @@
         <v>333</v>
       </c>
       <c r="M380" s="10" t="str">
-        <f>IF(OR(O380&lt;&gt;"", Q380&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S380" s="2" t="s">
@@ -23142,11 +23144,11 @@
         <v>1368</v>
       </c>
       <c r="I381" s="10" t="str">
-        <f>CONCATENATE(A381, B381,C381,D381,E381,F381,G381,H381)</f>
+        <f t="shared" si="10"/>
         <v>yMiscPersGrossMonthL2</v>
       </c>
       <c r="J381" s="10" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="K381" s="2" t="s">
         <v>497</v>
@@ -23155,7 +23157,7 @@
         <v>333</v>
       </c>
       <c r="M381" s="10" t="str">
-        <f>IF(OR(O381&lt;&gt;"", Q381&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S381" s="2" t="s">
@@ -23183,11 +23185,11 @@
         <v>1371</v>
       </c>
       <c r="I382" s="10" t="str">
-        <f>CONCATENATE(A382, B382,C382,D382,E382,F382,G382,H382)</f>
+        <f t="shared" si="10"/>
         <v>yMiscPersGrossMonthL3</v>
       </c>
       <c r="J382" s="10" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="K382" s="2" t="s">
         <v>498</v>
@@ -23196,7 +23198,7 @@
         <v>333</v>
       </c>
       <c r="M382" s="10" t="str">
-        <f>IF(OR(O382&lt;&gt;"", Q382&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="S382" s="2" t="s">
@@ -23206,7 +23208,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="383" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:22" ht="112" x14ac:dyDescent="0.2">
       <c r="B383" s="10" t="str" cm="1">
         <f t="array" ref="B383">_xlfn.IFS(S383 = Modules!$A$2,Modules!$B$2,S383 = Modules!$A$3,Modules!$B$3,S383 = Modules!$A$4,Modules!$B$4,S383 = Modules!$A$5,Modules!$B$5,S383 = Modules!$A$6,Modules!$B$6,S383 = Modules!$A$7,Modules!$B$7,S383 = Modules!$A$8,Modules!$B$8,S383 = Modules!$A$9,Modules!$B$9,S383 = Modules!$A$10,Modules!$B$10,S383 = Modules!$A$11,Modules!$B$11,S383 = Modules!$A$12,Modules!$B$12, S383 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23224,11 +23226,11 @@
         <v>1056</v>
       </c>
       <c r="I383" s="10" t="str">
-        <f>CONCATENATE(A383, B383,C383,D383,E383,F383,G383,H383)</f>
+        <f t="shared" si="10"/>
         <v>yNonBenPersGrossMonth</v>
       </c>
       <c r="J383" s="10" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="K383" s="2" t="s">
         <v>1372</v>
@@ -23237,7 +23239,7 @@
         <v>333</v>
       </c>
       <c r="M383" s="10" t="str">
-        <f>IF(OR(O383&lt;&gt;"", Q383&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N383" s="2" t="s">
@@ -23262,7 +23264,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="384" spans="1:22" ht="32" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B384" s="10" t="str" cm="1">
         <f t="array" ref="B384">_xlfn.IFS(S384 = Modules!$A$2,Modules!$B$2,S384 = Modules!$A$3,Modules!$B$3,S384 = Modules!$A$4,Modules!$B$4,S384 = Modules!$A$5,Modules!$B$5,S384 = Modules!$A$6,Modules!$B$6,S384 = Modules!$A$7,Modules!$B$7,S384 = Modules!$A$8,Modules!$B$8,S384 = Modules!$A$9,Modules!$B$9,S384 = Modules!$A$10,Modules!$B$10,S384 = Modules!$A$11,Modules!$B$11,S384 = Modules!$A$12,Modules!$B$12, S384 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23280,11 +23282,11 @@
         <v>1367</v>
       </c>
       <c r="I384" s="10" t="str">
-        <f>CONCATENATE(A384, B384,C384,D384,E384,F384,G384,H384)</f>
+        <f t="shared" si="10"/>
         <v>yNonBenPersGrossMonthL1</v>
       </c>
       <c r="J384" s="10" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="K384" s="2" t="s">
         <v>492</v>
@@ -23293,7 +23295,7 @@
         <v>333</v>
       </c>
       <c r="M384" s="10" t="str">
-        <f>IF(OR(O384&lt;&gt;"", Q384&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="Q384" s="2" t="s">
@@ -23324,11 +23326,11 @@
         <v>1056</v>
       </c>
       <c r="I385" s="10" t="str">
-        <f>CONCATENATE(A385, B385,C385,D385,E385,F385,G385,H385)</f>
+        <f t="shared" si="10"/>
         <v>yPensPersGrossMonth</v>
       </c>
       <c r="J385" s="10" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="K385" s="2" t="s">
         <v>1369</v>
@@ -23337,7 +23339,7 @@
         <v>333</v>
       </c>
       <c r="M385" s="10" t="str">
-        <f>IF(OR(O385&lt;&gt;"", Q385&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="N385" s="2" t="s">
@@ -23377,11 +23379,11 @@
         <v>1367</v>
       </c>
       <c r="I386" s="10" t="str">
-        <f>CONCATENATE(A386, B386,C386,D386,E386,F386,G386,H386)</f>
+        <f t="shared" ref="I386:I449" si="12">CONCATENATE(A386, B386,C386,D386,E386,F386,G386,H386)</f>
         <v>yPensPersGrossMonthL1</v>
       </c>
       <c r="J386" s="10" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="K386" s="2" t="s">
         <v>494</v>
@@ -23390,7 +23392,7 @@
         <v>333</v>
       </c>
       <c r="M386" s="10" t="str">
-        <f>IF(OR(O386&lt;&gt;"", Q386&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" ref="M386:M393" si="13">IF(OR(O386&lt;&gt;"", Q386&lt;&gt;""),"Yes","No")</f>
         <v>No</v>
       </c>
       <c r="S386" s="2" t="s">
@@ -23418,11 +23420,11 @@
         <v>1368</v>
       </c>
       <c r="I387" s="10" t="str">
-        <f>CONCATENATE(A387, B387,C387,D387,E387,F387,G387,H387)</f>
+        <f t="shared" si="12"/>
         <v>yPensPersGrossMonthL2</v>
       </c>
       <c r="J387" s="10" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="K387" s="2" t="s">
         <v>495</v>
@@ -23431,7 +23433,7 @@
         <v>333</v>
       </c>
       <c r="M387" s="10" t="str">
-        <f>IF(OR(O387&lt;&gt;"", Q387&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S387" s="2" t="s">
@@ -23441,7 +23443,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="388" spans="2:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="2:22" ht="192" x14ac:dyDescent="0.2">
       <c r="B388" s="10" t="str" cm="1">
         <f t="array" ref="B388">_xlfn.IFS(S388 = Modules!$A$2,Modules!$B$2,S388 = Modules!$A$3,Modules!$B$3,S388 = Modules!$A$4,Modules!$B$4,S388 = Modules!$A$5,Modules!$B$5,S388 = Modules!$A$6,Modules!$B$6,S388 = Modules!$A$7,Modules!$B$7,S388 = Modules!$A$8,Modules!$B$8,S388 = Modules!$A$9,Modules!$B$9,S388 = Modules!$A$10,Modules!$B$10,S388 = Modules!$A$11,Modules!$B$11,S388 = Modules!$A$12,Modules!$B$12, S388 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23453,11 +23455,11 @@
         <v>697</v>
       </c>
       <c r="I388" s="10" t="str">
-        <f>CONCATENATE(A388, B388,C388,D388,E388,F388,G388,H388)</f>
+        <f t="shared" si="12"/>
         <v>yPensYear</v>
       </c>
       <c r="J388" s="10" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="K388" s="2" t="s">
         <v>719</v>
@@ -23466,7 +23468,7 @@
         <v>449</v>
       </c>
       <c r="M388" s="10" t="str">
-        <f>IF(OR(O388&lt;&gt;"", Q388&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S388" s="2" t="s">
@@ -23479,7 +23481,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="389" spans="2:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B389" s="10" t="str" cm="1">
         <f t="array" ref="B389">_xlfn.IFS(S389 = Modules!$A$2,Modules!$B$2,S389 = Modules!$A$3,Modules!$B$3,S389 = Modules!$A$4,Modules!$B$4,S389 = Modules!$A$5,Modules!$B$5,S389 = Modules!$A$6,Modules!$B$6,S389 = Modules!$A$7,Modules!$B$7,S389 = Modules!$A$8,Modules!$B$8,S389 = Modules!$A$9,Modules!$B$9,S389 = Modules!$A$10,Modules!$B$10,S389 = Modules!$A$11,Modules!$B$11,S389 = Modules!$A$12,Modules!$B$12, S389 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23497,11 +23499,11 @@
         <v>1056</v>
       </c>
       <c r="I389" s="10" t="str">
-        <f>CONCATENATE(A389, B389,C389,D389,E389,F389,G389,H389)</f>
+        <f t="shared" si="12"/>
         <v>yPersAndPartnerGrossDiffMonth</v>
       </c>
       <c r="J389" s="10" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="K389" s="2" t="s">
         <v>1374</v>
@@ -23510,7 +23512,7 @@
         <v>333</v>
       </c>
       <c r="M389" s="10" t="str">
-        <f>IF(OR(O389&lt;&gt;"", Q389&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>Yes</v>
       </c>
       <c r="N389" s="2" t="s">
@@ -23535,7 +23537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="390" spans="2:22" ht="112" x14ac:dyDescent="0.2">
+    <row r="390" spans="2:22" ht="16" x14ac:dyDescent="0.2">
       <c r="B390" s="10" t="str" cm="1">
         <f t="array" ref="B390">_xlfn.IFS(S390 = Modules!$A$2,Modules!$B$2,S390 = Modules!$A$3,Modules!$B$3,S390 = Modules!$A$4,Modules!$B$4,S390 = Modules!$A$5,Modules!$B$5,S390 = Modules!$A$6,Modules!$B$6,S390 = Modules!$A$7,Modules!$B$7,S390 = Modules!$A$8,Modules!$B$8,S390 = Modules!$A$9,Modules!$B$9,S390 = Modules!$A$10,Modules!$B$10,S390 = Modules!$A$11,Modules!$B$11,S390 = Modules!$A$12,Modules!$B$12, S390 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23553,11 +23555,11 @@
         <v>1367</v>
       </c>
       <c r="I390" s="10" t="str">
-        <f>CONCATENATE(A390, B390,C390,D390,E390,F390,G390,H390)</f>
+        <f t="shared" si="12"/>
         <v>yPersAndPartnerGrossDiffMonthL1</v>
       </c>
       <c r="J390" s="10" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="K390" s="2" t="s">
         <v>502</v>
@@ -23566,7 +23568,7 @@
         <v>333</v>
       </c>
       <c r="M390" s="10" t="str">
-        <f>IF(OR(O390&lt;&gt;"", Q390&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S390" s="2" t="s">
@@ -23576,7 +23578,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="391" spans="2:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B391" s="10" t="str" cm="1">
         <f t="array" ref="B391">_xlfn.IFS(S391 = Modules!$A$2,Modules!$B$2,S391 = Modules!$A$3,Modules!$B$3,S391 = Modules!$A$4,Modules!$B$4,S391 = Modules!$A$5,Modules!$B$5,S391 = Modules!$A$6,Modules!$B$6,S391 = Modules!$A$7,Modules!$B$7,S391 = Modules!$A$8,Modules!$B$8,S391 = Modules!$A$9,Modules!$B$9,S391 = Modules!$A$10,Modules!$B$10,S391 = Modules!$A$11,Modules!$B$11,S391 = Modules!$A$12,Modules!$B$12, S391 = Modules!$A$13,Modules!$B$13)</f>
         <v>y</v>
@@ -23588,7 +23590,7 @@
         <v>968</v>
       </c>
       <c r="I391" s="10" t="str">
-        <f>CONCATENATE(A391, B391,C391,D391,E391,F391,G391,H391)</f>
+        <f t="shared" si="12"/>
         <v>yPvrtyFlag</v>
       </c>
       <c r="J391" s="10" t="s">
@@ -23601,7 +23603,7 @@
         <v>449</v>
       </c>
       <c r="M391" s="10" t="str">
-        <f>IF(OR(O391&lt;&gt;"", Q391&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S391" s="2" t="s">
@@ -23629,7 +23631,7 @@
         <v>1050</v>
       </c>
       <c r="I392" s="10" t="str">
-        <f>CONCATENATE(A392, B392,C392,D392,E392,F392,G392,H392)</f>
+        <f t="shared" si="12"/>
         <v>yPvrtyFlagL1</v>
       </c>
       <c r="J392" s="10" t="s">
@@ -23642,7 +23644,7 @@
         <v>449</v>
       </c>
       <c r="M392" s="10" t="str">
-        <f>IF(OR(O392&lt;&gt;"", Q392&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S392" s="2" t="s">
@@ -23664,7 +23666,7 @@
         <v>1086</v>
       </c>
       <c r="I393" s="10" t="str">
-        <f>CONCATENATE(A393, B393,C393,D393,E393,F393,G393,H393)</f>
+        <f t="shared" si="12"/>
         <v>yWageDesired</v>
       </c>
       <c r="J393" s="10" t="s">
@@ -23677,7 +23679,7 @@
         <v>333</v>
       </c>
       <c r="M393" s="10" t="str">
-        <f>IF(OR(O393&lt;&gt;"", Q393&lt;&gt;""),"Yes","No")</f>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="S393" s="2" t="s">
